--- a/Financial Analysis/RDDT.xlsx
+++ b/Financial Analysis/RDDT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B72066-CF37-4D12-8C62-4014419D8972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54644B2E-C1E2-4EDE-ACD2-851B97493132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{36256194-E29F-4FBF-A799-FCE3EDFD57DF}"/>
   </bookViews>
@@ -291,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -310,7 +310,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,14 +381,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -406,7 +405,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9022080" y="7620"/>
+          <a:off x="10233660" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -754,17 +753,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>96.02</v>
+        <v>246.5</v>
       </c>
       <c r="E3" s="11">
-        <v>45751</v>
+        <v>45887</v>
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45887</v>
       </c>
       <c r="G3" s="11">
-        <v>45790</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -772,8 +771,8 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f>185.4</f>
+        <v>185.4</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>62</v>
@@ -785,7 +784,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>17715.689999999999</v>
+        <v>45701.1</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -793,11 +792,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <f>635.7+1315.4</f>
-        <v>1951.1000000000001</v>
+        <f>734.1+1325.9</f>
+        <v>2060</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -808,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -817,7 +816,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>1951.1000000000001</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -826,7 +825,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>15764.589999999998</v>
+        <v>43641.1</v>
       </c>
     </row>
   </sheetData>
@@ -969,16 +968,13 @@
         <v>392.4</v>
       </c>
       <c r="P3" s="7">
-        <f>L3*1.45</f>
-        <v>407.73999999999995</v>
+        <v>499.6</v>
       </c>
       <c r="Q3" s="7">
-        <f>M3*1.25</f>
-        <v>435.5</v>
+        <v>540</v>
       </c>
       <c r="R3" s="7">
-        <f>N3*1.2</f>
-        <v>513.24</v>
+        <v>600</v>
       </c>
       <c r="T3" s="7">
         <v>666.7</v>
@@ -992,47 +988,47 @@
       </c>
       <c r="W3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>1748.8799999999999</v>
+        <v>2032</v>
       </c>
       <c r="X3" s="7">
-        <f>W3*1.17</f>
-        <v>2046.1895999999997</v>
+        <f>W3*1.4</f>
+        <v>2844.7999999999997</v>
       </c>
       <c r="Y3" s="7">
-        <f>X3*1.13</f>
-        <v>2312.1942479999993</v>
+        <f>X3*1.3</f>
+        <v>3698.24</v>
       </c>
       <c r="Z3" s="7">
-        <f>Y3*1.11</f>
-        <v>2566.5356152799995</v>
+        <f>Y3*1.15</f>
+        <v>4252.9759999999997</v>
       </c>
       <c r="AA3" s="7">
-        <f>Z3*1.07</f>
-        <v>2746.1931083495997</v>
+        <f>Z3*1.08</f>
+        <v>4593.2140799999997</v>
       </c>
       <c r="AB3" s="7">
-        <f>AA3*1.05</f>
-        <v>2883.5027637670796</v>
+        <f>AA3*1.06</f>
+        <v>4868.8069248000002</v>
       </c>
       <c r="AC3" s="7">
         <f>AB3*1.04</f>
-        <v>2998.8428743177628</v>
+        <v>5063.5592017920007</v>
       </c>
       <c r="AD3" s="7">
         <f>AC3*1.03</f>
-        <v>3088.8081605472958</v>
+        <v>5215.4659778457608</v>
       </c>
       <c r="AE3" s="7">
         <f t="shared" ref="AE3:AG3" si="0">AD3*1.03</f>
-        <v>3181.4724053637146</v>
+        <v>5371.9299571811334</v>
       </c>
       <c r="AF3" s="7">
         <f t="shared" si="0"/>
-        <v>3276.9165775246261</v>
+        <v>5533.0878558965678</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" si="0"/>
-        <v>3375.224074850365</v>
+        <v>5699.0804915734652</v>
       </c>
     </row>
     <row r="4" spans="1:143" x14ac:dyDescent="0.3">
@@ -1067,16 +1063,15 @@
         <v>37.1</v>
       </c>
       <c r="P4" s="2">
-        <f t="shared" ref="P4:R4" si="1">P3-P5</f>
-        <v>36.696599999999989</v>
+        <v>45.9</v>
       </c>
       <c r="Q4" s="2">
-        <f t="shared" si="1"/>
-        <v>39.194999999999993</v>
+        <f t="shared" ref="Q4:R4" si="1">Q3-Q5</f>
+        <v>48.599999999999966</v>
       </c>
       <c r="R4" s="2">
         <f t="shared" si="1"/>
-        <v>41.059199999999976</v>
+        <v>48</v>
       </c>
       <c r="T4" s="2">
         <v>104.8</v>
@@ -1088,17 +1083,17 @@
         <f>SUM(K4:N4)</f>
         <v>123.5</v>
       </c>
-      <c r="W4" s="12">
+      <c r="W4" s="2">
         <f>SUM(O4:R4)</f>
-        <v>154.05079999999995</v>
+        <v>179.59999999999997</v>
       </c>
       <c r="X4" s="2">
         <f>SUM(M4:T4)</f>
-        <v>325.25079999999997</v>
+        <v>350.79999999999995</v>
       </c>
       <c r="Y4" s="2">
         <f>SUM(N4:U4)</f>
-        <v>401.65079999999995</v>
+        <v>427.2</v>
       </c>
       <c r="Z4" s="2">
         <f t="shared" ref="Z4:AG4" si="2">SUM(S4:V4)</f>
@@ -1106,31 +1101,31 @@
       </c>
       <c r="AA4" s="2">
         <f t="shared" si="2"/>
-        <v>493.35079999999994</v>
+        <v>518.9</v>
       </c>
       <c r="AB4" s="2">
         <f t="shared" si="2"/>
-        <v>713.80160000000001</v>
+        <v>764.89999999999986</v>
       </c>
       <c r="AC4" s="2">
         <f t="shared" si="2"/>
-        <v>1004.4523999999999</v>
+        <v>1081.0999999999999</v>
       </c>
       <c r="AD4" s="2">
         <f t="shared" si="2"/>
-        <v>1220.2523999999999</v>
+        <v>1296.8999999999999</v>
       </c>
       <c r="AE4" s="2">
         <f t="shared" si="2"/>
-        <v>1559.5523999999998</v>
+        <v>1636.1999999999998</v>
       </c>
       <c r="AF4" s="2">
         <f t="shared" si="2"/>
-        <v>1948.1031999999998</v>
+        <v>2050.3000000000002</v>
       </c>
       <c r="AG4" s="2">
         <f t="shared" si="2"/>
-        <v>2550.9047999999998</v>
+        <v>2704.2</v>
       </c>
     </row>
     <row r="5" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1139,7 +1134,7 @@
         <v>12</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" ref="G5:O5" si="3">G3-G4</f>
+        <f t="shared" ref="G5:P5" si="3">G3-G4</f>
         <v>136.79999999999998</v>
       </c>
       <c r="H5" s="7">
@@ -1175,16 +1170,16 @@
         <v>355.29999999999995</v>
       </c>
       <c r="P5" s="7">
-        <f>P3*0.91</f>
-        <v>371.04339999999996</v>
+        <f t="shared" si="3"/>
+        <v>453.70000000000005</v>
       </c>
       <c r="Q5" s="7">
-        <f t="shared" ref="Q5:R5" si="4">Q3*0.91</f>
-        <v>396.30500000000001</v>
+        <f t="shared" ref="Q5" si="4">Q3*0.91</f>
+        <v>491.40000000000003</v>
       </c>
       <c r="R5" s="7">
         <f>R3*0.92</f>
-        <v>472.18080000000003</v>
+        <v>552</v>
       </c>
       <c r="T5" s="7">
         <f>T3-T4</f>
@@ -1200,47 +1195,47 @@
       </c>
       <c r="W5" s="7">
         <f>W3-W4</f>
-        <v>1594.8291999999999</v>
+        <v>1852.4</v>
       </c>
       <c r="X5" s="7">
         <f>X3*0.92</f>
-        <v>1882.4944319999997</v>
+        <v>2617.2159999999999</v>
       </c>
       <c r="Y5" s="7">
         <f t="shared" ref="Y5:AG5" si="5">Y3*0.92</f>
-        <v>2127.2187081599996</v>
+        <v>3402.3807999999999</v>
       </c>
       <c r="Z5" s="7">
         <f t="shared" si="5"/>
-        <v>2361.2127660575998</v>
+        <v>3912.73792</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="5"/>
-        <v>2526.4976596816318</v>
+        <v>4225.7569536000001</v>
       </c>
       <c r="AB5" s="7">
         <f t="shared" si="5"/>
-        <v>2652.8225426657132</v>
+        <v>4479.3023708159999</v>
       </c>
       <c r="AC5" s="7">
         <f t="shared" si="5"/>
-        <v>2758.9354443723419</v>
+        <v>4658.4744656486409</v>
       </c>
       <c r="AD5" s="7">
         <f t="shared" si="5"/>
-        <v>2841.7035077035121</v>
+        <v>4798.2286996181001</v>
       </c>
       <c r="AE5" s="7">
         <f t="shared" si="5"/>
-        <v>2926.9546129346177</v>
+        <v>4942.1755606066426</v>
       </c>
       <c r="AF5" s="7">
         <f t="shared" si="5"/>
-        <v>3014.7632513226563</v>
+        <v>5090.4408274248426</v>
       </c>
       <c r="AG5" s="7">
         <f t="shared" si="5"/>
-        <v>3105.2061488623358</v>
+        <v>5243.154052247588</v>
       </c>
     </row>
     <row r="6" spans="1:143" x14ac:dyDescent="0.3">
@@ -1275,8 +1270,7 @@
         <v>191.3</v>
       </c>
       <c r="P6" s="2">
-        <f>L6*1.3</f>
-        <v>185.64000000000001</v>
+        <v>196.6</v>
       </c>
       <c r="Q6" s="2">
         <f>M6*1.2</f>
@@ -1296,49 +1290,49 @@
         <f>SUM(K6:N6)</f>
         <v>935.1</v>
       </c>
-      <c r="W6" s="12">
+      <c r="W6" s="2">
         <f>SUM(O6:R6)</f>
-        <v>803.3</v>
+        <v>814.26</v>
       </c>
       <c r="X6" s="2">
         <f t="shared" ref="X6:Y6" si="6">W6*1.05</f>
-        <v>843.46500000000003</v>
+        <v>854.97300000000007</v>
       </c>
       <c r="Y6" s="2">
         <f t="shared" si="6"/>
-        <v>885.63825000000008</v>
+        <v>897.72165000000007</v>
       </c>
       <c r="Z6" s="2">
         <f>Y6*1.04</f>
-        <v>921.06378000000007</v>
+        <v>933.63051600000006</v>
       </c>
       <c r="AA6" s="2">
         <f>Z6*1.03</f>
-        <v>948.6956934000001</v>
+        <v>961.6394314800001</v>
       </c>
       <c r="AB6" s="2">
         <f t="shared" ref="AB6:AG6" si="7">AA6*1.03</f>
-        <v>977.15656420200014</v>
+        <v>990.48861442440011</v>
       </c>
       <c r="AC6" s="2">
         <f t="shared" si="7"/>
-        <v>1006.4712611280602</v>
+        <v>1020.2032728571321</v>
       </c>
       <c r="AD6" s="2">
         <f t="shared" si="7"/>
-        <v>1036.6653989619019</v>
+        <v>1050.8093710428461</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="7"/>
-        <v>1067.765360930759</v>
+        <v>1082.3336521741314</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="7"/>
-        <v>1099.7983217586818</v>
+        <v>1114.8036617393554</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="7"/>
-        <v>1132.7922714114422</v>
+        <v>1148.2477715915361</v>
       </c>
     </row>
     <row r="7" spans="1:143" x14ac:dyDescent="0.3">
@@ -1373,16 +1367,15 @@
         <v>90.7</v>
       </c>
       <c r="P7" s="2">
-        <f>P3*0.23</f>
-        <v>93.780199999999994</v>
+        <v>120.6</v>
       </c>
       <c r="Q7" s="2">
-        <f>Q3*0.21</f>
-        <v>91.454999999999998</v>
+        <f>Q3*0.24</f>
+        <v>129.6</v>
       </c>
       <c r="R7" s="2">
-        <f>R3*0.19</f>
-        <v>97.515600000000006</v>
+        <f>R3*0.23</f>
+        <v>138</v>
       </c>
       <c r="T7" s="2">
         <v>225.1</v>
@@ -1394,49 +1387,49 @@
         <f>SUM(K7:N7)</f>
         <v>350.6</v>
       </c>
-      <c r="W7" s="12">
+      <c r="W7" s="2">
         <f>SUM(O7:R7)</f>
-        <v>373.45080000000002</v>
+        <v>478.9</v>
       </c>
       <c r="X7" s="2">
-        <f>X3*0.2</f>
-        <v>409.23791999999997</v>
+        <f>X3*0.23</f>
+        <v>654.30399999999997</v>
       </c>
       <c r="Y7" s="2">
-        <f t="shared" ref="Y7:AG7" si="8">Y3*0.2</f>
-        <v>462.43884959999991</v>
+        <f>Y3*0.22</f>
+        <v>813.61279999999999</v>
       </c>
       <c r="Z7" s="2">
-        <f t="shared" si="8"/>
-        <v>513.30712305599991</v>
+        <f>Z3*0.21</f>
+        <v>893.12495999999987</v>
       </c>
       <c r="AA7" s="2">
-        <f t="shared" si="8"/>
-        <v>549.23862166992001</v>
+        <f>AA3*0.2</f>
+        <v>918.64281600000004</v>
       </c>
       <c r="AB7" s="2">
-        <f t="shared" si="8"/>
-        <v>576.70055275341599</v>
+        <f t="shared" ref="AB7:AG7" si="8">AB3*0.2</f>
+        <v>973.7613849600001</v>
       </c>
       <c r="AC7" s="2">
         <f t="shared" si="8"/>
-        <v>599.76857486355254</v>
+        <v>1012.7118403584002</v>
       </c>
       <c r="AD7" s="2">
         <f t="shared" si="8"/>
-        <v>617.76163210945924</v>
+        <v>1043.0931955691522</v>
       </c>
       <c r="AE7" s="2">
         <f t="shared" si="8"/>
-        <v>636.294481072743</v>
+        <v>1074.3859914362267</v>
       </c>
       <c r="AF7" s="2">
         <f t="shared" si="8"/>
-        <v>655.38331550492524</v>
+        <v>1106.6175711793137</v>
       </c>
       <c r="AG7" s="2">
         <f t="shared" si="8"/>
-        <v>675.04481497007305</v>
+        <v>1139.8160983146931</v>
       </c>
     </row>
     <row r="8" spans="1:143" x14ac:dyDescent="0.3">
@@ -1471,12 +1464,11 @@
         <v>69.400000000000006</v>
       </c>
       <c r="P8" s="2">
-        <f>L8*1.1</f>
-        <v>75.350000000000009</v>
+        <v>68.8</v>
       </c>
       <c r="Q8" s="2">
-        <f>M8*1.18</f>
-        <v>77.525999999999996</v>
+        <f>M8*1.1</f>
+        <v>72.27000000000001</v>
       </c>
       <c r="R8" s="2">
         <f>N8*1.14</f>
@@ -1492,49 +1484,49 @@
         <f>SUM(K8:N8)</f>
         <v>451.5</v>
       </c>
-      <c r="W8" s="12">
+      <c r="W8" s="2">
         <f>SUM(O8:R8)</f>
-        <v>306.40800000000002</v>
+        <v>294.60199999999998</v>
       </c>
       <c r="X8" s="2">
         <f>W8*1.03</f>
-        <v>315.60024000000004</v>
+        <v>303.44005999999996</v>
       </c>
       <c r="Y8" s="2">
         <f>X8*1.03</f>
-        <v>325.06824720000003</v>
+        <v>312.54326179999998</v>
       </c>
       <c r="Z8" s="2">
         <f>Y8*1.03</f>
-        <v>334.82029461600001</v>
+        <v>321.91955965400001</v>
       </c>
       <c r="AA8" s="2">
         <f>Z8*1.02</f>
-        <v>341.51670050832001</v>
+        <v>328.35795084708002</v>
       </c>
       <c r="AB8" s="2">
         <f>AA8*1.02</f>
-        <v>348.3470345184864</v>
+        <v>334.92510986402164</v>
       </c>
       <c r="AC8" s="2">
         <f t="shared" ref="AC8:AG8" si="9">AB8*1.02</f>
-        <v>355.31397520885611</v>
+        <v>341.62361206130208</v>
       </c>
       <c r="AD8" s="2">
         <f t="shared" si="9"/>
-        <v>362.42025471303322</v>
+        <v>348.45608430252815</v>
       </c>
       <c r="AE8" s="2">
         <f t="shared" si="9"/>
-        <v>369.66865980729386</v>
+        <v>355.42520598857874</v>
       </c>
       <c r="AF8" s="2">
         <f t="shared" si="9"/>
-        <v>377.06203300343975</v>
+        <v>362.53371010835031</v>
       </c>
       <c r="AG8" s="2">
         <f t="shared" si="9"/>
-        <v>384.60327366350856</v>
+        <v>369.78438431051734</v>
       </c>
     </row>
     <row r="9" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1580,15 +1572,15 @@
       </c>
       <c r="P9" s="7">
         <f t="shared" si="13"/>
-        <v>16.273199999999918</v>
+        <v>67.700000000000045</v>
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="13"/>
-        <v>27.283999999999992</v>
+        <v>89.490000000000066</v>
       </c>
       <c r="R9" s="7">
         <f t="shared" si="13"/>
-        <v>64.213200000000029</v>
+        <v>103.548</v>
       </c>
       <c r="T9" s="7">
         <f>T5-SUM(T6:T8)</f>
@@ -1604,47 +1596,47 @@
       </c>
       <c r="W9" s="7">
         <f>W5-SUM(W6:W8)</f>
-        <v>111.67039999999974</v>
+        <v>264.63800000000037</v>
       </c>
       <c r="X9" s="7">
         <f t="shared" ref="X9:AG9" si="14">X5-SUM(X6:X8)</f>
-        <v>314.1912719999998</v>
+        <v>804.49893999999995</v>
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="14"/>
-        <v>454.07336135999935</v>
+        <v>1378.5030881999999</v>
       </c>
       <c r="Z9" s="7">
         <f t="shared" si="14"/>
-        <v>592.02156838559995</v>
+        <v>1764.0628843460004</v>
       </c>
       <c r="AA9" s="7">
         <f t="shared" si="14"/>
-        <v>687.04664410339183</v>
+        <v>2017.1167552729203</v>
       </c>
       <c r="AB9" s="7">
         <f t="shared" si="14"/>
-        <v>750.61839119181059</v>
+        <v>2180.127261567578</v>
       </c>
       <c r="AC9" s="7">
         <f t="shared" si="14"/>
-        <v>797.38163317187286</v>
+        <v>2283.9357403718068</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="14"/>
-        <v>824.85622191911762</v>
+        <v>2355.8700487035735</v>
       </c>
       <c r="AE9" s="7">
         <f t="shared" si="14"/>
-        <v>853.22611112382174</v>
+        <v>2430.0307110077056</v>
       </c>
       <c r="AF9" s="7">
         <f t="shared" si="14"/>
-        <v>882.51958105560925</v>
+        <v>2506.4858843978227</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="14"/>
-        <v>912.76578881731211</v>
+        <v>2585.3057980308413</v>
       </c>
     </row>
     <row r="10" spans="1:143" x14ac:dyDescent="0.3">
@@ -1679,11 +1671,10 @@
         <v>-20.5</v>
       </c>
       <c r="P10" s="2">
-        <f t="shared" ref="P10:R10" si="15">L10*1.03</f>
-        <v>-21.321000000000002</v>
+        <v>-21.1</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="Q10:R10" si="15">M10*1.03</f>
         <v>-23.69</v>
       </c>
       <c r="R10" s="2">
@@ -1700,49 +1691,49 @@
         <f>SUM(K10:N10)</f>
         <v>-75.400000000000006</v>
       </c>
-      <c r="W10" s="12">
+      <c r="W10" s="2">
         <f>SUM(O10:R10)</f>
-        <v>-83.123999999999995</v>
+        <v>-82.903000000000006</v>
       </c>
       <c r="X10" s="2">
         <f t="shared" ref="X10:AG10" si="16">W10*1.03</f>
-        <v>-85.617719999999991</v>
+        <v>-85.390090000000015</v>
       </c>
       <c r="Y10" s="2">
         <f t="shared" si="16"/>
-        <v>-88.186251599999991</v>
+        <v>-87.951792700000013</v>
       </c>
       <c r="Z10" s="2">
         <f t="shared" si="16"/>
-        <v>-90.831839148</v>
+        <v>-90.590346481000012</v>
       </c>
       <c r="AA10" s="2">
         <f t="shared" si="16"/>
-        <v>-93.556794322439998</v>
+        <v>-93.308056875430012</v>
       </c>
       <c r="AB10" s="2">
         <f t="shared" si="16"/>
-        <v>-96.363498152113195</v>
+        <v>-96.107298581692916</v>
       </c>
       <c r="AC10" s="2">
         <f t="shared" si="16"/>
-        <v>-99.254403096676597</v>
+        <v>-98.99051753914371</v>
       </c>
       <c r="AD10" s="2">
         <f t="shared" si="16"/>
-        <v>-102.23203518957689</v>
+        <v>-101.96023306531802</v>
       </c>
       <c r="AE10" s="2">
         <f t="shared" si="16"/>
-        <v>-105.29899624526421</v>
+        <v>-105.01904005727756</v>
       </c>
       <c r="AF10" s="2">
         <f t="shared" si="16"/>
-        <v>-108.45796613262213</v>
+        <v>-108.1696112589959</v>
       </c>
       <c r="AG10" s="2">
         <f t="shared" si="16"/>
-        <v>-111.7117051166008</v>
+        <v>-111.41469959676579</v>
       </c>
     </row>
     <row r="11" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1788,15 +1779,15 @@
       </c>
       <c r="P11" s="7">
         <f t="shared" si="20"/>
-        <v>37.594199999999915</v>
+        <v>88.80000000000004</v>
       </c>
       <c r="Q11" s="7">
         <f t="shared" si="20"/>
-        <v>50.97399999999999</v>
+        <v>113.18000000000006</v>
       </c>
       <c r="R11" s="7">
         <f t="shared" si="20"/>
-        <v>81.826200000000028</v>
+        <v>121.161</v>
       </c>
       <c r="T11" s="7">
         <f>T9-T10</f>
@@ -1812,47 +1803,47 @@
       </c>
       <c r="W11" s="7">
         <f>W9-W10</f>
-        <v>194.79439999999974</v>
+        <v>347.54100000000039</v>
       </c>
       <c r="X11" s="7">
         <f t="shared" ref="X11:AG11" si="21">X9-X10</f>
-        <v>399.80899199999976</v>
+        <v>889.88902999999993</v>
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="21"/>
-        <v>542.25961295999934</v>
+        <v>1466.4548808999998</v>
       </c>
       <c r="Z11" s="7">
         <f t="shared" si="21"/>
-        <v>682.85340753359992</v>
+        <v>1854.6532308270005</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="21"/>
-        <v>780.60343842583188</v>
+        <v>2110.4248121483502</v>
       </c>
       <c r="AB11" s="7">
         <f t="shared" si="21"/>
-        <v>846.98188934392374</v>
+        <v>2276.2345601492707</v>
       </c>
       <c r="AC11" s="7">
         <f t="shared" si="21"/>
-        <v>896.63603626854945</v>
+        <v>2382.9262579109504</v>
       </c>
       <c r="AD11" s="7">
         <f t="shared" si="21"/>
-        <v>927.08825710869451</v>
+        <v>2457.8302817688914</v>
       </c>
       <c r="AE11" s="7">
         <f t="shared" si="21"/>
-        <v>958.52510736908596</v>
+        <v>2535.049751064983</v>
       </c>
       <c r="AF11" s="7">
         <f t="shared" si="21"/>
-        <v>990.97754718823137</v>
+        <v>2614.6554956568184</v>
       </c>
       <c r="AG11" s="7">
         <f t="shared" si="21"/>
-        <v>1024.4774939339129</v>
+        <v>2696.7204976276071</v>
       </c>
     </row>
     <row r="12" spans="1:143" x14ac:dyDescent="0.3">
@@ -1887,7 +1878,7 @@
         <v>-1.7</v>
       </c>
       <c r="P12" s="2">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="Q12" s="2">
         <v>0</v>
@@ -1905,49 +1896,49 @@
         <f>SUM(K12:N12)</f>
         <v>-0.8</v>
       </c>
-      <c r="W12" s="12">
+      <c r="W12" s="2">
         <f>SUM(O12:R12)</f>
-        <v>-1.7</v>
+        <v>-2.1</v>
       </c>
       <c r="X12" s="2">
         <f t="shared" ref="X12:AG12" si="22">X11*0.15</f>
-        <v>59.971348799999959</v>
+        <v>133.48335449999999</v>
       </c>
       <c r="Y12" s="2">
         <f t="shared" si="22"/>
-        <v>81.338941943999899</v>
+        <v>219.96823213499997</v>
       </c>
       <c r="Z12" s="2">
         <f t="shared" si="22"/>
-        <v>102.42801113003999</v>
+        <v>278.19798462405004</v>
       </c>
       <c r="AA12" s="2">
         <f t="shared" si="22"/>
-        <v>117.09051576387478</v>
+        <v>316.56372182225249</v>
       </c>
       <c r="AB12" s="2">
         <f t="shared" si="22"/>
-        <v>127.04728340158856</v>
+        <v>341.43518402239062</v>
       </c>
       <c r="AC12" s="2">
         <f t="shared" si="22"/>
-        <v>134.49540544028241</v>
+        <v>357.43893868664253</v>
       </c>
       <c r="AD12" s="2">
         <f t="shared" si="22"/>
-        <v>139.06323856630416</v>
+        <v>368.67454226533368</v>
       </c>
       <c r="AE12" s="2">
         <f t="shared" si="22"/>
-        <v>143.77876610536288</v>
+        <v>380.25746265974743</v>
       </c>
       <c r="AF12" s="2">
         <f t="shared" si="22"/>
-        <v>148.64663207823469</v>
+        <v>392.19832434852276</v>
       </c>
       <c r="AG12" s="2">
         <f t="shared" si="22"/>
-        <v>153.67162409008694</v>
+        <v>404.50807464414106</v>
       </c>
     </row>
     <row r="13" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1993,15 +1984,15 @@
       </c>
       <c r="P13" s="7">
         <f t="shared" si="27"/>
-        <v>37.594199999999915</v>
+        <v>89.200000000000045</v>
       </c>
       <c r="Q13" s="7">
         <f t="shared" si="27"/>
-        <v>50.97399999999999</v>
+        <v>113.18000000000006</v>
       </c>
       <c r="R13" s="7">
         <f t="shared" si="27"/>
-        <v>81.826200000000028</v>
+        <v>121.161</v>
       </c>
       <c r="T13" s="7">
         <f>T11-T12</f>
@@ -2017,487 +2008,487 @@
       </c>
       <c r="W13" s="7">
         <f t="shared" ref="W13" si="28">W11-W12</f>
-        <v>196.49439999999973</v>
+        <v>349.64100000000042</v>
       </c>
       <c r="X13" s="7">
         <f t="shared" ref="X13" si="29">X11-X12</f>
-        <v>339.83764319999977</v>
+        <v>756.40567549999992</v>
       </c>
       <c r="Y13" s="7">
         <f t="shared" ref="Y13" si="30">Y11-Y12</f>
-        <v>460.92067101599946</v>
+        <v>1246.4866487649999</v>
       </c>
       <c r="Z13" s="7">
         <f t="shared" ref="Z13" si="31">Z11-Z12</f>
-        <v>580.42539640355994</v>
+        <v>1576.4552462029505</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" ref="AA13" si="32">AA11-AA12</f>
-        <v>663.51292266195708</v>
+        <v>1793.8610903260976</v>
       </c>
       <c r="AB13" s="7">
         <f t="shared" ref="AB13" si="33">AB11-AB12</f>
-        <v>719.93460594233522</v>
+        <v>1934.7993761268801</v>
       </c>
       <c r="AC13" s="7">
         <f t="shared" ref="AC13" si="34">AC11-AC12</f>
-        <v>762.14063082826704</v>
+        <v>2025.4873192243078</v>
       </c>
       <c r="AD13" s="7">
         <f t="shared" ref="AD13" si="35">AD11-AD12</f>
-        <v>788.0250185423904</v>
+        <v>2089.1557395035579</v>
       </c>
       <c r="AE13" s="7">
         <f t="shared" ref="AE13" si="36">AE11-AE12</f>
-        <v>814.74634126372302</v>
+        <v>2154.7922884052355</v>
       </c>
       <c r="AF13" s="7">
         <f t="shared" ref="AF13" si="37">AF11-AF12</f>
-        <v>842.33091510999668</v>
+        <v>2222.4571713082955</v>
       </c>
       <c r="AG13" s="7">
         <f t="shared" ref="AG13" si="38">AG11-AG12</f>
-        <v>870.80586984382603</v>
+        <v>2292.2124229834662</v>
       </c>
       <c r="AH13" s="6">
         <f>AG13*(1+$AJ$18)</f>
-        <v>862.09781114538771</v>
+        <v>2269.2902987536318</v>
       </c>
       <c r="AI13" s="6">
         <f t="shared" ref="AI13:CT13" si="39">AH13*(1+$AJ$18)</f>
-        <v>853.47683303393387</v>
+        <v>2246.5973957660954</v>
       </c>
       <c r="AJ13" s="6">
         <f t="shared" si="39"/>
-        <v>844.9420647035945</v>
+        <v>2224.1314218084344</v>
       </c>
       <c r="AK13" s="6">
         <f t="shared" si="39"/>
-        <v>836.49264405655856</v>
+        <v>2201.89010759035</v>
       </c>
       <c r="AL13" s="6">
         <f t="shared" si="39"/>
-        <v>828.12771761599299</v>
+        <v>2179.8712065144464</v>
       </c>
       <c r="AM13" s="6">
         <f t="shared" si="39"/>
-        <v>819.84644043983303</v>
+        <v>2158.0724944493018</v>
       </c>
       <c r="AN13" s="6">
         <f t="shared" si="39"/>
-        <v>811.64797603543468</v>
+        <v>2136.4917695048089</v>
       </c>
       <c r="AO13" s="6">
         <f t="shared" si="39"/>
-        <v>803.53149627508037</v>
+        <v>2115.1268518097609</v>
       </c>
       <c r="AP13" s="6">
         <f t="shared" si="39"/>
-        <v>795.49618131232955</v>
+        <v>2093.975583291663</v>
       </c>
       <c r="AQ13" s="6">
         <f t="shared" si="39"/>
-        <v>787.54121949920625</v>
+        <v>2073.0358274587466</v>
       </c>
       <c r="AR13" s="6">
         <f t="shared" si="39"/>
-        <v>779.66580730421413</v>
+        <v>2052.3054691841589</v>
       </c>
       <c r="AS13" s="6">
         <f t="shared" si="39"/>
-        <v>771.86914923117195</v>
+        <v>2031.7824144923172</v>
       </c>
       <c r="AT13" s="6">
         <f t="shared" si="39"/>
-        <v>764.15045773886027</v>
+        <v>2011.4645903473941</v>
       </c>
       <c r="AU13" s="6">
         <f t="shared" si="39"/>
-        <v>756.50895316147171</v>
+        <v>1991.3499444439201</v>
       </c>
       <c r="AV13" s="6">
         <f t="shared" si="39"/>
-        <v>748.94386362985699</v>
+        <v>1971.436444999481</v>
       </c>
       <c r="AW13" s="6">
         <f t="shared" si="39"/>
-        <v>741.4544249935584</v>
+        <v>1951.7220805494862</v>
       </c>
       <c r="AX13" s="6">
         <f t="shared" si="39"/>
-        <v>734.0398807436228</v>
+        <v>1932.2048597439914</v>
       </c>
       <c r="AY13" s="6">
         <f t="shared" si="39"/>
-        <v>726.69948193618654</v>
+        <v>1912.8828111465514</v>
       </c>
       <c r="AZ13" s="6">
         <f t="shared" si="39"/>
-        <v>719.43248711682463</v>
+        <v>1893.7539830350859</v>
       </c>
       <c r="BA13" s="6">
         <f t="shared" si="39"/>
-        <v>712.23816224565633</v>
+        <v>1874.8164432047349</v>
       </c>
       <c r="BB13" s="6">
         <f t="shared" si="39"/>
-        <v>705.11578062319973</v>
+        <v>1856.0682787726876</v>
       </c>
       <c r="BC13" s="6">
         <f t="shared" si="39"/>
-        <v>698.0646228169677</v>
+        <v>1837.5075959849607</v>
       </c>
       <c r="BD13" s="6">
         <f t="shared" si="39"/>
-        <v>691.08397658879801</v>
+        <v>1819.132520025111</v>
       </c>
       <c r="BE13" s="6">
         <f t="shared" si="39"/>
-        <v>684.17313682291001</v>
+        <v>1800.9411948248598</v>
       </c>
       <c r="BF13" s="6">
         <f t="shared" si="39"/>
-        <v>677.33140545468086</v>
+        <v>1782.9317828766111</v>
       </c>
       <c r="BG13" s="6">
         <f t="shared" si="39"/>
-        <v>670.558091400134</v>
+        <v>1765.102465047845</v>
       </c>
       <c r="BH13" s="6">
         <f t="shared" si="39"/>
-        <v>663.8525104861327</v>
+        <v>1747.4514403973665</v>
       </c>
       <c r="BI13" s="6">
         <f t="shared" si="39"/>
-        <v>657.21398538127141</v>
+        <v>1729.9769259933928</v>
       </c>
       <c r="BJ13" s="6">
         <f t="shared" si="39"/>
-        <v>650.64184552745871</v>
+        <v>1712.6771567334588</v>
       </c>
       <c r="BK13" s="6">
         <f t="shared" si="39"/>
-        <v>644.13542707218414</v>
+        <v>1695.5503851661242</v>
       </c>
       <c r="BL13" s="6">
         <f t="shared" si="39"/>
-        <v>637.69407280146231</v>
+        <v>1678.594881314463</v>
       </c>
       <c r="BM13" s="6">
         <f t="shared" si="39"/>
-        <v>631.31713207344774</v>
+        <v>1661.8089325013184</v>
       </c>
       <c r="BN13" s="6">
         <f t="shared" si="39"/>
-        <v>625.00396075271328</v>
+        <v>1645.1908431763052</v>
       </c>
       <c r="BO13" s="6">
         <f t="shared" si="39"/>
-        <v>618.75392114518615</v>
+        <v>1628.7389347445421</v>
       </c>
       <c r="BP13" s="6">
         <f t="shared" si="39"/>
-        <v>612.56638193373431</v>
+        <v>1612.4515453970967</v>
       </c>
       <c r="BQ13" s="6">
         <f t="shared" si="39"/>
-        <v>606.44071811439699</v>
+        <v>1596.3270299431256</v>
       </c>
       <c r="BR13" s="6">
         <f t="shared" si="39"/>
-        <v>600.37631093325297</v>
+        <v>1580.3637596436943</v>
       </c>
       <c r="BS13" s="6">
         <f t="shared" si="39"/>
-        <v>594.3725478239204</v>
+        <v>1564.5601220472572</v>
       </c>
       <c r="BT13" s="6">
         <f t="shared" si="39"/>
-        <v>588.42882234568117</v>
+        <v>1548.9145208267846</v>
       </c>
       <c r="BU13" s="6">
         <f t="shared" si="39"/>
-        <v>582.54453412222438</v>
+        <v>1533.4253756185167</v>
       </c>
       <c r="BV13" s="6">
         <f t="shared" si="39"/>
-        <v>576.71908878100214</v>
+        <v>1518.0911218623314</v>
       </c>
       <c r="BW13" s="6">
         <f t="shared" si="39"/>
-        <v>570.95189789319215</v>
+        <v>1502.9102106437081</v>
       </c>
       <c r="BX13" s="6">
         <f t="shared" si="39"/>
-        <v>565.24237891426026</v>
+        <v>1487.8811085372711</v>
       </c>
       <c r="BY13" s="6">
         <f t="shared" si="39"/>
-        <v>559.58995512511763</v>
+        <v>1473.0022974518984</v>
       </c>
       <c r="BZ13" s="6">
         <f t="shared" si="39"/>
-        <v>553.99405557386649</v>
+        <v>1458.2722744773794</v>
       </c>
       <c r="CA13" s="6">
         <f t="shared" si="39"/>
-        <v>548.45411501812782</v>
+        <v>1443.6895517326057</v>
       </c>
       <c r="CB13" s="6">
         <f t="shared" si="39"/>
-        <v>542.96957386794656</v>
+        <v>1429.2526562152796</v>
       </c>
       <c r="CC13" s="6">
         <f t="shared" si="39"/>
-        <v>537.53987812926709</v>
+        <v>1414.9601296531268</v>
       </c>
       <c r="CD13" s="6">
         <f t="shared" si="39"/>
-        <v>532.16447934797441</v>
+        <v>1400.8105283565956</v>
       </c>
       <c r="CE13" s="6">
         <f t="shared" si="39"/>
-        <v>526.84283455449463</v>
+        <v>1386.8024230730296</v>
       </c>
       <c r="CF13" s="6">
         <f t="shared" si="39"/>
-        <v>521.57440620894965</v>
+        <v>1372.9343988422993</v>
       </c>
       <c r="CG13" s="6">
         <f t="shared" si="39"/>
-        <v>516.35866214686018</v>
+        <v>1359.2050548538764</v>
       </c>
       <c r="CH13" s="6">
         <f t="shared" si="39"/>
-        <v>511.19507552539159</v>
+        <v>1345.6130043053377</v>
       </c>
       <c r="CI13" s="6">
         <f t="shared" si="39"/>
-        <v>506.08312477013766</v>
+        <v>1332.1568742622842</v>
       </c>
       <c r="CJ13" s="6">
         <f t="shared" si="39"/>
-        <v>501.02229352243626</v>
+        <v>1318.8353055196612</v>
       </c>
       <c r="CK13" s="6">
         <f t="shared" si="39"/>
-        <v>496.01207058721189</v>
+        <v>1305.6469524644647</v>
       </c>
       <c r="CL13" s="6">
         <f t="shared" si="39"/>
-        <v>491.05194988133979</v>
+        <v>1292.59048293982</v>
       </c>
       <c r="CM13" s="6">
         <f t="shared" si="39"/>
-        <v>486.14143038252638</v>
+        <v>1279.6645781104219</v>
       </c>
       <c r="CN13" s="6">
         <f t="shared" si="39"/>
-        <v>481.28001607870112</v>
+        <v>1266.8679323293177</v>
       </c>
       <c r="CO13" s="6">
         <f t="shared" si="39"/>
-        <v>476.46721591791413</v>
+        <v>1254.1992530060245</v>
       </c>
       <c r="CP13" s="6">
         <f t="shared" si="39"/>
-        <v>471.70254375873498</v>
+        <v>1241.6572604759642</v>
       </c>
       <c r="CQ13" s="6">
         <f t="shared" si="39"/>
-        <v>466.98551832114759</v>
+        <v>1229.2406878712045</v>
       </c>
       <c r="CR13" s="6">
         <f t="shared" si="39"/>
-        <v>462.3156631379361</v>
+        <v>1216.9482809924925</v>
       </c>
       <c r="CS13" s="6">
         <f t="shared" si="39"/>
-        <v>457.69250650655675</v>
+        <v>1204.7787981825677</v>
       </c>
       <c r="CT13" s="6">
         <f t="shared" si="39"/>
-        <v>453.1155814414912</v>
+        <v>1192.731010200742</v>
       </c>
       <c r="CU13" s="6">
         <f t="shared" ref="CU13:EM13" si="40">CT13*(1+$AJ$18)</f>
-        <v>448.58442562707626</v>
+        <v>1180.8037000987347</v>
       </c>
       <c r="CV13" s="6">
         <f t="shared" si="40"/>
-        <v>444.0985813708055</v>
+        <v>1168.9956630977474</v>
       </c>
       <c r="CW13" s="6">
         <f t="shared" si="40"/>
-        <v>439.65759555709747</v>
+        <v>1157.3057064667698</v>
       </c>
       <c r="CX13" s="6">
         <f t="shared" si="40"/>
-        <v>435.26101960152647</v>
+        <v>1145.7326494021022</v>
       </c>
       <c r="CY13" s="6">
         <f t="shared" si="40"/>
-        <v>430.90840940551118</v>
+        <v>1134.2753229080811</v>
       </c>
       <c r="CZ13" s="6">
         <f t="shared" si="40"/>
-        <v>426.59932531145608</v>
+        <v>1122.9325696790002</v>
       </c>
       <c r="DA13" s="6">
         <f t="shared" si="40"/>
-        <v>422.33333205834151</v>
+        <v>1111.7032439822101</v>
       </c>
       <c r="DB13" s="6">
         <f t="shared" si="40"/>
-        <v>418.10999873775808</v>
+        <v>1100.5862115423879</v>
       </c>
       <c r="DC13" s="6">
         <f t="shared" si="40"/>
-        <v>413.92889875038048</v>
+        <v>1089.5803494269639</v>
       </c>
       <c r="DD13" s="6">
         <f t="shared" si="40"/>
-        <v>409.78960976287669</v>
+        <v>1078.6845459326944</v>
       </c>
       <c r="DE13" s="6">
         <f t="shared" si="40"/>
-        <v>405.6917136652479</v>
+        <v>1067.8977004733674</v>
       </c>
       <c r="DF13" s="6">
         <f t="shared" si="40"/>
-        <v>401.63479652859542</v>
+        <v>1057.2187234686337</v>
       </c>
       <c r="DG13" s="6">
         <f t="shared" si="40"/>
-        <v>397.61844856330947</v>
+        <v>1046.6465362339472</v>
       </c>
       <c r="DH13" s="6">
         <f t="shared" si="40"/>
-        <v>393.64226407767637</v>
+        <v>1036.1800708716078</v>
       </c>
       <c r="DI13" s="6">
         <f t="shared" si="40"/>
-        <v>389.70584143689962</v>
+        <v>1025.8182701628916</v>
       </c>
       <c r="DJ13" s="6">
         <f t="shared" si="40"/>
-        <v>385.80878302253063</v>
+        <v>1015.5600874612627</v>
       </c>
       <c r="DK13" s="6">
         <f t="shared" si="40"/>
-        <v>381.95069519230532</v>
+        <v>1005.40448658665</v>
       </c>
       <c r="DL13" s="6">
         <f t="shared" si="40"/>
-        <v>378.13118824038224</v>
+        <v>995.35044172078346</v>
       </c>
       <c r="DM13" s="6">
         <f t="shared" si="40"/>
-        <v>374.34987635797842</v>
+        <v>985.39693730357567</v>
       </c>
       <c r="DN13" s="6">
         <f t="shared" si="40"/>
-        <v>370.60637759439862</v>
+        <v>975.54296793053993</v>
       </c>
       <c r="DO13" s="6">
         <f t="shared" si="40"/>
-        <v>366.90031381845461</v>
+        <v>965.78753825123454</v>
       </c>
       <c r="DP13" s="6">
         <f t="shared" si="40"/>
-        <v>363.23131068027004</v>
+        <v>956.12966286872222</v>
       </c>
       <c r="DQ13" s="6">
         <f t="shared" si="40"/>
-        <v>359.59899757346733</v>
+        <v>946.56836624003495</v>
       </c>
       <c r="DR13" s="6">
         <f t="shared" si="40"/>
-        <v>356.00300759773268</v>
+        <v>937.1026825776346</v>
       </c>
       <c r="DS13" s="6">
         <f t="shared" si="40"/>
-        <v>352.44297752175532</v>
+        <v>927.73165575185828</v>
       </c>
       <c r="DT13" s="6">
         <f t="shared" si="40"/>
-        <v>348.91854774653774</v>
+        <v>918.4543391943397</v>
       </c>
       <c r="DU13" s="6">
         <f t="shared" si="40"/>
-        <v>345.42936226907239</v>
+        <v>909.26979580239629</v>
       </c>
       <c r="DV13" s="6">
         <f t="shared" si="40"/>
-        <v>341.97506864638166</v>
+        <v>900.17709784437227</v>
       </c>
       <c r="DW13" s="6">
         <f t="shared" si="40"/>
-        <v>338.55531795991783</v>
+        <v>891.17532686592858</v>
       </c>
       <c r="DX13" s="6">
         <f t="shared" si="40"/>
-        <v>335.16976478031864</v>
+        <v>882.26357359726933</v>
       </c>
       <c r="DY13" s="6">
         <f t="shared" si="40"/>
-        <v>331.81806713251547</v>
+        <v>873.44093786129667</v>
       </c>
       <c r="DZ13" s="6">
         <f t="shared" si="40"/>
-        <v>328.49988646119033</v>
+        <v>864.70652848268367</v>
       </c>
       <c r="EA13" s="6">
         <f t="shared" si="40"/>
-        <v>325.21488759657842</v>
+        <v>856.05946319785687</v>
       </c>
       <c r="EB13" s="6">
         <f t="shared" si="40"/>
-        <v>321.96273872061261</v>
+        <v>847.4988685658783</v>
       </c>
       <c r="EC13" s="6">
         <f t="shared" si="40"/>
-        <v>318.74311133340649</v>
+        <v>839.02387988021951</v>
       </c>
       <c r="ED13" s="6">
         <f t="shared" si="40"/>
-        <v>315.55568022007242</v>
+        <v>830.6336410814173</v>
       </c>
       <c r="EE13" s="6">
         <f t="shared" si="40"/>
-        <v>312.40012341787167</v>
+        <v>822.3273046706031</v>
       </c>
       <c r="EF13" s="6">
         <f t="shared" si="40"/>
-        <v>309.27612218369296</v>
+        <v>814.10403162389707</v>
       </c>
       <c r="EG13" s="6">
         <f t="shared" si="40"/>
-        <v>306.18336096185601</v>
+        <v>805.96299130765806</v>
       </c>
       <c r="EH13" s="6">
         <f t="shared" si="40"/>
-        <v>303.12152735223742</v>
+        <v>797.90336139458145</v>
       </c>
       <c r="EI13" s="6">
         <f t="shared" si="40"/>
-        <v>300.09031207871504</v>
+        <v>789.92432778063562</v>
       </c>
       <c r="EJ13" s="6">
         <f t="shared" si="40"/>
-        <v>297.0894089579279</v>
+        <v>782.02508450282926</v>
       </c>
       <c r="EK13" s="6">
         <f t="shared" si="40"/>
-        <v>294.1185148683486</v>
+        <v>774.20483365780092</v>
       </c>
       <c r="EL13" s="6">
         <f t="shared" si="40"/>
-        <v>291.17732971966512</v>
+        <v>766.4627853212229</v>
       </c>
       <c r="EM13" s="6">
         <f t="shared" si="40"/>
-        <v>288.26555642246848</v>
+        <v>758.79815746801069</v>
       </c>
     </row>
     <row r="14" spans="1:143" x14ac:dyDescent="0.3">
@@ -2534,16 +2525,16 @@
         <v>184.5</v>
       </c>
       <c r="P14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f>185.4</f>
+        <v>185.4</v>
       </c>
       <c r="Q14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f>185.4</f>
+        <v>185.4</v>
       </c>
       <c r="R14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f>185.4</f>
+        <v>185.4</v>
       </c>
       <c r="T14" s="2">
         <v>164</v>
@@ -2555,48 +2546,48 @@
         <v>164</v>
       </c>
       <c r="W14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" ref="W14:AG14" si="41">185.4</f>
+        <v>185.4</v>
       </c>
       <c r="X14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="Y14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="Z14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="AA14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="AB14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="AC14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="AD14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="AE14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="AF14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
       <c r="AG14" s="2">
-        <f>129.5+55</f>
-        <v>184.5</v>
+        <f t="shared" si="41"/>
+        <v>185.4</v>
       </c>
     </row>
     <row r="15" spans="1:143" x14ac:dyDescent="0.3">
@@ -2608,15 +2599,15 @@
         <v>-1.0499139414802068</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" ref="H15" si="41">H13/H14</f>
+        <f t="shared" ref="H15" si="42">H13/H14</f>
         <v>-0.70085470085470147</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" ref="I15" si="42">I13/I14</f>
+        <f t="shared" ref="I15" si="43">I13/I14</f>
         <v>-0.12563667232597614</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" ref="J15" si="43">J13/J14</f>
+        <f t="shared" ref="J15" si="44">J13/J14</f>
         <v>0.30655737704918024</v>
       </c>
       <c r="K15" s="5">
@@ -2624,32 +2615,32 @@
         <v>-8.1908831908831914</v>
       </c>
       <c r="L15" s="5">
-        <f t="shared" ref="L15:N15" si="44">L13/L14</f>
+        <f t="shared" ref="L15:N15" si="45">L13/L14</f>
         <v>-6.2043795620438102E-2</v>
       </c>
       <c r="M15" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.1767139479905436</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.39303482587064642</v>
       </c>
       <c r="O15" s="5">
-        <f t="shared" ref="O15:R15" si="45">O13/O14</f>
+        <f t="shared" ref="O15:R15" si="46">O13/O14</f>
         <v>0.14146341463414622</v>
       </c>
       <c r="P15" s="5">
-        <f t="shared" si="45"/>
-        <v>0.20376260162601581</v>
+        <f t="shared" si="46"/>
+        <v>0.481121898597627</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="45"/>
-        <v>0.2762818428184281</v>
+        <f t="shared" si="46"/>
+        <v>0.61046386192017288</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="45"/>
-        <v>0.4435024390243904</v>
+        <f t="shared" si="46"/>
+        <v>0.65351132686084146</v>
       </c>
       <c r="T15" s="5">
         <f>T13/T14</f>
@@ -2664,48 +2655,48 @@
         <v>-2.9524390243902445</v>
       </c>
       <c r="W15" s="5">
-        <f t="shared" ref="W15" si="46">W13/W14</f>
-        <v>1.0650102981029796</v>
+        <f t="shared" ref="W15" si="47">W13/W14</f>
+        <v>1.8858737864077693</v>
       </c>
       <c r="X15" s="5">
-        <f t="shared" ref="X15" si="47">X13/X14</f>
-        <v>1.841938445528454</v>
+        <f t="shared" ref="X15" si="48">X13/X14</f>
+        <v>4.0798580124056087</v>
       </c>
       <c r="Y15" s="5">
-        <f t="shared" ref="Y15" si="48">Y13/Y14</f>
-        <v>2.4982150190569077</v>
+        <f t="shared" ref="Y15" si="49">Y13/Y14</f>
+        <v>6.7232289577400213</v>
       </c>
       <c r="Z15" s="5">
-        <f t="shared" ref="Z15" si="49">Z13/Z14</f>
-        <v>3.1459371078783738</v>
+        <f t="shared" ref="Z15" si="50">Z13/Z14</f>
+        <v>8.5029948554635943</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" ref="AA15" si="50">AA13/AA14</f>
-        <v>3.5962760035878434</v>
+        <f t="shared" ref="AA15" si="51">AA13/AA14</f>
+        <v>9.6756261614136871</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" ref="AB15" si="51">AB13/AB14</f>
-        <v>3.9020845850533075</v>
+        <f t="shared" ref="AB15" si="52">AB13/AB14</f>
+        <v>10.435811090220497</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" ref="AC15" si="52">AC13/AC14</f>
-        <v>4.1308435275244824</v>
+        <f t="shared" ref="AC15" si="53">AC13/AC14</f>
+        <v>10.924958571867895</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" ref="AD15" si="53">AD13/AD14</f>
-        <v>4.2711383118828747</v>
+        <f t="shared" ref="AD15" si="54">AD13/AD14</f>
+        <v>11.26836968448521</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" ref="AE15" si="54">AE13/AE14</f>
-        <v>4.4159693293426718</v>
+        <f t="shared" ref="AE15" si="55">AE13/AE14</f>
+        <v>11.622396377590267</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" ref="AF15" si="55">AF13/AF14</f>
-        <v>4.5654792146883292</v>
+        <f t="shared" ref="AF15" si="56">AF13/AF14</f>
+        <v>11.98736338353989</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" ref="AG15" si="56">AG13/AG14</f>
-        <v>4.7198150127036644</v>
+        <f t="shared" ref="AG15" si="57">AG13/AG14</f>
+        <v>12.363605301960444</v>
       </c>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.3">
@@ -2721,32 +2712,32 @@
         <v>0.48442272449602952</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" ref="L17:N17" si="57">L3/H3-1</f>
+        <f t="shared" ref="L17:N17" si="58">L3/H3-1</f>
         <v>0.53661202185792334</v>
       </c>
       <c r="M17" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.67903614457831307</v>
       </c>
       <c r="N17" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.71216973578863074</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" ref="O17" si="58">O3/K3-1</f>
+        <f t="shared" ref="O17" si="59">O3/K3-1</f>
         <v>0.6148148148148147</v>
       </c>
       <c r="P17" s="8">
-        <f t="shared" ref="P17" si="59">P3/L3-1</f>
-        <v>0.44999999999999996</v>
+        <f t="shared" ref="P17" si="60">P3/L3-1</f>
+        <v>0.77667140825035585</v>
       </c>
       <c r="Q17" s="8">
-        <f t="shared" ref="Q17" si="60">Q3/M3-1</f>
-        <v>0.25</v>
+        <f t="shared" ref="Q17" si="61">Q3/M3-1</f>
+        <v>0.54994259471871421</v>
       </c>
       <c r="R17" s="8">
-        <f t="shared" ref="R17" si="61">R3/N3-1</f>
-        <v>0.19999999999999996</v>
+        <f t="shared" ref="R17" si="62">R3/N3-1</f>
+        <v>0.40285246668225394</v>
       </c>
       <c r="T17" s="8"/>
       <c r="U17" s="8">
@@ -2754,51 +2745,51 @@
         <v>0.2059397030148491</v>
       </c>
       <c r="V17" s="8">
-        <f t="shared" ref="V17:AG17" si="62">V3/U3-1</f>
+        <f t="shared" ref="V17:AG17" si="63">V3/U3-1</f>
         <v>0.61728855721393039</v>
       </c>
       <c r="W17" s="8">
-        <f t="shared" si="62"/>
-        <v>0.34498192724755827</v>
+        <f t="shared" si="63"/>
+        <v>0.56271629623932951</v>
       </c>
       <c r="X17" s="8">
-        <f t="shared" si="62"/>
-        <v>0.16999999999999993</v>
+        <f t="shared" si="63"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" si="62"/>
-        <v>0.12999999999999989</v>
+        <f t="shared" si="63"/>
+        <v>0.30000000000000004</v>
       </c>
       <c r="Z17" s="8">
-        <f t="shared" si="62"/>
-        <v>0.1100000000000001</v>
+        <f t="shared" si="63"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AA17" s="8">
-        <f t="shared" si="62"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="63"/>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AB17" s="8">
-        <f t="shared" si="62"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="63"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AC17" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE17" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF17" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG17" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -2807,19 +2798,19 @@
         <v>35</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" ref="G18:J18" si="63">G5/G3</f>
+        <f t="shared" ref="G18:J18" si="64">G5/G3</f>
         <v>0.83567501527183863</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.84262295081967209</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.8727710843373494</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.88430744595676536</v>
       </c>
       <c r="K18" s="8">
@@ -2827,31 +2818,31 @@
         <v>0.88641975308641974</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" ref="L18:N18" si="64">L5/L3</f>
+        <f t="shared" ref="L18:N18" si="65">L5/L3</f>
         <v>0.89509246088193462</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.90068886337543042</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.92564881926584053</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" ref="O18:R18" si="65">O5/O3</f>
+        <f t="shared" ref="O18:R18" si="66">O5/O3</f>
         <v>0.90545361875637098</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
+        <v>0.90812650120096083</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="66"/>
         <v>0.91</v>
       </c>
-      <c r="Q18" s="8">
-        <f t="shared" si="65"/>
-        <v>0.91</v>
-      </c>
       <c r="R18" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.92</v>
       </c>
       <c r="T18" s="8">
@@ -2863,51 +2854,51 @@
         <v>0.86194029850746268</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" ref="V18:AG18" si="66">V5/V3</f>
+        <f t="shared" ref="V18:AG18" si="67">V5/V3</f>
         <v>0.90502191801891874</v>
       </c>
       <c r="W18" s="8">
-        <f t="shared" si="66"/>
-        <v>0.91191459677050457</v>
+        <f t="shared" si="67"/>
+        <v>0.91161417322834648</v>
       </c>
       <c r="X18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.92</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.92</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.92</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.92</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.91999999999999993</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.92</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.92</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
+        <v>0.91999999999999993</v>
+      </c>
+      <c r="AF18" s="8">
+        <f t="shared" si="67"/>
         <v>0.92</v>
       </c>
-      <c r="AF18" s="8">
-        <f t="shared" si="66"/>
-        <v>0.92</v>
-      </c>
       <c r="AG18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.92</v>
       </c>
       <c r="AI18" t="s">
@@ -2930,31 +2921,31 @@
         <v>3.0165441176470589</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" ref="L19:N19" si="67">L6/H6-1</f>
+        <f t="shared" ref="L19:N19" si="68">L6/H6-1</f>
         <v>0.30173199635369197</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.53924284395198518</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.68996415770609332</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" ref="O19" si="68">O6/K6-1</f>
+        <f t="shared" ref="O19" si="69">O6/K6-1</f>
         <v>-0.56224256292906172</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" ref="P19" si="69">P6/L6-1</f>
-        <v>0.30000000000000004</v>
+        <f t="shared" ref="P19" si="70">P6/L6-1</f>
+        <v>0.37675070028011182</v>
       </c>
       <c r="Q19" s="8">
-        <f t="shared" ref="Q19" si="70">Q6/M6-1</f>
+        <f t="shared" ref="Q19" si="71">Q6/M6-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="R19" s="8">
-        <f t="shared" ref="R19" si="71">R6/N6-1</f>
+        <f t="shared" ref="R19" si="72">R6/N6-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="T19" s="8"/>
@@ -2963,51 +2954,51 @@
         <v>0.20016429353778764</v>
       </c>
       <c r="V19" s="8">
-        <f t="shared" ref="V19:AG19" si="72">V6/U6-1</f>
+        <f t="shared" ref="V19:AG19" si="73">V6/U6-1</f>
         <v>1.1334702258726899</v>
       </c>
       <c r="W19" s="8">
-        <f t="shared" si="72"/>
-        <v>-0.14094749224681857</v>
+        <f t="shared" si="73"/>
+        <v>-0.12922682066089186</v>
       </c>
       <c r="X19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Y19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Z19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AA19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG19" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI19" t="s">
@@ -3022,19 +3013,19 @@
         <v>37</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" ref="G20:J20" si="73">G7/G3</f>
+        <f t="shared" ref="G20:J20" si="74">G7/G3</f>
         <v>0.3536957849725107</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.32349726775956283</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.26554216867469882</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.23178542834267413</v>
       </c>
       <c r="K20" s="8">
@@ -3042,32 +3033,32 @@
         <v>0.51069958847736618</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" ref="L20:N20" si="74">L7/L3</f>
+        <f t="shared" ref="L20:N20" si="75">L7/L3</f>
         <v>0.25426742532005692</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.21383467278989668</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.18821603927986907</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" ref="O20:R20" si="75">O7/O3</f>
+        <f t="shared" ref="O20:R20" si="76">O7/O3</f>
         <v>0.2311416921508665</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
+        <v>0.24139311449159326</v>
+      </c>
+      <c r="Q20" s="8">
+        <f t="shared" si="76"/>
+        <v>0.24</v>
+      </c>
+      <c r="R20" s="8">
+        <f t="shared" si="76"/>
         <v>0.23</v>
-      </c>
-      <c r="Q20" s="8">
-        <f t="shared" si="75"/>
-        <v>0.21</v>
-      </c>
-      <c r="R20" s="8">
-        <f t="shared" si="75"/>
-        <v>0.19</v>
       </c>
       <c r="T20" s="8">
         <f>T7/T3</f>
@@ -3078,51 +3069,51 @@
         <v>0.28631840796019897</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" ref="V20:AG20" si="76">V7/V3</f>
+        <f t="shared" ref="V20:AG20" si="77">V7/V3</f>
         <v>0.26963008536491584</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" si="76"/>
-        <v>0.2135371209002333</v>
+        <f t="shared" si="77"/>
+        <v>0.23567913385826769</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
+        <v>0.23</v>
+      </c>
+      <c r="Y20" s="8">
+        <f t="shared" si="77"/>
+        <v>0.22</v>
+      </c>
+      <c r="Z20" s="8">
+        <f t="shared" si="77"/>
+        <v>0.21</v>
+      </c>
+      <c r="AA20" s="8">
+        <f t="shared" si="77"/>
         <v>0.2</v>
       </c>
-      <c r="Y20" s="8">
-        <f t="shared" si="76"/>
+      <c r="AB20" s="8">
+        <f t="shared" si="77"/>
         <v>0.2</v>
       </c>
-      <c r="Z20" s="8">
-        <f t="shared" si="76"/>
+      <c r="AC20" s="8">
+        <f t="shared" si="77"/>
         <v>0.2</v>
       </c>
-      <c r="AA20" s="8">
-        <f t="shared" si="76"/>
+      <c r="AD20" s="8">
+        <f t="shared" si="77"/>
         <v>0.2</v>
       </c>
-      <c r="AB20" s="8">
-        <f t="shared" si="76"/>
+      <c r="AE20" s="8">
+        <f t="shared" si="77"/>
         <v>0.2</v>
       </c>
-      <c r="AC20" s="8">
-        <f t="shared" si="76"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="AD20" s="8">
-        <f t="shared" si="76"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AE20" s="8">
-        <f t="shared" si="76"/>
+      <c r="AF20" s="8">
+        <f t="shared" si="77"/>
         <v>0.2</v>
       </c>
-      <c r="AF20" s="8">
-        <f t="shared" si="76"/>
-        <v>0.2</v>
-      </c>
       <c r="AG20" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.2</v>
       </c>
       <c r="AI20" t="s">
@@ -3130,7 +3121,7 @@
       </c>
       <c r="AJ20" s="2">
         <f>NPV(AJ19,W13:EM13)</f>
-        <v>8320.6591379964448</v>
+        <v>21774.856271998346</v>
       </c>
     </row>
     <row r="21" spans="2:36" x14ac:dyDescent="0.3">
@@ -3142,35 +3133,35 @@
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8">
-        <f t="shared" ref="K21" si="77">K8/G8-1</f>
+        <f t="shared" ref="K21" si="78">K8/G8-1</f>
         <v>4.9681372549019613</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" ref="L21" si="78">L8/H8-1</f>
+        <f t="shared" ref="L21" si="79">L8/H8-1</f>
         <v>0.79319371727748678</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" ref="M21" si="79">M8/I8-1</f>
+        <f t="shared" ref="M21" si="80">M8/I8-1</f>
         <v>0.76139410187667589</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" ref="N21" si="80">N8/J8-1</f>
+        <f t="shared" ref="N21" si="81">N8/J8-1</f>
         <v>0.52795031055900621</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" ref="O21" si="81">O8/K8-1</f>
+        <f t="shared" ref="O21" si="82">O8/K8-1</f>
         <v>-0.71498973305954827</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21" si="82">P8/L8-1</f>
+        <f t="shared" ref="P21" si="83">P8/L8-1</f>
+        <v>4.3795620437956373E-3</v>
+      </c>
+      <c r="Q21" s="8">
+        <f t="shared" ref="Q21" si="84">Q8/M8-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="Q21" s="8">
-        <f t="shared" ref="Q21" si="83">Q8/M8-1</f>
-        <v>0.17999999999999994</v>
-      </c>
       <c r="R21" s="8">
-        <f t="shared" ref="R21" si="84">R8/N8-1</f>
+        <f t="shared" ref="R21" si="85">R8/N8-1</f>
         <v>0.1399999999999999</v>
       </c>
       <c r="T21" s="8"/>
@@ -3179,51 +3170,51 @@
         <v>0.14534075104311528</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" ref="V21:AG21" si="85">V8/U8-1</f>
+        <f t="shared" ref="V21:AG21" si="86">V8/U8-1</f>
         <v>1.7413479052823315</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" si="85"/>
-        <v>-0.32135548172757467</v>
+        <f t="shared" si="86"/>
+        <v>-0.34750387596899235</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI21" t="s">
@@ -3231,7 +3222,7 @@
       </c>
       <c r="AJ21" s="2">
         <f>Main!D8</f>
-        <v>1951.1000000000001</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.3">
@@ -3239,19 +3230,19 @@
         <v>39</v>
       </c>
       <c r="G22" s="8">
-        <f t="shared" ref="G22:J22" si="86">G9/G3</f>
+        <f t="shared" ref="G22:J22" si="87">G9/G3</f>
         <v>-0.43188759926695186</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-0.28907103825136632</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-9.4457831325301181E-2</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>1.2409927942353859E-2</v>
       </c>
       <c r="K22" s="8">
@@ -3259,32 +3250,32 @@
         <v>-2.4246913580246914</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" ref="L22:N22" si="87">L9/L3</f>
+        <f t="shared" ref="L22:N22" si="88">L9/L3</f>
         <v>-0.11059743954480805</v>
       </c>
       <c r="M22" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1.9804822043627948E-2</v>
       </c>
       <c r="N22" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.12391863455693231</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" ref="O22:R22" si="88">O9/O3</f>
+        <f t="shared" ref="O22:R22" si="89">O9/O3</f>
         <v>9.9388379204892394E-3</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="88"/>
-        <v>3.9910727424338842E-2</v>
+        <f t="shared" si="89"/>
+        <v>0.13550840672538039</v>
       </c>
       <c r="Q22" s="8">
-        <f t="shared" si="88"/>
-        <v>6.264982778415612E-2</v>
+        <f t="shared" si="89"/>
+        <v>0.16572222222222235</v>
       </c>
       <c r="R22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.12511339724105686</v>
+        <f t="shared" si="89"/>
+        <v>0.17258000000000001</v>
       </c>
       <c r="T22" s="8">
         <f>T9/T3</f>
@@ -3295,59 +3286,59 @@
         <v>-0.17437810945273638</v>
       </c>
       <c r="V22" s="8">
-        <f t="shared" ref="V22:AG22" si="89">V9/V3</f>
+        <f t="shared" ref="V22:AG22" si="90">V9/V3</f>
         <v>-0.43097746673844506</v>
       </c>
       <c r="W22" s="8">
-        <f t="shared" si="89"/>
-        <v>6.3852522757421745E-2</v>
+        <f t="shared" si="90"/>
+        <v>0.13023523622047262</v>
       </c>
       <c r="X22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.15354944233906762</v>
+        <f t="shared" si="90"/>
+        <v>0.2827963090551181</v>
       </c>
       <c r="Y22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.19638201321223919</v>
+        <f t="shared" si="90"/>
+        <v>0.37274570828285886</v>
       </c>
       <c r="Z22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.230669531667891</v>
+        <f t="shared" si="90"/>
+        <v>0.41478317402825704</v>
       </c>
       <c r="AA22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.25018147559050991</v>
+        <f t="shared" si="90"/>
+        <v>0.43915147871203086</v>
       </c>
       <c r="AB22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.26031478125277885</v>
+        <f t="shared" si="90"/>
+        <v>0.44777443329345673</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.2658964362556932</v>
+        <f t="shared" si="90"/>
+        <v>0.45105342889316247</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.26704676336162103</v>
+        <f t="shared" si="90"/>
+        <v>0.45170844919913783</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.26818592224321952</v>
+        <f t="shared" si="90"/>
+        <v>0.45235711008466684</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.26931402132985094</v>
+        <f t="shared" si="90"/>
+        <v>0.45299947329169565</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.27043116799816558</v>
+        <f t="shared" si="90"/>
+        <v>0.45363559996273389</v>
       </c>
       <c r="AI22" t="s">
         <v>44</v>
       </c>
       <c r="AJ22" s="2">
         <f>AJ20+AJ21</f>
-        <v>10271.759137996445</v>
+        <v>23834.856271998346</v>
       </c>
     </row>
     <row r="23" spans="2:36" x14ac:dyDescent="0.3">
@@ -3355,19 +3346,19 @@
         <v>19</v>
       </c>
       <c r="G23" s="8">
-        <f t="shared" ref="G23:J23" si="90">G12/G11</f>
+        <f t="shared" ref="G23:J23" si="91">G12/G11</f>
         <v>-1.6666666666666663E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-3.5353535353535318E-2</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-5.714285714285719E-2</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>4.5918367346938792E-2</v>
       </c>
       <c r="K23" s="8">
@@ -3375,31 +3366,31 @@
         <v>-6.9613644274277764E-4</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" ref="L23:N23" si="91">L12/L11</f>
+        <f t="shared" ref="L23:N23" si="92">L12/L11</f>
         <v>1.923076923076919E-2</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="N23" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>-1.4265335235378044E-2</v>
       </c>
       <c r="O23" s="8">
-        <f t="shared" ref="O23:R23" si="92">O12/O11</f>
+        <f t="shared" ref="O23:R23" si="93">O12/O11</f>
         <v>-6.9672131147541047E-2</v>
       </c>
       <c r="P23" s="8">
-        <f t="shared" si="92"/>
-        <v>0</v>
+        <f t="shared" si="93"/>
+        <v>-4.5045045045045027E-3</v>
       </c>
       <c r="Q23" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="R23" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="T23" s="8">
@@ -3411,51 +3402,51 @@
         <v>-4.362801377726748E-2</v>
       </c>
       <c r="V23" s="8">
-        <f t="shared" ref="V23:AG23" si="93">V12/V11</f>
+        <f t="shared" ref="V23:AG23" si="94">V12/V11</f>
         <v>1.6494845360824739E-3</v>
       </c>
       <c r="W23" s="8">
-        <f t="shared" si="93"/>
-        <v>-8.7271502671534811E-3</v>
+        <f t="shared" si="94"/>
+        <v>-6.0424525451673265E-3</v>
       </c>
       <c r="X23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="Y23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="Z23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="AA23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="AB23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="AC23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="AD23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="AE23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="AF23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="AG23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.15</v>
       </c>
       <c r="AI23" t="s">
@@ -3463,7 +3454,7 @@
       </c>
       <c r="AJ23" s="1">
         <f>AJ22/AG14</f>
-        <v>55.673491262853361</v>
+        <v>128.55909531822192</v>
       </c>
     </row>
     <row r="24" spans="2:36" x14ac:dyDescent="0.3">
@@ -3471,19 +3462,19 @@
         <v>40</v>
       </c>
       <c r="G24" s="8">
-        <f t="shared" ref="G24:J24" si="94">G13/G3</f>
+        <f t="shared" ref="G24:J24" si="95">G13/G3</f>
         <v>-0.37263286499694576</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-0.22404371584699473</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-3.5662650602409612E-2</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>7.4859887910328243E-2</v>
       </c>
       <c r="K24" s="8">
@@ -3491,32 +3482,32 @@
         <v>-2.3662551440329218</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" ref="L24:N24" si="95">L13/L3</f>
+        <f t="shared" ref="L24:N24" si="96">L13/L3</f>
         <v>-3.627311522048373E-2</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>8.5820895522388002E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.16623801730184695</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" ref="O24:R24" si="96">O13/O3</f>
+        <f t="shared" ref="O24:R24" si="97">O13/O3</f>
         <v>6.6513761467889856E-2</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" si="96"/>
-        <v>9.2201402854760195E-2</v>
+        <f t="shared" si="97"/>
+        <v>0.17854283426741402</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.11704707233065439</v>
+        <f t="shared" si="97"/>
+        <v>0.20959259259259272</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.15943067570727151</v>
+        <f t="shared" si="97"/>
+        <v>0.201935</v>
       </c>
       <c r="T24" s="8">
         <f>T13/T3</f>
@@ -3527,59 +3518,59 @@
         <v>-0.11305970149253737</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" ref="V24:AG24" si="97">V13/V3</f>
+        <f t="shared" ref="V24:AG24" si="98">V13/V3</f>
         <v>-0.3723756056294702</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.11235442111522788</v>
+        <f t="shared" si="98"/>
+        <v>0.17206742125984273</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.16608316414080093</v>
+        <f t="shared" si="98"/>
+        <v>0.26589063396372326</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.19934340352878502</v>
+        <f t="shared" si="98"/>
+        <v>0.33704860927495239</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.22615131188827772</v>
+        <f t="shared" si="98"/>
+        <v>0.37067108918624292</v>
       </c>
       <c r="AA24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.24161189562547311</v>
+        <f t="shared" si="98"/>
+        <v>0.39054593560901429</v>
       </c>
       <c r="AB24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.24967363131700099</v>
+        <f t="shared" si="98"/>
+        <v>0.39738675326632661</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.2541449028074384</v>
+        <f t="shared" si="98"/>
+        <v>0.4000125679398564</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.25512268084747708</v>
+        <f t="shared" si="98"/>
+        <v>0.40056933519993548</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.25609096589683572</v>
+        <f t="shared" si="98"/>
+        <v>0.40112069695263508</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.25704985012047243</v>
+        <f t="shared" si="98"/>
+        <v>0.40166670567860957</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.25799942478853993</v>
+        <f t="shared" si="98"/>
+        <v>0.40220741334899218</v>
       </c>
       <c r="AI24" t="s">
         <v>46</v>
       </c>
       <c r="AJ24" s="1">
         <f>Main!D3</f>
-        <v>96.02</v>
+        <v>246.5</v>
       </c>
     </row>
     <row r="25" spans="2:36" x14ac:dyDescent="0.3">
@@ -3588,7 +3579,7 @@
       </c>
       <c r="AJ25" s="9">
         <f>AJ23/AJ24-1</f>
-        <v>-0.4201885933883216</v>
+        <v>-0.47846208795853173</v>
       </c>
     </row>
     <row r="26" spans="2:36" x14ac:dyDescent="0.3">
@@ -3616,48 +3607,48 @@
         <v>-484.2000000000001</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" ref="W27:AG27" si="98">W13</f>
-        <v>196.49439999999973</v>
+        <f t="shared" ref="W27:AG27" si="99">W13</f>
+        <v>349.64100000000042</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="98"/>
-        <v>339.83764319999977</v>
+        <f t="shared" si="99"/>
+        <v>756.40567549999992</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="98"/>
-        <v>460.92067101599946</v>
+        <f t="shared" si="99"/>
+        <v>1246.4866487649999</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="98"/>
-        <v>580.42539640355994</v>
+        <f t="shared" si="99"/>
+        <v>1576.4552462029505</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" si="98"/>
-        <v>663.51292266195708</v>
+        <f t="shared" si="99"/>
+        <v>1793.8610903260976</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="98"/>
-        <v>719.93460594233522</v>
+        <f t="shared" si="99"/>
+        <v>1934.7993761268801</v>
       </c>
       <c r="AC27" s="7">
-        <f t="shared" si="98"/>
-        <v>762.14063082826704</v>
+        <f t="shared" si="99"/>
+        <v>2025.4873192243078</v>
       </c>
       <c r="AD27" s="7">
-        <f t="shared" si="98"/>
-        <v>788.0250185423904</v>
+        <f t="shared" si="99"/>
+        <v>2089.1557395035579</v>
       </c>
       <c r="AE27" s="7">
-        <f t="shared" si="98"/>
-        <v>814.74634126372302</v>
+        <f t="shared" si="99"/>
+        <v>2154.7922884052355</v>
       </c>
       <c r="AF27" s="7">
-        <f t="shared" si="98"/>
-        <v>842.33091510999668</v>
+        <f t="shared" si="99"/>
+        <v>2222.4571713082955</v>
       </c>
       <c r="AG27" s="7">
-        <f t="shared" si="98"/>
-        <v>870.80586984382603</v>
+        <f t="shared" si="99"/>
+        <v>2292.2124229834662</v>
       </c>
     </row>
     <row r="28" spans="2:36" x14ac:dyDescent="0.3">
@@ -3678,15 +3669,15 @@
         <v>18.72</v>
       </c>
       <c r="X28">
-        <f t="shared" ref="X28:Z28" si="99">W28*1.2</f>
+        <f t="shared" ref="X28:Z28" si="100">W28*1.2</f>
         <v>22.463999999999999</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>26.956799999999998</v>
       </c>
       <c r="Z28">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>32.348159999999993</v>
       </c>
       <c r="AA28">
@@ -3694,27 +3685,27 @@
         <v>33.965567999999998</v>
       </c>
       <c r="AB28">
-        <f t="shared" ref="AB28:AG28" si="100">AA28*1.05</f>
+        <f t="shared" ref="AB28:AG28" si="101">AA28*1.05</f>
         <v>35.663846399999997</v>
       </c>
       <c r="AC28">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>37.447038720000002</v>
       </c>
       <c r="AD28">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>39.319390656000003</v>
       </c>
       <c r="AE28">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>41.285360188800006</v>
       </c>
       <c r="AF28">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>43.349628198240005</v>
       </c>
       <c r="AG28">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>45.517109608152005</v>
       </c>
     </row>
@@ -3834,7 +3825,7 @@
         <v>224.44800000000001</v>
       </c>
       <c r="Y31">
-        <f t="shared" ref="Y31" si="101">X31*0.7</f>
+        <f t="shared" ref="Y31" si="102">X31*0.7</f>
         <v>157.11359999999999</v>
       </c>
       <c r="Z31">
@@ -3842,31 +3833,31 @@
         <v>149.25791999999998</v>
       </c>
       <c r="AA31">
-        <f t="shared" ref="AA31:AG31" si="102">Z31*0.95</f>
+        <f t="shared" ref="AA31:AG31" si="103">Z31*0.95</f>
         <v>141.79502399999998</v>
       </c>
       <c r="AB31">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>134.70527279999999</v>
       </c>
       <c r="AC31">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>127.97000915999999</v>
       </c>
       <c r="AD31">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>121.57150870199999</v>
       </c>
       <c r="AE31">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>115.49293326689998</v>
       </c>
       <c r="AF31">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>109.71828660355497</v>
       </c>
       <c r="AG31">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>104.23237227337722</v>
       </c>
     </row>
@@ -4169,48 +4160,48 @@
         <v>221.99999999999983</v>
       </c>
       <c r="W38" s="7">
-        <f t="shared" ref="W38" si="103">W27+SUM(W28:W37)</f>
-        <v>545.85439999999971</v>
+        <f t="shared" ref="W38" si="104">W27+SUM(W28:W37)</f>
+        <v>699.00100000000043</v>
       </c>
       <c r="X38" s="7">
-        <f t="shared" ref="X38" si="104">X27+SUM(X28:X37)</f>
-        <v>596.74964319999981</v>
+        <f t="shared" ref="X38" si="105">X27+SUM(X28:X37)</f>
+        <v>1013.3176755</v>
       </c>
       <c r="Y38" s="7">
-        <f t="shared" ref="Y38" si="105">Y27+SUM(Y28:Y37)</f>
-        <v>654.99107101599952</v>
+        <f t="shared" ref="Y38" si="106">Y27+SUM(Y28:Y37)</f>
+        <v>1440.557048765</v>
       </c>
       <c r="Z38" s="7">
-        <f t="shared" ref="Z38" si="106">Z27+SUM(Z28:Z37)</f>
-        <v>772.03147640355996</v>
+        <f t="shared" ref="Z38" si="107">Z27+SUM(Z28:Z37)</f>
+        <v>1768.0613262029506</v>
       </c>
       <c r="AA38" s="7">
-        <f t="shared" ref="AA38" si="107">AA27+SUM(AA28:AA37)</f>
-        <v>849.27351466195705</v>
+        <f t="shared" ref="AA38" si="108">AA27+SUM(AA28:AA37)</f>
+        <v>1979.6216823260975</v>
       </c>
       <c r="AB38" s="7">
-        <f t="shared" ref="AB38" si="108">AB27+SUM(AB28:AB37)</f>
-        <v>900.30372514233522</v>
+        <f t="shared" ref="AB38" si="109">AB27+SUM(AB28:AB37)</f>
+        <v>2115.16849532688</v>
       </c>
       <c r="AC38" s="7">
-        <f t="shared" ref="AC38" si="109">AC27+SUM(AC28:AC37)</f>
-        <v>937.55767870826708</v>
+        <f t="shared" ref="AC38" si="110">AC27+SUM(AC28:AC37)</f>
+        <v>2200.9043671043078</v>
       </c>
       <c r="AD38" s="7">
-        <f t="shared" ref="AD38" si="110">AD27+SUM(AD28:AD37)</f>
-        <v>958.91591790039035</v>
+        <f t="shared" ref="AD38" si="111">AD27+SUM(AD28:AD37)</f>
+        <v>2260.0466388615578</v>
       </c>
       <c r="AE38" s="7">
-        <f t="shared" ref="AE38" si="111">AE27+SUM(AE28:AE37)</f>
-        <v>981.52463471942303</v>
+        <f t="shared" ref="AE38" si="112">AE27+SUM(AE28:AE37)</f>
+        <v>2321.5705818609354</v>
       </c>
       <c r="AF38" s="7">
-        <f t="shared" ref="AF38" si="112">AF27+SUM(AF28:AF37)</f>
-        <v>1005.3988299117916</v>
+        <f t="shared" ref="AF38" si="113">AF27+SUM(AF28:AF37)</f>
+        <v>2385.5250861100903</v>
       </c>
       <c r="AG38" s="7">
-        <f t="shared" ref="AG38" si="113">AG27+SUM(AG28:AG37)</f>
-        <v>1030.5553517253552</v>
+        <f t="shared" ref="AG38" si="114">AG27+SUM(AG28:AG37)</f>
+        <v>2451.9619048649956</v>
       </c>
     </row>
     <row r="39" spans="2:144" x14ac:dyDescent="0.3">
@@ -4277,528 +4268,528 @@
         <v>215.79999999999984</v>
       </c>
       <c r="W40" s="7">
-        <f t="shared" ref="W40" si="114">W38-W39</f>
-        <v>539.65439999999967</v>
+        <f t="shared" ref="W40" si="115">W38-W39</f>
+        <v>692.80100000000039</v>
       </c>
       <c r="X40" s="7">
-        <f t="shared" ref="X40" si="115">X38-X39</f>
-        <v>590.54964319999976</v>
+        <f t="shared" ref="X40" si="116">X38-X39</f>
+        <v>1007.1176754999999</v>
       </c>
       <c r="Y40" s="7">
-        <f t="shared" ref="Y40" si="116">Y38-Y39</f>
-        <v>648.79107101599948</v>
+        <f t="shared" ref="Y40" si="117">Y38-Y39</f>
+        <v>1434.3570487649999</v>
       </c>
       <c r="Z40" s="7">
-        <f t="shared" ref="Z40" si="117">Z38-Z39</f>
-        <v>765.83147640355992</v>
+        <f t="shared" ref="Z40" si="118">Z38-Z39</f>
+        <v>1761.8613262029505</v>
       </c>
       <c r="AA40" s="7">
-        <f t="shared" ref="AA40" si="118">AA38-AA39</f>
-        <v>843.07351466195701</v>
+        <f t="shared" ref="AA40" si="119">AA38-AA39</f>
+        <v>1973.4216823260974</v>
       </c>
       <c r="AB40" s="7">
-        <f t="shared" ref="AB40" si="119">AB38-AB39</f>
-        <v>894.10372514233518</v>
+        <f t="shared" ref="AB40" si="120">AB38-AB39</f>
+        <v>2108.9684953268802</v>
       </c>
       <c r="AC40" s="7">
-        <f t="shared" ref="AC40" si="120">AC38-AC39</f>
-        <v>931.35767870826703</v>
+        <f t="shared" ref="AC40" si="121">AC38-AC39</f>
+        <v>2194.7043671043079</v>
       </c>
       <c r="AD40" s="7">
-        <f t="shared" ref="AD40" si="121">AD38-AD39</f>
-        <v>952.71591790039031</v>
+        <f t="shared" ref="AD40" si="122">AD38-AD39</f>
+        <v>2253.8466388615579</v>
       </c>
       <c r="AE40" s="7">
-        <f t="shared" ref="AE40" si="122">AE38-AE39</f>
-        <v>975.32463471942299</v>
+        <f t="shared" ref="AE40" si="123">AE38-AE39</f>
+        <v>2315.3705818609355</v>
       </c>
       <c r="AF40" s="7">
-        <f t="shared" ref="AF40" si="123">AF38-AF39</f>
-        <v>999.19882991179156</v>
+        <f t="shared" ref="AF40" si="124">AF38-AF39</f>
+        <v>2379.3250861100905</v>
       </c>
       <c r="AG40" s="7">
-        <f t="shared" ref="AG40" si="124">AG38-AG39</f>
-        <v>1024.3553517253551</v>
+        <f t="shared" ref="AG40" si="125">AG38-AG39</f>
+        <v>2445.7619048649958</v>
       </c>
       <c r="AH40" s="6">
         <f>AG40*(1+$AJ$18)</f>
-        <v>1014.1117982081016</v>
+        <v>2421.3042858163458</v>
       </c>
       <c r="AI40" s="6">
-        <f t="shared" ref="AI40:CT40" si="125">AH40*(1+$AJ$18)</f>
-        <v>1003.9706802260206</v>
+        <f t="shared" ref="AI40:CT40" si="126">AH40*(1+$AJ$18)</f>
+        <v>2397.0912429581822</v>
       </c>
       <c r="AJ40" s="6">
-        <f t="shared" si="125"/>
-        <v>993.93097342376041</v>
+        <f t="shared" si="126"/>
+        <v>2373.1203305286003</v>
       </c>
       <c r="AK40" s="6">
-        <f t="shared" si="125"/>
-        <v>983.99166368952274</v>
+        <f t="shared" si="126"/>
+        <v>2349.3891272233145</v>
       </c>
       <c r="AL40" s="6">
-        <f t="shared" si="125"/>
-        <v>974.15174705262746</v>
+        <f t="shared" si="126"/>
+        <v>2325.8952359510813</v>
       </c>
       <c r="AM40" s="6">
-        <f t="shared" si="125"/>
-        <v>964.41022958210112</v>
+        <f t="shared" si="126"/>
+        <v>2302.6362835915706</v>
       </c>
       <c r="AN40" s="6">
-        <f t="shared" si="125"/>
-        <v>954.76612728628015</v>
+        <f t="shared" si="126"/>
+        <v>2279.6099207556549</v>
       </c>
       <c r="AO40" s="6">
-        <f t="shared" si="125"/>
-        <v>945.21846601341736</v>
+        <f t="shared" si="126"/>
+        <v>2256.8138215480985</v>
       </c>
       <c r="AP40" s="6">
-        <f t="shared" si="125"/>
-        <v>935.76628135328315</v>
+        <f t="shared" si="126"/>
+        <v>2234.2456833326173</v>
       </c>
       <c r="AQ40" s="6">
-        <f t="shared" si="125"/>
-        <v>926.40861853975036</v>
+        <f t="shared" si="126"/>
+        <v>2211.9032264992911</v>
       </c>
       <c r="AR40" s="6">
-        <f t="shared" si="125"/>
-        <v>917.1445323543528</v>
+        <f t="shared" si="126"/>
+        <v>2189.7841942342984</v>
       </c>
       <c r="AS40" s="6">
-        <f t="shared" si="125"/>
-        <v>907.97308703080932</v>
+        <f t="shared" si="126"/>
+        <v>2167.8863522919555</v>
       </c>
       <c r="AT40" s="6">
-        <f t="shared" si="125"/>
-        <v>898.89335616050118</v>
+        <f t="shared" si="126"/>
+        <v>2146.207488769036</v>
       </c>
       <c r="AU40" s="6">
-        <f t="shared" si="125"/>
-        <v>889.90442259889619</v>
+        <f t="shared" si="126"/>
+        <v>2124.7454138813455</v>
       </c>
       <c r="AV40" s="6">
-        <f t="shared" si="125"/>
-        <v>881.00537837290722</v>
+        <f t="shared" si="126"/>
+        <v>2103.4979597425322</v>
       </c>
       <c r="AW40" s="6">
-        <f t="shared" si="125"/>
-        <v>872.19532458917809</v>
+        <f t="shared" si="126"/>
+        <v>2082.4629801451069</v>
       </c>
       <c r="AX40" s="6">
-        <f t="shared" si="125"/>
-        <v>863.47337134328632</v>
+        <f t="shared" si="126"/>
+        <v>2061.6383503436559</v>
       </c>
       <c r="AY40" s="6">
-        <f t="shared" si="125"/>
-        <v>854.83863762985345</v>
+        <f t="shared" si="126"/>
+        <v>2041.0219668402194</v>
       </c>
       <c r="AZ40" s="6">
-        <f t="shared" si="125"/>
-        <v>846.29025125355486</v>
+        <f t="shared" si="126"/>
+        <v>2020.6117471718171</v>
       </c>
       <c r="BA40" s="6">
-        <f t="shared" si="125"/>
-        <v>837.82734874101925</v>
+        <f t="shared" si="126"/>
+        <v>2000.4056297000989</v>
       </c>
       <c r="BB40" s="6">
-        <f t="shared" si="125"/>
-        <v>829.44907525360907</v>
+        <f t="shared" si="126"/>
+        <v>1980.4015734030979</v>
       </c>
       <c r="BC40" s="6">
-        <f t="shared" si="125"/>
-        <v>821.15458450107292</v>
+        <f t="shared" si="126"/>
+        <v>1960.5975576690669</v>
       </c>
       <c r="BD40" s="6">
-        <f t="shared" si="125"/>
-        <v>812.94303865606219</v>
+        <f t="shared" si="126"/>
+        <v>1940.9915820923761</v>
       </c>
       <c r="BE40" s="6">
-        <f t="shared" si="125"/>
-        <v>804.81360826950151</v>
+        <f t="shared" si="126"/>
+        <v>1921.5816662714524</v>
       </c>
       <c r="BF40" s="6">
-        <f t="shared" si="125"/>
-        <v>796.76547218680651</v>
+        <f t="shared" si="126"/>
+        <v>1902.3658496087378</v>
       </c>
       <c r="BG40" s="6">
-        <f t="shared" si="125"/>
-        <v>788.79781746493848</v>
+        <f t="shared" si="126"/>
+        <v>1883.3421911126504</v>
       </c>
       <c r="BH40" s="6">
-        <f t="shared" si="125"/>
-        <v>780.90983929028903</v>
+        <f t="shared" si="126"/>
+        <v>1864.5087692015238</v>
       </c>
       <c r="BI40" s="6">
-        <f t="shared" si="125"/>
-        <v>773.10074089738612</v>
+        <f t="shared" si="126"/>
+        <v>1845.8636815095085</v>
       </c>
       <c r="BJ40" s="6">
-        <f t="shared" si="125"/>
-        <v>765.36973348841229</v>
+        <f t="shared" si="126"/>
+        <v>1827.4050446944134</v>
       </c>
       <c r="BK40" s="6">
-        <f t="shared" si="125"/>
-        <v>757.71603615352819</v>
+        <f t="shared" si="126"/>
+        <v>1809.1309942474693</v>
       </c>
       <c r="BL40" s="6">
-        <f t="shared" si="125"/>
-        <v>750.13887579199286</v>
+        <f t="shared" si="126"/>
+        <v>1791.0396843049946</v>
       </c>
       <c r="BM40" s="6">
-        <f t="shared" si="125"/>
-        <v>742.63748703407293</v>
+        <f t="shared" si="126"/>
+        <v>1773.1292874619446</v>
       </c>
       <c r="BN40" s="6">
-        <f t="shared" si="125"/>
-        <v>735.2111121637322</v>
+        <f t="shared" si="126"/>
+        <v>1755.3979945873252</v>
       </c>
       <c r="BO40" s="6">
-        <f t="shared" si="125"/>
-        <v>727.85900104209486</v>
+        <f t="shared" si="126"/>
+        <v>1737.8440146414518</v>
       </c>
       <c r="BP40" s="6">
-        <f t="shared" si="125"/>
-        <v>720.58041103167386</v>
+        <f t="shared" si="126"/>
+        <v>1720.4655744950373</v>
       </c>
       <c r="BQ40" s="6">
-        <f t="shared" si="125"/>
-        <v>713.3746069213571</v>
+        <f t="shared" si="126"/>
+        <v>1703.2609187500871</v>
       </c>
       <c r="BR40" s="6">
-        <f t="shared" si="125"/>
-        <v>706.24086085214356</v>
+        <f t="shared" si="126"/>
+        <v>1686.2283095625862</v>
       </c>
       <c r="BS40" s="6">
-        <f t="shared" si="125"/>
-        <v>699.17845224362213</v>
+        <f t="shared" si="126"/>
+        <v>1669.3660264669604</v>
       </c>
       <c r="BT40" s="6">
-        <f t="shared" si="125"/>
-        <v>692.18666772118593</v>
+        <f t="shared" si="126"/>
+        <v>1652.6723662022907</v>
       </c>
       <c r="BU40" s="6">
-        <f t="shared" si="125"/>
-        <v>685.2648010439741</v>
+        <f t="shared" si="126"/>
+        <v>1636.1456425402678</v>
       </c>
       <c r="BV40" s="6">
-        <f t="shared" si="125"/>
-        <v>678.41215303353431</v>
+        <f t="shared" si="126"/>
+        <v>1619.7841861148652</v>
       </c>
       <c r="BW40" s="6">
-        <f t="shared" si="125"/>
-        <v>671.62803150319894</v>
+        <f t="shared" si="126"/>
+        <v>1603.5863442537166</v>
       </c>
       <c r="BX40" s="6">
-        <f t="shared" si="125"/>
-        <v>664.91175118816693</v>
+        <f t="shared" si="126"/>
+        <v>1587.5504808111793</v>
       </c>
       <c r="BY40" s="6">
-        <f t="shared" si="125"/>
-        <v>658.2626336762853</v>
+        <f t="shared" si="126"/>
+        <v>1571.6749760030675</v>
       </c>
       <c r="BZ40" s="6">
-        <f t="shared" si="125"/>
-        <v>651.68000733952249</v>
+        <f t="shared" si="126"/>
+        <v>1555.9582262430367</v>
       </c>
       <c r="CA40" s="6">
-        <f t="shared" si="125"/>
-        <v>645.1632072661273</v>
+        <f t="shared" si="126"/>
+        <v>1540.3986439806063</v>
       </c>
       <c r="CB40" s="6">
-        <f t="shared" si="125"/>
-        <v>638.71157519346605</v>
+        <f t="shared" si="126"/>
+        <v>1524.9946575408003</v>
       </c>
       <c r="CC40" s="6">
-        <f t="shared" si="125"/>
-        <v>632.32445944153142</v>
+        <f t="shared" si="126"/>
+        <v>1509.7447109653922</v>
       </c>
       <c r="CD40" s="6">
-        <f t="shared" si="125"/>
-        <v>626.0012148471161</v>
+        <f t="shared" si="126"/>
+        <v>1494.6472638557382</v>
       </c>
       <c r="CE40" s="6">
-        <f t="shared" si="125"/>
-        <v>619.74120269864488</v>
+        <f t="shared" si="126"/>
+        <v>1479.7007912171807</v>
       </c>
       <c r="CF40" s="6">
-        <f t="shared" si="125"/>
-        <v>613.54379067165848</v>
+        <f t="shared" si="126"/>
+        <v>1464.9037833050088</v>
       </c>
       <c r="CG40" s="6">
-        <f t="shared" si="125"/>
-        <v>607.40835276494192</v>
+        <f t="shared" si="126"/>
+        <v>1450.2547454719588</v>
       </c>
       <c r="CH40" s="6">
-        <f t="shared" si="125"/>
-        <v>601.33426923729246</v>
+        <f t="shared" si="126"/>
+        <v>1435.7521980172392</v>
       </c>
       <c r="CI40" s="6">
-        <f t="shared" si="125"/>
-        <v>595.32092654491953</v>
+        <f t="shared" si="126"/>
+        <v>1421.3946760370668</v>
       </c>
       <c r="CJ40" s="6">
-        <f t="shared" si="125"/>
-        <v>589.3677172794703</v>
+        <f t="shared" si="126"/>
+        <v>1407.1807292766962</v>
       </c>
       <c r="CK40" s="6">
-        <f t="shared" si="125"/>
-        <v>583.4740401066756</v>
+        <f t="shared" si="126"/>
+        <v>1393.1089219839291</v>
       </c>
       <c r="CL40" s="6">
-        <f t="shared" si="125"/>
-        <v>577.63929970560889</v>
+        <f t="shared" si="126"/>
+        <v>1379.1778327640898</v>
       </c>
       <c r="CM40" s="6">
-        <f t="shared" si="125"/>
-        <v>571.86290670855283</v>
+        <f t="shared" si="126"/>
+        <v>1365.3860544364488</v>
       </c>
       <c r="CN40" s="6">
-        <f t="shared" si="125"/>
-        <v>566.14427764146728</v>
+        <f t="shared" si="126"/>
+        <v>1351.7321938920843</v>
       </c>
       <c r="CO40" s="6">
-        <f t="shared" si="125"/>
-        <v>560.48283486505261</v>
+        <f t="shared" si="126"/>
+        <v>1338.2148719531635</v>
       </c>
       <c r="CP40" s="6">
-        <f t="shared" si="125"/>
-        <v>554.87800651640202</v>
+        <f t="shared" si="126"/>
+        <v>1324.8327232336319</v>
       </c>
       <c r="CQ40" s="6">
-        <f t="shared" si="125"/>
-        <v>549.32922645123801</v>
+        <f t="shared" si="126"/>
+        <v>1311.5843960012955</v>
       </c>
       <c r="CR40" s="6">
-        <f t="shared" si="125"/>
-        <v>543.83593418672558</v>
+        <f t="shared" si="126"/>
+        <v>1298.4685520412825</v>
       </c>
       <c r="CS40" s="6">
-        <f t="shared" si="125"/>
-        <v>538.39757484485835</v>
+        <f t="shared" si="126"/>
+        <v>1285.4838665208697</v>
       </c>
       <c r="CT40" s="6">
-        <f t="shared" si="125"/>
-        <v>533.01359909640973</v>
+        <f t="shared" si="126"/>
+        <v>1272.629027855661</v>
       </c>
       <c r="CU40" s="6">
-        <f t="shared" ref="CU40:EN40" si="126">CT40*(1+$AJ$18)</f>
-        <v>527.68346310544564</v>
+        <f t="shared" ref="CU40:EN40" si="127">CT40*(1+$AJ$18)</f>
+        <v>1259.9027375771043</v>
       </c>
       <c r="CV40" s="6">
-        <f t="shared" si="126"/>
-        <v>522.40662847439114</v>
+        <f t="shared" si="127"/>
+        <v>1247.3037102013332</v>
       </c>
       <c r="CW40" s="6">
-        <f t="shared" si="126"/>
-        <v>517.18256218964723</v>
+        <f t="shared" si="127"/>
+        <v>1234.8306730993197</v>
       </c>
       <c r="CX40" s="6">
-        <f t="shared" si="126"/>
-        <v>512.01073656775077</v>
+        <f t="shared" si="127"/>
+        <v>1222.4823663683264</v>
       </c>
       <c r="CY40" s="6">
-        <f t="shared" si="126"/>
-        <v>506.89062920207323</v>
+        <f t="shared" si="127"/>
+        <v>1210.2575427046431</v>
       </c>
       <c r="CZ40" s="6">
-        <f t="shared" si="126"/>
-        <v>501.82172291005247</v>
+        <f t="shared" si="127"/>
+        <v>1198.1549672775966</v>
       </c>
       <c r="DA40" s="6">
-        <f t="shared" si="126"/>
-        <v>496.80350568095196</v>
+        <f t="shared" si="127"/>
+        <v>1186.1734176048205</v>
       </c>
       <c r="DB40" s="6">
-        <f t="shared" si="126"/>
-        <v>491.83547062414243</v>
+        <f t="shared" si="127"/>
+        <v>1174.3116834287723</v>
       </c>
       <c r="DC40" s="6">
-        <f t="shared" si="126"/>
-        <v>486.91711591790101</v>
+        <f t="shared" si="127"/>
+        <v>1162.5685665944845</v>
       </c>
       <c r="DD40" s="6">
-        <f t="shared" si="126"/>
-        <v>482.047944758722</v>
+        <f t="shared" si="127"/>
+        <v>1150.9428809285396</v>
       </c>
       <c r="DE40" s="6">
-        <f t="shared" si="126"/>
-        <v>477.22746531113478</v>
+        <f t="shared" si="127"/>
+        <v>1139.4334521192541</v>
       </c>
       <c r="DF40" s="6">
-        <f t="shared" si="126"/>
-        <v>472.45519065802341</v>
+        <f t="shared" si="127"/>
+        <v>1128.0391175980615</v>
       </c>
       <c r="DG40" s="6">
-        <f t="shared" si="126"/>
-        <v>467.73063875144317</v>
+        <f t="shared" si="127"/>
+        <v>1116.7587264220808</v>
       </c>
       <c r="DH40" s="6">
-        <f t="shared" si="126"/>
-        <v>463.05333236392875</v>
+        <f t="shared" si="127"/>
+        <v>1105.59113915786</v>
       </c>
       <c r="DI40" s="6">
-        <f t="shared" si="126"/>
-        <v>458.42279904028948</v>
+        <f t="shared" si="127"/>
+        <v>1094.5352277662814</v>
       </c>
       <c r="DJ40" s="6">
-        <f t="shared" si="126"/>
-        <v>453.83857104988658</v>
+        <f t="shared" si="127"/>
+        <v>1083.5898754886186</v>
       </c>
       <c r="DK40" s="6">
-        <f t="shared" si="126"/>
-        <v>449.30018533938772</v>
+        <f t="shared" si="127"/>
+        <v>1072.7539767337325</v>
       </c>
       <c r="DL40" s="6">
-        <f t="shared" si="126"/>
-        <v>444.80718348599385</v>
+        <f t="shared" si="127"/>
+        <v>1062.0264369663953</v>
       </c>
       <c r="DM40" s="6">
-        <f t="shared" si="126"/>
-        <v>440.3591116511339</v>
+        <f t="shared" si="127"/>
+        <v>1051.4061725967313</v>
       </c>
       <c r="DN40" s="6">
-        <f t="shared" si="126"/>
-        <v>435.95552053462256</v>
+        <f t="shared" si="127"/>
+        <v>1040.8921108707639</v>
       </c>
       <c r="DO40" s="6">
-        <f t="shared" si="126"/>
-        <v>431.59596532927634</v>
+        <f t="shared" si="127"/>
+        <v>1030.4831897620563</v>
       </c>
       <c r="DP40" s="6">
-        <f t="shared" si="126"/>
-        <v>427.28000567598355</v>
+        <f t="shared" si="127"/>
+        <v>1020.1783578644357</v>
       </c>
       <c r="DQ40" s="6">
-        <f t="shared" si="126"/>
-        <v>423.00720561922373</v>
+        <f t="shared" si="127"/>
+        <v>1009.9765742857913</v>
       </c>
       <c r="DR40" s="6">
-        <f t="shared" si="126"/>
-        <v>418.7771335630315</v>
+        <f t="shared" si="127"/>
+        <v>999.87680854293342</v>
       </c>
       <c r="DS40" s="6">
-        <f t="shared" si="126"/>
-        <v>414.58936222740118</v>
+        <f t="shared" si="127"/>
+        <v>989.87804045750408</v>
       </c>
       <c r="DT40" s="6">
-        <f t="shared" si="126"/>
-        <v>410.44346860512718</v>
+        <f t="shared" si="127"/>
+        <v>979.97926005292902</v>
       </c>
       <c r="DU40" s="6">
-        <f t="shared" si="126"/>
-        <v>406.33903391907592</v>
+        <f t="shared" si="127"/>
+        <v>970.17946745239976</v>
       </c>
       <c r="DV40" s="6">
-        <f t="shared" si="126"/>
-        <v>402.27564357988513</v>
+        <f t="shared" si="127"/>
+        <v>960.4776727778758</v>
       </c>
       <c r="DW40" s="6">
-        <f t="shared" si="126"/>
-        <v>398.25288714408629</v>
+        <f t="shared" si="127"/>
+        <v>950.87289605009698</v>
       </c>
       <c r="DX40" s="6">
-        <f t="shared" si="126"/>
-        <v>394.27035827264541</v>
+        <f t="shared" si="127"/>
+        <v>941.36416708959598</v>
       </c>
       <c r="DY40" s="6">
-        <f t="shared" si="126"/>
-        <v>390.32765468991897</v>
+        <f t="shared" si="127"/>
+        <v>931.95052541870007</v>
       </c>
       <c r="DZ40" s="6">
-        <f t="shared" si="126"/>
-        <v>386.42437814301979</v>
+        <f t="shared" si="127"/>
+        <v>922.63102016451307</v>
       </c>
       <c r="EA40" s="6">
-        <f t="shared" si="126"/>
-        <v>382.56013436158958</v>
+        <f t="shared" si="127"/>
+        <v>913.40470996286797</v>
       </c>
       <c r="EB40" s="6">
-        <f t="shared" si="126"/>
-        <v>378.73453301797366</v>
+        <f t="shared" si="127"/>
+        <v>904.27066286323929</v>
       </c>
       <c r="EC40" s="6">
-        <f t="shared" si="126"/>
-        <v>374.94718768779393</v>
+        <f t="shared" si="127"/>
+        <v>895.22795623460695</v>
       </c>
       <c r="ED40" s="6">
-        <f t="shared" si="126"/>
-        <v>371.19771581091601</v>
+        <f t="shared" si="127"/>
+        <v>886.27567667226083</v>
       </c>
       <c r="EE40" s="6">
-        <f t="shared" si="126"/>
-        <v>367.48573865280684</v>
+        <f t="shared" si="127"/>
+        <v>877.41291990553816</v>
       </c>
       <c r="EF40" s="6">
-        <f t="shared" si="126"/>
-        <v>363.81088126627878</v>
+        <f t="shared" si="127"/>
+        <v>868.63879070648272</v>
       </c>
       <c r="EG40" s="6">
-        <f t="shared" si="126"/>
-        <v>360.17277245361601</v>
+        <f t="shared" si="127"/>
+        <v>859.95240279941788</v>
       </c>
       <c r="EH40" s="6">
-        <f t="shared" si="126"/>
-        <v>356.57104472907986</v>
+        <f t="shared" si="127"/>
+        <v>851.35287877142366</v>
       </c>
       <c r="EI40" s="6">
-        <f t="shared" si="126"/>
-        <v>353.00533428178903</v>
+        <f t="shared" si="127"/>
+        <v>842.83934998370944</v>
       </c>
       <c r="EJ40" s="6">
-        <f t="shared" si="126"/>
-        <v>349.47528093897114</v>
+        <f t="shared" si="127"/>
+        <v>834.41095648387238</v>
       </c>
       <c r="EK40" s="6">
-        <f t="shared" si="126"/>
-        <v>345.98052812958144</v>
+        <f t="shared" si="127"/>
+        <v>826.06684691903365</v>
       </c>
       <c r="EL40" s="6">
-        <f t="shared" si="126"/>
-        <v>342.52072284828563</v>
+        <f t="shared" si="127"/>
+        <v>817.80617844984329</v>
       </c>
       <c r="EM40" s="6">
-        <f t="shared" si="126"/>
-        <v>339.09551561980277</v>
+        <f t="shared" si="127"/>
+        <v>809.62811666534481</v>
       </c>
       <c r="EN40" s="6">
-        <f t="shared" si="126"/>
-        <v>335.70456046360476</v>
+        <f t="shared" si="127"/>
+        <v>801.53183549869129</v>
       </c>
     </row>
     <row r="43" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ43" s="10">
         <f>NPV(AJ19,W40:EN40)</f>
-        <v>10501.661284077858</v>
+        <v>23955.897369809136</v>
       </c>
     </row>
     <row r="44" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ44" s="2">
         <f>Main!D8</f>
-        <v>1951.1000000000001</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="45" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ45" s="10">
         <f>AJ43+AJ44</f>
-        <v>12452.761284077858</v>
+        <v>26015.897369809136</v>
       </c>
     </row>
     <row r="46" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ46" s="1">
         <f>AJ45/AG14</f>
-        <v>67.49464110611305</v>
+        <v>140.32307103456924</v>
       </c>
     </row>
     <row r="47" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ47" s="1">
         <f>Main!D3</f>
-        <v>96.02</v>
+        <v>246.5</v>
       </c>
     </row>
     <row r="48" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ48" s="9">
         <f>AJ46/AJ47-1</f>
-        <v>-0.29707726404797907</v>
+        <v>-0.43073804854130127</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RDDT.xlsx
+++ b/Financial Analysis/RDDT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54644B2E-C1E2-4EDE-ACD2-851B97493132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5B7C95-5989-4BC9-8222-9D5B588859E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{36256194-E29F-4FBF-A799-FCE3EDFD57DF}"/>
   </bookViews>
@@ -753,14 +753,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>246.5</v>
+        <v>203.63</v>
       </c>
       <c r="E3" s="11">
-        <v>45887</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="11">
         <v>45965</v>
@@ -784,7 +784,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>45701.1</v>
+        <v>37753.002</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -825,7 +825,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>43641.1</v>
+        <v>35693.002</v>
       </c>
     </row>
   </sheetData>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="AJ24" s="1">
         <f>Main!D3</f>
-        <v>246.5</v>
+        <v>203.63</v>
       </c>
     </row>
     <row r="25" spans="2:36" x14ac:dyDescent="0.3">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AJ25" s="9">
         <f>AJ23/AJ24-1</f>
-        <v>-0.47846208795853173</v>
+        <v>-0.36866328478995269</v>
       </c>
     </row>
     <row r="26" spans="2:36" x14ac:dyDescent="0.3">
@@ -4783,13 +4783,13 @@
     <row r="47" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ47" s="1">
         <f>Main!D3</f>
-        <v>246.5</v>
+        <v>203.63</v>
       </c>
     </row>
     <row r="48" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ48" s="9">
         <f>AJ46/AJ47-1</f>
-        <v>-0.43073804854130127</v>
+        <v>-0.31089195582885998</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RDDT.xlsx
+++ b/Financial Analysis/RDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5B7C95-5989-4BC9-8222-9D5B588859E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CE598A-7AC2-4041-9AEF-A394DF77AC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{36256194-E29F-4FBF-A799-FCE3EDFD57DF}"/>
   </bookViews>
@@ -381,13 +381,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -405,7 +405,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10233660" y="7620"/>
+          <a:off x="10843260" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -753,17 +753,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>203.63</v>
+        <v>218.54</v>
       </c>
       <c r="E3" s="11">
-        <v>45937</v>
+        <v>45961</v>
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45961</v>
       </c>
       <c r="G3" s="11">
-        <v>45965</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -771,8 +771,8 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <f>185.4</f>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>62</v>
@@ -784,7 +784,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>37753.002</v>
+        <v>41085.519999999997</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -825,7 +825,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>35693.002</v>
+        <v>39025.519999999997</v>
       </c>
     </row>
   </sheetData>
@@ -971,10 +971,11 @@
         <v>499.6</v>
       </c>
       <c r="Q3" s="7">
-        <v>540</v>
+        <f>584.9</f>
+        <v>584.9</v>
       </c>
       <c r="R3" s="7">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="T3" s="7">
         <v>666.7</v>
@@ -988,47 +989,47 @@
       </c>
       <c r="W3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>2032</v>
+        <v>2136.9</v>
       </c>
       <c r="X3" s="7">
         <f>W3*1.4</f>
-        <v>2844.7999999999997</v>
+        <v>2991.66</v>
       </c>
       <c r="Y3" s="7">
         <f>X3*1.3</f>
-        <v>3698.24</v>
+        <v>3889.1579999999999</v>
       </c>
       <c r="Z3" s="7">
         <f>Y3*1.15</f>
-        <v>4252.9759999999997</v>
+        <v>4472.5316999999995</v>
       </c>
       <c r="AA3" s="7">
         <f>Z3*1.08</f>
-        <v>4593.2140799999997</v>
+        <v>4830.3342359999997</v>
       </c>
       <c r="AB3" s="7">
         <f>AA3*1.06</f>
-        <v>4868.8069248000002</v>
+        <v>5120.1542901599996</v>
       </c>
       <c r="AC3" s="7">
-        <f>AB3*1.04</f>
-        <v>5063.5592017920007</v>
+        <f>AB3*1.05</f>
+        <v>5376.162004668</v>
       </c>
       <c r="AD3" s="7">
-        <f>AC3*1.03</f>
-        <v>5215.4659778457608</v>
+        <f t="shared" ref="AD3:AG3" si="0">AC3*1.05</f>
+        <v>5644.9701049014002</v>
       </c>
       <c r="AE3" s="7">
-        <f t="shared" ref="AE3:AG3" si="0">AD3*1.03</f>
-        <v>5371.9299571811334</v>
+        <f t="shared" si="0"/>
+        <v>5927.2186101464704</v>
       </c>
       <c r="AF3" s="7">
         <f t="shared" si="0"/>
-        <v>5533.0878558965678</v>
+        <v>6223.5795406537945</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" si="0"/>
-        <v>5699.0804915734652</v>
+        <v>6534.758517686485</v>
       </c>
     </row>
     <row r="4" spans="1:143" x14ac:dyDescent="0.3">
@@ -1066,12 +1067,11 @@
         <v>45.9</v>
       </c>
       <c r="Q4" s="2">
-        <f t="shared" ref="Q4:R4" si="1">Q3-Q5</f>
-        <v>48.599999999999966</v>
+        <v>52.5</v>
       </c>
       <c r="R4" s="2">
-        <f t="shared" si="1"/>
-        <v>48</v>
+        <f t="shared" ref="Q4:R4" si="1">R3-R5</f>
+        <v>52.799999999999955</v>
       </c>
       <c r="T4" s="2">
         <v>104.8</v>
@@ -1085,15 +1085,15 @@
       </c>
       <c r="W4" s="2">
         <f>SUM(O4:R4)</f>
-        <v>179.59999999999997</v>
+        <v>188.29999999999995</v>
       </c>
       <c r="X4" s="2">
         <f>SUM(M4:T4)</f>
-        <v>350.79999999999995</v>
+        <v>359.49999999999994</v>
       </c>
       <c r="Y4" s="2">
         <f>SUM(N4:U4)</f>
-        <v>427.2</v>
+        <v>435.9</v>
       </c>
       <c r="Z4" s="2">
         <f t="shared" ref="Z4:AG4" si="2">SUM(S4:V4)</f>
@@ -1101,31 +1101,31 @@
       </c>
       <c r="AA4" s="2">
         <f t="shared" si="2"/>
-        <v>518.9</v>
+        <v>527.59999999999991</v>
       </c>
       <c r="AB4" s="2">
         <f t="shared" si="2"/>
-        <v>764.89999999999986</v>
+        <v>782.3</v>
       </c>
       <c r="AC4" s="2">
         <f t="shared" si="2"/>
-        <v>1081.0999999999999</v>
+        <v>1107.1999999999998</v>
       </c>
       <c r="AD4" s="2">
         <f t="shared" si="2"/>
-        <v>1296.8999999999999</v>
+        <v>1323</v>
       </c>
       <c r="AE4" s="2">
         <f t="shared" si="2"/>
-        <v>1636.1999999999998</v>
+        <v>1662.2999999999997</v>
       </c>
       <c r="AF4" s="2">
         <f t="shared" si="2"/>
-        <v>2050.3000000000002</v>
+        <v>2085.1</v>
       </c>
       <c r="AG4" s="2">
         <f t="shared" si="2"/>
-        <v>2704.2</v>
+        <v>2756.3999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1134,7 +1134,7 @@
         <v>12</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" ref="G5:P5" si="3">G3-G4</f>
+        <f t="shared" ref="G5:Q5" si="3">G3-G4</f>
         <v>136.79999999999998</v>
       </c>
       <c r="H5" s="7">
@@ -1174,12 +1174,12 @@
         <v>453.70000000000005</v>
       </c>
       <c r="Q5" s="7">
-        <f t="shared" ref="Q5" si="4">Q3*0.91</f>
-        <v>491.40000000000003</v>
+        <f t="shared" si="3"/>
+        <v>532.4</v>
       </c>
       <c r="R5" s="7">
         <f>R3*0.92</f>
-        <v>552</v>
+        <v>607.20000000000005</v>
       </c>
       <c r="T5" s="7">
         <f>T3-T4</f>
@@ -1195,47 +1195,47 @@
       </c>
       <c r="W5" s="7">
         <f>W3-W4</f>
-        <v>1852.4</v>
+        <v>1948.6000000000001</v>
       </c>
       <c r="X5" s="7">
         <f>X3*0.92</f>
-        <v>2617.2159999999999</v>
+        <v>2752.3272000000002</v>
       </c>
       <c r="Y5" s="7">
-        <f t="shared" ref="Y5:AG5" si="5">Y3*0.92</f>
-        <v>3402.3807999999999</v>
+        <f t="shared" ref="Y5:AG5" si="4">Y3*0.92</f>
+        <v>3578.0253600000001</v>
       </c>
       <c r="Z5" s="7">
-        <f t="shared" si="5"/>
-        <v>3912.73792</v>
+        <f t="shared" si="4"/>
+        <v>4114.7291639999994</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" si="5"/>
-        <v>4225.7569536000001</v>
+        <f t="shared" si="4"/>
+        <v>4443.9074971199998</v>
       </c>
       <c r="AB5" s="7">
-        <f t="shared" si="5"/>
-        <v>4479.3023708159999</v>
+        <f t="shared" si="4"/>
+        <v>4710.5419469471999</v>
       </c>
       <c r="AC5" s="7">
-        <f t="shared" si="5"/>
-        <v>4658.4744656486409</v>
+        <f t="shared" si="4"/>
+        <v>4946.0690442945606</v>
       </c>
       <c r="AD5" s="7">
-        <f t="shared" si="5"/>
-        <v>4798.2286996181001</v>
+        <f t="shared" si="4"/>
+        <v>5193.3724965092888</v>
       </c>
       <c r="AE5" s="7">
-        <f t="shared" si="5"/>
-        <v>4942.1755606066426</v>
+        <f t="shared" si="4"/>
+        <v>5453.0411213347534</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" si="5"/>
-        <v>5090.4408274248426</v>
+        <f t="shared" si="4"/>
+        <v>5725.6931774014911</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" si="5"/>
-        <v>5243.154052247588</v>
+        <f t="shared" si="4"/>
+        <v>6011.977836271566</v>
       </c>
     </row>
     <row r="6" spans="1:143" x14ac:dyDescent="0.3">
@@ -1273,8 +1273,7 @@
         <v>196.6</v>
       </c>
       <c r="Q6" s="2">
-        <f>M6*1.2</f>
-        <v>200.04</v>
+        <v>196.4</v>
       </c>
       <c r="R6" s="2">
         <f>N6*1.2</f>
@@ -1292,47 +1291,47 @@
       </c>
       <c r="W6" s="2">
         <f>SUM(O6:R6)</f>
-        <v>814.26</v>
+        <v>810.61999999999989</v>
       </c>
       <c r="X6" s="2">
-        <f t="shared" ref="X6:Y6" si="6">W6*1.05</f>
-        <v>854.97300000000007</v>
+        <f t="shared" ref="X6:Y6" si="5">W6*1.05</f>
+        <v>851.15099999999995</v>
       </c>
       <c r="Y6" s="2">
-        <f t="shared" si="6"/>
-        <v>897.72165000000007</v>
+        <f t="shared" si="5"/>
+        <v>893.70854999999995</v>
       </c>
       <c r="Z6" s="2">
         <f>Y6*1.04</f>
-        <v>933.63051600000006</v>
+        <v>929.45689199999993</v>
       </c>
       <c r="AA6" s="2">
         <f>Z6*1.03</f>
-        <v>961.6394314800001</v>
+        <v>957.34059875999992</v>
       </c>
       <c r="AB6" s="2">
-        <f t="shared" ref="AB6:AG6" si="7">AA6*1.03</f>
-        <v>990.48861442440011</v>
+        <f t="shared" ref="AB6:AG6" si="6">AA6*1.03</f>
+        <v>986.06081672279993</v>
       </c>
       <c r="AC6" s="2">
-        <f t="shared" si="7"/>
-        <v>1020.2032728571321</v>
+        <f t="shared" si="6"/>
+        <v>1015.6426412244839</v>
       </c>
       <c r="AD6" s="2">
-        <f t="shared" si="7"/>
-        <v>1050.8093710428461</v>
+        <f t="shared" si="6"/>
+        <v>1046.1119204612185</v>
       </c>
       <c r="AE6" s="2">
-        <f t="shared" si="7"/>
-        <v>1082.3336521741314</v>
+        <f t="shared" si="6"/>
+        <v>1077.495278075055</v>
       </c>
       <c r="AF6" s="2">
-        <f t="shared" si="7"/>
-        <v>1114.8036617393554</v>
+        <f t="shared" si="6"/>
+        <v>1109.8201364173067</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" si="7"/>
-        <v>1148.2477715915361</v>
+        <f t="shared" si="6"/>
+        <v>1143.1147405098259</v>
       </c>
     </row>
     <row r="7" spans="1:143" x14ac:dyDescent="0.3">
@@ -1370,12 +1369,11 @@
         <v>120.6</v>
       </c>
       <c r="Q7" s="2">
-        <f>Q3*0.24</f>
-        <v>129.6</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="R7" s="2">
         <f>R3*0.23</f>
-        <v>138</v>
+        <v>151.80000000000001</v>
       </c>
       <c r="T7" s="2">
         <v>225.1</v>
@@ -1389,47 +1387,47 @@
       </c>
       <c r="W7" s="2">
         <f>SUM(O7:R7)</f>
-        <v>478.9</v>
+        <v>491.8</v>
       </c>
       <c r="X7" s="2">
         <f>X3*0.23</f>
-        <v>654.30399999999997</v>
+        <v>688.08180000000004</v>
       </c>
       <c r="Y7" s="2">
         <f>Y3*0.22</f>
-        <v>813.61279999999999</v>
+        <v>855.61475999999993</v>
       </c>
       <c r="Z7" s="2">
         <f>Z3*0.21</f>
-        <v>893.12495999999987</v>
+        <v>939.23165699999981</v>
       </c>
       <c r="AA7" s="2">
         <f>AA3*0.2</f>
-        <v>918.64281600000004</v>
+        <v>966.06684719999998</v>
       </c>
       <c r="AB7" s="2">
-        <f t="shared" ref="AB7:AG7" si="8">AB3*0.2</f>
-        <v>973.7613849600001</v>
+        <f t="shared" ref="AB7:AG7" si="7">AB3*0.2</f>
+        <v>1024.030858032</v>
       </c>
       <c r="AC7" s="2">
-        <f t="shared" si="8"/>
-        <v>1012.7118403584002</v>
+        <f t="shared" si="7"/>
+        <v>1075.2324009336</v>
       </c>
       <c r="AD7" s="2">
-        <f t="shared" si="8"/>
-        <v>1043.0931955691522</v>
+        <f t="shared" si="7"/>
+        <v>1128.9940209802801</v>
       </c>
       <c r="AE7" s="2">
-        <f t="shared" si="8"/>
-        <v>1074.3859914362267</v>
+        <f t="shared" si="7"/>
+        <v>1185.4437220292941</v>
       </c>
       <c r="AF7" s="2">
-        <f t="shared" si="8"/>
-        <v>1106.6175711793137</v>
+        <f t="shared" si="7"/>
+        <v>1244.7159081307591</v>
       </c>
       <c r="AG7" s="2">
-        <f t="shared" si="8"/>
-        <v>1139.8160983146931</v>
+        <f t="shared" si="7"/>
+        <v>1306.9517035372971</v>
       </c>
     </row>
     <row r="8" spans="1:143" x14ac:dyDescent="0.3">
@@ -1467,12 +1465,11 @@
         <v>68.8</v>
       </c>
       <c r="Q8" s="2">
-        <f>M8*1.1</f>
-        <v>72.27000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="R8" s="2">
-        <f>N8*1.14</f>
-        <v>84.131999999999991</v>
+        <f>N8*1.1</f>
+        <v>81.180000000000007</v>
       </c>
       <c r="T8" s="2">
         <v>143.80000000000001</v>
@@ -1486,47 +1483,47 @@
       </c>
       <c r="W8" s="2">
         <f>SUM(O8:R8)</f>
-        <v>294.60199999999998</v>
+        <v>288.18</v>
       </c>
       <c r="X8" s="2">
         <f>W8*1.03</f>
-        <v>303.44005999999996</v>
+        <v>296.8254</v>
       </c>
       <c r="Y8" s="2">
         <f>X8*1.03</f>
-        <v>312.54326179999998</v>
+        <v>305.73016200000001</v>
       </c>
       <c r="Z8" s="2">
         <f>Y8*1.03</f>
-        <v>321.91955965400001</v>
+        <v>314.90206685999999</v>
       </c>
       <c r="AA8" s="2">
         <f>Z8*1.02</f>
-        <v>328.35795084708002</v>
+        <v>321.2001081972</v>
       </c>
       <c r="AB8" s="2">
         <f>AA8*1.02</f>
-        <v>334.92510986402164</v>
+        <v>327.62411036114401</v>
       </c>
       <c r="AC8" s="2">
-        <f t="shared" ref="AC8:AG8" si="9">AB8*1.02</f>
-        <v>341.62361206130208</v>
+        <f t="shared" ref="AC8:AG8" si="8">AB8*1.02</f>
+        <v>334.17659256836691</v>
       </c>
       <c r="AD8" s="2">
-        <f t="shared" si="9"/>
-        <v>348.45608430252815</v>
+        <f t="shared" si="8"/>
+        <v>340.86012441973423</v>
       </c>
       <c r="AE8" s="2">
-        <f t="shared" si="9"/>
-        <v>355.42520598857874</v>
+        <f t="shared" si="8"/>
+        <v>347.67732690812892</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" si="9"/>
-        <v>362.53371010835031</v>
+        <f t="shared" si="8"/>
+        <v>354.6308734462915</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" si="9"/>
-        <v>369.78438431051734</v>
+        <f t="shared" si="8"/>
+        <v>361.72349091521733</v>
       </c>
     </row>
     <row r="9" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1539,15 +1536,15 @@
         <v>-70.700000000000017</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" ref="H9" si="10">H5-SUM(H6:H8)</f>
+        <f t="shared" ref="H9" si="9">H5-SUM(H6:H8)</f>
         <v>-52.900000000000034</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" ref="I9" si="11">I5-SUM(I6:I8)</f>
+        <f t="shared" ref="I9" si="10">I5-SUM(I6:I8)</f>
         <v>-19.599999999999994</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" ref="J9" si="12">J5-SUM(J6:J8)</f>
+        <f t="shared" ref="J9" si="11">J5-SUM(J6:J8)</f>
         <v>3.0999999999999943</v>
       </c>
       <c r="K9" s="7">
@@ -1555,32 +1552,32 @@
         <v>-589.20000000000005</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" ref="L9:R9" si="13">L5-SUM(L6:L8)</f>
+        <f t="shared" ref="L9:R9" si="12">L5-SUM(L6:L8)</f>
         <v>-31.100000000000023</v>
       </c>
       <c r="M9" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6.8999999999999773</v>
       </c>
       <c r="N9" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>52.999999999999943</v>
       </c>
       <c r="O9" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>3.8999999999999773</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>67.700000000000045</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" si="13"/>
-        <v>89.490000000000066</v>
+        <f t="shared" si="12"/>
+        <v>138.49999999999994</v>
       </c>
       <c r="R9" s="7">
-        <f t="shared" si="13"/>
-        <v>103.548</v>
+        <f t="shared" si="12"/>
+        <v>147.90000000000003</v>
       </c>
       <c r="T9" s="7">
         <f>T5-SUM(T6:T8)</f>
@@ -1596,47 +1593,47 @@
       </c>
       <c r="W9" s="7">
         <f>W5-SUM(W6:W8)</f>
-        <v>264.63800000000037</v>
+        <v>358.00000000000023</v>
       </c>
       <c r="X9" s="7">
-        <f t="shared" ref="X9:AG9" si="14">X5-SUM(X6:X8)</f>
-        <v>804.49893999999995</v>
+        <f t="shared" ref="X9:AG9" si="13">X5-SUM(X6:X8)</f>
+        <v>916.26900000000023</v>
       </c>
       <c r="Y9" s="7">
-        <f t="shared" si="14"/>
-        <v>1378.5030881999999</v>
+        <f t="shared" si="13"/>
+        <v>1522.9718880000005</v>
       </c>
       <c r="Z9" s="7">
-        <f t="shared" si="14"/>
-        <v>1764.0628843460004</v>
+        <f t="shared" si="13"/>
+        <v>1931.1385481399998</v>
       </c>
       <c r="AA9" s="7">
-        <f t="shared" si="14"/>
-        <v>2017.1167552729203</v>
+        <f t="shared" si="13"/>
+        <v>2199.2999429627998</v>
       </c>
       <c r="AB9" s="7">
-        <f t="shared" si="14"/>
-        <v>2180.127261567578</v>
+        <f t="shared" si="13"/>
+        <v>2372.8261618312558</v>
       </c>
       <c r="AC9" s="7">
-        <f t="shared" si="14"/>
-        <v>2283.9357403718068</v>
+        <f t="shared" si="13"/>
+        <v>2521.0174095681095</v>
       </c>
       <c r="AD9" s="7">
-        <f t="shared" si="14"/>
-        <v>2355.8700487035735</v>
+        <f t="shared" si="13"/>
+        <v>2677.4064306480559</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" si="14"/>
-        <v>2430.0307110077056</v>
+        <f t="shared" si="13"/>
+        <v>2842.4247943222749</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="14"/>
-        <v>2506.4858843978227</v>
+        <f t="shared" si="13"/>
+        <v>3016.5262594071341</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="14"/>
-        <v>2585.3057980308413</v>
+        <f t="shared" si="13"/>
+        <v>3200.1879013092257</v>
       </c>
     </row>
     <row r="10" spans="1:143" x14ac:dyDescent="0.3">
@@ -1674,11 +1671,10 @@
         <v>-21.1</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" ref="Q10:R10" si="15">M10*1.03</f>
-        <v>-23.69</v>
+        <v>-22</v>
       </c>
       <c r="R10" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="Q10:R10" si="14">N10*1.03</f>
         <v>-17.613000000000003</v>
       </c>
       <c r="T10" s="2">
@@ -1693,47 +1689,47 @@
       </c>
       <c r="W10" s="2">
         <f>SUM(O10:R10)</f>
-        <v>-82.903000000000006</v>
+        <v>-81.213000000000008</v>
       </c>
       <c r="X10" s="2">
-        <f t="shared" ref="X10:AG10" si="16">W10*1.03</f>
-        <v>-85.390090000000015</v>
+        <f t="shared" ref="X10:AG10" si="15">W10*1.03</f>
+        <v>-83.649390000000011</v>
       </c>
       <c r="Y10" s="2">
-        <f t="shared" si="16"/>
-        <v>-87.951792700000013</v>
+        <f t="shared" si="15"/>
+        <v>-86.15887170000002</v>
       </c>
       <c r="Z10" s="2">
-        <f t="shared" si="16"/>
-        <v>-90.590346481000012</v>
+        <f t="shared" si="15"/>
+        <v>-88.743637851000017</v>
       </c>
       <c r="AA10" s="2">
-        <f t="shared" si="16"/>
-        <v>-93.308056875430012</v>
+        <f t="shared" si="15"/>
+        <v>-91.405946986530026</v>
       </c>
       <c r="AB10" s="2">
-        <f t="shared" si="16"/>
-        <v>-96.107298581692916</v>
+        <f t="shared" si="15"/>
+        <v>-94.148125396125934</v>
       </c>
       <c r="AC10" s="2">
-        <f t="shared" si="16"/>
-        <v>-98.99051753914371</v>
+        <f t="shared" si="15"/>
+        <v>-96.972569158009719</v>
       </c>
       <c r="AD10" s="2">
-        <f t="shared" si="16"/>
-        <v>-101.96023306531802</v>
+        <f t="shared" si="15"/>
+        <v>-99.881746232750018</v>
       </c>
       <c r="AE10" s="2">
-        <f t="shared" si="16"/>
-        <v>-105.01904005727756</v>
+        <f t="shared" si="15"/>
+        <v>-102.87819861973252</v>
       </c>
       <c r="AF10" s="2">
-        <f t="shared" si="16"/>
-        <v>-108.1696112589959</v>
+        <f t="shared" si="15"/>
+        <v>-105.96454457832449</v>
       </c>
       <c r="AG10" s="2">
-        <f t="shared" si="16"/>
-        <v>-111.41469959676579</v>
+        <f t="shared" si="15"/>
+        <v>-109.14348091567423</v>
       </c>
     </row>
     <row r="11" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1746,15 +1742,15 @@
         <v>-60.000000000000014</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" ref="H11" si="17">H9-H10</f>
+        <f t="shared" ref="H11" si="16">H9-H10</f>
         <v>-39.600000000000037</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" ref="I11" si="18">I9-I10</f>
+        <f t="shared" ref="I11" si="17">I9-I10</f>
         <v>-6.9999999999999947</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" ref="J11" si="19">J9-J10</f>
+        <f t="shared" ref="J11" si="18">J9-J10</f>
         <v>19.599999999999994</v>
       </c>
       <c r="K11" s="7">
@@ -1762,32 +1758,32 @@
         <v>-574.6</v>
       </c>
       <c r="L11" s="7">
-        <f t="shared" ref="L11:R11" si="20">L9-L10</f>
+        <f t="shared" ref="L11:R11" si="19">L9-L10</f>
         <v>-10.400000000000023</v>
       </c>
       <c r="M11" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>29.899999999999977</v>
       </c>
       <c r="N11" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>70.099999999999937</v>
       </c>
       <c r="O11" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>24.399999999999977</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>88.80000000000004</v>
       </c>
       <c r="Q11" s="7">
-        <f t="shared" si="20"/>
-        <v>113.18000000000006</v>
+        <f t="shared" si="19"/>
+        <v>160.49999999999994</v>
       </c>
       <c r="R11" s="7">
-        <f t="shared" si="20"/>
-        <v>121.161</v>
+        <f t="shared" si="19"/>
+        <v>165.51300000000003</v>
       </c>
       <c r="T11" s="7">
         <f>T9-T10</f>
@@ -1803,47 +1799,47 @@
       </c>
       <c r="W11" s="7">
         <f>W9-W10</f>
-        <v>347.54100000000039</v>
+        <v>439.21300000000025</v>
       </c>
       <c r="X11" s="7">
-        <f t="shared" ref="X11:AG11" si="21">X9-X10</f>
-        <v>889.88902999999993</v>
+        <f t="shared" ref="X11:AG11" si="20">X9-X10</f>
+        <v>999.91839000000027</v>
       </c>
       <c r="Y11" s="7">
-        <f t="shared" si="21"/>
-        <v>1466.4548808999998</v>
+        <f t="shared" si="20"/>
+        <v>1609.1307597000005</v>
       </c>
       <c r="Z11" s="7">
-        <f t="shared" si="21"/>
-        <v>1854.6532308270005</v>
+        <f t="shared" si="20"/>
+        <v>2019.8821859909999</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" si="21"/>
-        <v>2110.4248121483502</v>
+        <f t="shared" si="20"/>
+        <v>2290.70588994933</v>
       </c>
       <c r="AB11" s="7">
-        <f t="shared" si="21"/>
-        <v>2276.2345601492707</v>
+        <f t="shared" si="20"/>
+        <v>2466.9742872273819</v>
       </c>
       <c r="AC11" s="7">
-        <f t="shared" si="21"/>
-        <v>2382.9262579109504</v>
+        <f t="shared" si="20"/>
+        <v>2617.9899787261193</v>
       </c>
       <c r="AD11" s="7">
-        <f t="shared" si="21"/>
-        <v>2457.8302817688914</v>
+        <f t="shared" si="20"/>
+        <v>2777.2881768808061</v>
       </c>
       <c r="AE11" s="7">
-        <f t="shared" si="21"/>
-        <v>2535.049751064983</v>
+        <f t="shared" si="20"/>
+        <v>2945.3029929420072</v>
       </c>
       <c r="AF11" s="7">
-        <f t="shared" si="21"/>
-        <v>2614.6554956568184</v>
+        <f t="shared" si="20"/>
+        <v>3122.4908039854586</v>
       </c>
       <c r="AG11" s="7">
-        <f t="shared" si="21"/>
-        <v>2696.7204976276071</v>
+        <f t="shared" si="20"/>
+        <v>3309.3313822249002</v>
       </c>
     </row>
     <row r="12" spans="1:143" x14ac:dyDescent="0.3">
@@ -1881,7 +1877,7 @@
         <v>-0.4</v>
       </c>
       <c r="Q12" s="2">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="R12" s="2">
         <v>0</v>
@@ -1898,47 +1894,47 @@
       </c>
       <c r="W12" s="2">
         <f>SUM(O12:R12)</f>
-        <v>-2.1</v>
+        <v>-4.2</v>
       </c>
       <c r="X12" s="2">
-        <f t="shared" ref="X12:AG12" si="22">X11*0.15</f>
-        <v>133.48335449999999</v>
+        <f t="shared" ref="X12:AG12" si="21">X11*0.15</f>
+        <v>149.98775850000004</v>
       </c>
       <c r="Y12" s="2">
-        <f t="shared" si="22"/>
-        <v>219.96823213499997</v>
+        <f t="shared" si="21"/>
+        <v>241.36961395500006</v>
       </c>
       <c r="Z12" s="2">
-        <f t="shared" si="22"/>
-        <v>278.19798462405004</v>
+        <f t="shared" si="21"/>
+        <v>302.98232789865</v>
       </c>
       <c r="AA12" s="2">
-        <f t="shared" si="22"/>
-        <v>316.56372182225249</v>
+        <f t="shared" si="21"/>
+        <v>343.60588349239947</v>
       </c>
       <c r="AB12" s="2">
-        <f t="shared" si="22"/>
-        <v>341.43518402239062</v>
+        <f t="shared" si="21"/>
+        <v>370.04614308410726</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" si="22"/>
-        <v>357.43893868664253</v>
+        <f t="shared" si="21"/>
+        <v>392.69849680891787</v>
       </c>
       <c r="AD12" s="2">
-        <f t="shared" si="22"/>
-        <v>368.67454226533368</v>
+        <f t="shared" si="21"/>
+        <v>416.59322653212092</v>
       </c>
       <c r="AE12" s="2">
-        <f t="shared" si="22"/>
-        <v>380.25746265974743</v>
+        <f t="shared" si="21"/>
+        <v>441.79544894130106</v>
       </c>
       <c r="AF12" s="2">
-        <f t="shared" si="22"/>
-        <v>392.19832434852276</v>
+        <f t="shared" si="21"/>
+        <v>468.37362059781879</v>
       </c>
       <c r="AG12" s="2">
-        <f t="shared" si="22"/>
-        <v>404.50807464414106</v>
+        <f t="shared" si="21"/>
+        <v>496.39970733373502</v>
       </c>
     </row>
     <row r="13" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1951,15 +1947,15 @@
         <v>-61.000000000000014</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" ref="H13" si="23">H11-H12</f>
+        <f t="shared" ref="H13" si="22">H11-H12</f>
         <v>-41.000000000000036</v>
       </c>
       <c r="I13" s="7">
-        <f t="shared" ref="I13" si="24">I11-I12</f>
+        <f t="shared" ref="I13" si="23">I11-I12</f>
         <v>-7.399999999999995</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" ref="J13" si="25">J11-J12</f>
+        <f t="shared" ref="J13" si="24">J11-J12</f>
         <v>18.699999999999996</v>
       </c>
       <c r="K13" s="7">
@@ -1967,32 +1963,32 @@
         <v>-575</v>
       </c>
       <c r="L13" s="7">
-        <f t="shared" ref="L13:N13" si="26">L11-L12</f>
+        <f t="shared" ref="L13:N13" si="25">L11-L12</f>
         <v>-10.200000000000024</v>
       </c>
       <c r="M13" s="7">
+        <f t="shared" si="25"/>
+        <v>29.899999999999977</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="25"/>
+        <v>71.099999999999937</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" ref="O13:R13" si="26">O11-O12</f>
+        <v>26.099999999999977</v>
+      </c>
+      <c r="P13" s="7">
         <f t="shared" si="26"/>
-        <v>29.899999999999977</v>
-      </c>
-      <c r="N13" s="7">
+        <v>89.200000000000045</v>
+      </c>
+      <c r="Q13" s="7">
         <f t="shared" si="26"/>
-        <v>71.099999999999937</v>
-      </c>
-      <c r="O13" s="7">
-        <f t="shared" ref="O13:R13" si="27">O11-O12</f>
-        <v>26.099999999999977</v>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="27"/>
-        <v>89.200000000000045</v>
-      </c>
-      <c r="Q13" s="7">
-        <f t="shared" si="27"/>
-        <v>113.18000000000006</v>
+        <v>162.59999999999994</v>
       </c>
       <c r="R13" s="7">
-        <f t="shared" si="27"/>
-        <v>121.161</v>
+        <f t="shared" si="26"/>
+        <v>165.51300000000003</v>
       </c>
       <c r="T13" s="7">
         <f>T11-T12</f>
@@ -2007,488 +2003,488 @@
         <v>-484.2000000000001</v>
       </c>
       <c r="W13" s="7">
-        <f t="shared" ref="W13" si="28">W11-W12</f>
-        <v>349.64100000000042</v>
+        <f t="shared" ref="W13" si="27">W11-W12</f>
+        <v>443.41300000000024</v>
       </c>
       <c r="X13" s="7">
-        <f t="shared" ref="X13" si="29">X11-X12</f>
-        <v>756.40567549999992</v>
+        <f t="shared" ref="X13" si="28">X11-X12</f>
+        <v>849.93063150000023</v>
       </c>
       <c r="Y13" s="7">
-        <f t="shared" ref="Y13" si="30">Y11-Y12</f>
-        <v>1246.4866487649999</v>
+        <f t="shared" ref="Y13" si="29">Y11-Y12</f>
+        <v>1367.7611457450005</v>
       </c>
       <c r="Z13" s="7">
-        <f t="shared" ref="Z13" si="31">Z11-Z12</f>
-        <v>1576.4552462029505</v>
+        <f t="shared" ref="Z13" si="30">Z11-Z12</f>
+        <v>1716.8998580923499</v>
       </c>
       <c r="AA13" s="7">
-        <f t="shared" ref="AA13" si="32">AA11-AA12</f>
-        <v>1793.8610903260976</v>
+        <f t="shared" ref="AA13" si="31">AA11-AA12</f>
+        <v>1947.1000064569305</v>
       </c>
       <c r="AB13" s="7">
-        <f t="shared" ref="AB13" si="33">AB11-AB12</f>
-        <v>1934.7993761268801</v>
+        <f t="shared" ref="AB13" si="32">AB11-AB12</f>
+        <v>2096.9281441432745</v>
       </c>
       <c r="AC13" s="7">
-        <f t="shared" ref="AC13" si="34">AC11-AC12</f>
-        <v>2025.4873192243078</v>
+        <f t="shared" ref="AC13" si="33">AC11-AC12</f>
+        <v>2225.2914819172015</v>
       </c>
       <c r="AD13" s="7">
-        <f t="shared" ref="AD13" si="35">AD11-AD12</f>
-        <v>2089.1557395035579</v>
+        <f t="shared" ref="AD13" si="34">AD11-AD12</f>
+        <v>2360.6949503486853</v>
       </c>
       <c r="AE13" s="7">
-        <f t="shared" ref="AE13" si="36">AE11-AE12</f>
-        <v>2154.7922884052355</v>
+        <f t="shared" ref="AE13" si="35">AE11-AE12</f>
+        <v>2503.5075440007063</v>
       </c>
       <c r="AF13" s="7">
-        <f t="shared" ref="AF13" si="37">AF11-AF12</f>
-        <v>2222.4571713082955</v>
+        <f t="shared" ref="AF13" si="36">AF11-AF12</f>
+        <v>2654.1171833876397</v>
       </c>
       <c r="AG13" s="7">
-        <f t="shared" ref="AG13" si="38">AG11-AG12</f>
-        <v>2292.2124229834662</v>
+        <f t="shared" ref="AG13" si="37">AG11-AG12</f>
+        <v>2812.9316748911651</v>
       </c>
       <c r="AH13" s="6">
         <f>AG13*(1+$AJ$18)</f>
-        <v>2269.2902987536318</v>
+        <v>2784.8023581422535</v>
       </c>
       <c r="AI13" s="6">
-        <f t="shared" ref="AI13:CT13" si="39">AH13*(1+$AJ$18)</f>
-        <v>2246.5973957660954</v>
+        <f t="shared" ref="AI13:CT13" si="38">AH13*(1+$AJ$18)</f>
+        <v>2756.9543345608308</v>
       </c>
       <c r="AJ13" s="6">
+        <f t="shared" si="38"/>
+        <v>2729.3847912152223</v>
+      </c>
+      <c r="AK13" s="6">
+        <f t="shared" si="38"/>
+        <v>2702.0909433030702</v>
+      </c>
+      <c r="AL13" s="6">
+        <f t="shared" si="38"/>
+        <v>2675.0700338700394</v>
+      </c>
+      <c r="AM13" s="6">
+        <f t="shared" si="38"/>
+        <v>2648.319333531339</v>
+      </c>
+      <c r="AN13" s="6">
+        <f t="shared" si="38"/>
+        <v>2621.8361401960256</v>
+      </c>
+      <c r="AO13" s="6">
+        <f t="shared" si="38"/>
+        <v>2595.6177787940651</v>
+      </c>
+      <c r="AP13" s="6">
+        <f t="shared" si="38"/>
+        <v>2569.6616010061243</v>
+      </c>
+      <c r="AQ13" s="6">
+        <f t="shared" si="38"/>
+        <v>2543.9649849960629</v>
+      </c>
+      <c r="AR13" s="6">
+        <f t="shared" si="38"/>
+        <v>2518.5253351461024</v>
+      </c>
+      <c r="AS13" s="6">
+        <f t="shared" si="38"/>
+        <v>2493.3400817946413</v>
+      </c>
+      <c r="AT13" s="6">
+        <f t="shared" si="38"/>
+        <v>2468.406680976695</v>
+      </c>
+      <c r="AU13" s="6">
+        <f t="shared" si="38"/>
+        <v>2443.722614166928</v>
+      </c>
+      <c r="AV13" s="6">
+        <f t="shared" si="38"/>
+        <v>2419.2853880252587</v>
+      </c>
+      <c r="AW13" s="6">
+        <f t="shared" si="38"/>
+        <v>2395.0925341450061</v>
+      </c>
+      <c r="AX13" s="6">
+        <f t="shared" si="38"/>
+        <v>2371.1416088035562</v>
+      </c>
+      <c r="AY13" s="6">
+        <f t="shared" si="38"/>
+        <v>2347.4301927155207</v>
+      </c>
+      <c r="AZ13" s="6">
+        <f t="shared" si="38"/>
+        <v>2323.9558907883657</v>
+      </c>
+      <c r="BA13" s="6">
+        <f t="shared" si="38"/>
+        <v>2300.7163318804819</v>
+      </c>
+      <c r="BB13" s="6">
+        <f t="shared" si="38"/>
+        <v>2277.709168561677</v>
+      </c>
+      <c r="BC13" s="6">
+        <f t="shared" si="38"/>
+        <v>2254.9320768760604</v>
+      </c>
+      <c r="BD13" s="6">
+        <f t="shared" si="38"/>
+        <v>2232.3827561072999</v>
+      </c>
+      <c r="BE13" s="6">
+        <f t="shared" si="38"/>
+        <v>2210.058928546227</v>
+      </c>
+      <c r="BF13" s="6">
+        <f t="shared" si="38"/>
+        <v>2187.9583392607647</v>
+      </c>
+      <c r="BG13" s="6">
+        <f t="shared" si="38"/>
+        <v>2166.0787558681568</v>
+      </c>
+      <c r="BH13" s="6">
+        <f t="shared" si="38"/>
+        <v>2144.4179683094753</v>
+      </c>
+      <c r="BI13" s="6">
+        <f t="shared" si="38"/>
+        <v>2122.9737886263806</v>
+      </c>
+      <c r="BJ13" s="6">
+        <f t="shared" si="38"/>
+        <v>2101.7440507401166</v>
+      </c>
+      <c r="BK13" s="6">
+        <f t="shared" si="38"/>
+        <v>2080.7266102327153</v>
+      </c>
+      <c r="BL13" s="6">
+        <f t="shared" si="38"/>
+        <v>2059.9193441303883</v>
+      </c>
+      <c r="BM13" s="6">
+        <f t="shared" si="38"/>
+        <v>2039.3201506890844</v>
+      </c>
+      <c r="BN13" s="6">
+        <f t="shared" si="38"/>
+        <v>2018.9269491821935</v>
+      </c>
+      <c r="BO13" s="6">
+        <f t="shared" si="38"/>
+        <v>1998.7376796903716</v>
+      </c>
+      <c r="BP13" s="6">
+        <f t="shared" si="38"/>
+        <v>1978.7503028934677</v>
+      </c>
+      <c r="BQ13" s="6">
+        <f t="shared" si="38"/>
+        <v>1958.9627998645331</v>
+      </c>
+      <c r="BR13" s="6">
+        <f t="shared" si="38"/>
+        <v>1939.3731718658878</v>
+      </c>
+      <c r="BS13" s="6">
+        <f t="shared" si="38"/>
+        <v>1919.9794401472288</v>
+      </c>
+      <c r="BT13" s="6">
+        <f t="shared" si="38"/>
+        <v>1900.7796457457566</v>
+      </c>
+      <c r="BU13" s="6">
+        <f t="shared" si="38"/>
+        <v>1881.7718492882991</v>
+      </c>
+      <c r="BV13" s="6">
+        <f t="shared" si="38"/>
+        <v>1862.9541307954162</v>
+      </c>
+      <c r="BW13" s="6">
+        <f t="shared" si="38"/>
+        <v>1844.3245894874619</v>
+      </c>
+      <c r="BX13" s="6">
+        <f t="shared" si="38"/>
+        <v>1825.8813435925872</v>
+      </c>
+      <c r="BY13" s="6">
+        <f t="shared" si="38"/>
+        <v>1807.6225301566612</v>
+      </c>
+      <c r="BZ13" s="6">
+        <f t="shared" si="38"/>
+        <v>1789.5463048550946</v>
+      </c>
+      <c r="CA13" s="6">
+        <f t="shared" si="38"/>
+        <v>1771.6508418065437</v>
+      </c>
+      <c r="CB13" s="6">
+        <f t="shared" si="38"/>
+        <v>1753.9343333884783</v>
+      </c>
+      <c r="CC13" s="6">
+        <f t="shared" si="38"/>
+        <v>1736.3949900545936</v>
+      </c>
+      <c r="CD13" s="6">
+        <f t="shared" si="38"/>
+        <v>1719.0310401540476</v>
+      </c>
+      <c r="CE13" s="6">
+        <f t="shared" si="38"/>
+        <v>1701.8407297525071</v>
+      </c>
+      <c r="CF13" s="6">
+        <f t="shared" si="38"/>
+        <v>1684.822322454982</v>
+      </c>
+      <c r="CG13" s="6">
+        <f t="shared" si="38"/>
+        <v>1667.9740992304321</v>
+      </c>
+      <c r="CH13" s="6">
+        <f t="shared" si="38"/>
+        <v>1651.2943582381279</v>
+      </c>
+      <c r="CI13" s="6">
+        <f t="shared" si="38"/>
+        <v>1634.7814146557466</v>
+      </c>
+      <c r="CJ13" s="6">
+        <f t="shared" si="38"/>
+        <v>1618.4336005091891</v>
+      </c>
+      <c r="CK13" s="6">
+        <f t="shared" si="38"/>
+        <v>1602.2492645040973</v>
+      </c>
+      <c r="CL13" s="6">
+        <f t="shared" si="38"/>
+        <v>1586.2267718590563</v>
+      </c>
+      <c r="CM13" s="6">
+        <f t="shared" si="38"/>
+        <v>1570.3645041404657</v>
+      </c>
+      <c r="CN13" s="6">
+        <f t="shared" si="38"/>
+        <v>1554.6608590990611</v>
+      </c>
+      <c r="CO13" s="6">
+        <f t="shared" si="38"/>
+        <v>1539.1142505080704</v>
+      </c>
+      <c r="CP13" s="6">
+        <f t="shared" si="38"/>
+        <v>1523.7231080029896</v>
+      </c>
+      <c r="CQ13" s="6">
+        <f t="shared" si="38"/>
+        <v>1508.4858769229597</v>
+      </c>
+      <c r="CR13" s="6">
+        <f t="shared" si="38"/>
+        <v>1493.4010181537301</v>
+      </c>
+      <c r="CS13" s="6">
+        <f t="shared" si="38"/>
+        <v>1478.4670079721927</v>
+      </c>
+      <c r="CT13" s="6">
+        <f t="shared" si="38"/>
+        <v>1463.6823378924707</v>
+      </c>
+      <c r="CU13" s="6">
+        <f t="shared" ref="CU13:EM13" si="39">CT13*(1+$AJ$18)</f>
+        <v>1449.0455145135461</v>
+      </c>
+      <c r="CV13" s="6">
         <f t="shared" si="39"/>
-        <v>2224.1314218084344</v>
-      </c>
-      <c r="AK13" s="6">
+        <v>1434.5550593684106</v>
+      </c>
+      <c r="CW13" s="6">
         <f t="shared" si="39"/>
-        <v>2201.89010759035</v>
-      </c>
-      <c r="AL13" s="6">
+        <v>1420.2095087747266</v>
+      </c>
+      <c r="CX13" s="6">
         <f t="shared" si="39"/>
-        <v>2179.8712065144464</v>
-      </c>
-      <c r="AM13" s="6">
+        <v>1406.0074136869794</v>
+      </c>
+      <c r="CY13" s="6">
         <f t="shared" si="39"/>
-        <v>2158.0724944493018</v>
-      </c>
-      <c r="AN13" s="6">
+        <v>1391.9473395501095</v>
+      </c>
+      <c r="CZ13" s="6">
         <f t="shared" si="39"/>
-        <v>2136.4917695048089</v>
-      </c>
-      <c r="AO13" s="6">
+        <v>1378.0278661546083</v>
+      </c>
+      <c r="DA13" s="6">
         <f t="shared" si="39"/>
-        <v>2115.1268518097609</v>
-      </c>
-      <c r="AP13" s="6">
+        <v>1364.2475874930622</v>
+      </c>
+      <c r="DB13" s="6">
         <f t="shared" si="39"/>
-        <v>2093.975583291663</v>
-      </c>
-      <c r="AQ13" s="6">
+        <v>1350.6051116181316</v>
+      </c>
+      <c r="DC13" s="6">
         <f t="shared" si="39"/>
-        <v>2073.0358274587466</v>
-      </c>
-      <c r="AR13" s="6">
+        <v>1337.0990605019501</v>
+      </c>
+      <c r="DD13" s="6">
         <f t="shared" si="39"/>
-        <v>2052.3054691841589</v>
-      </c>
-      <c r="AS13" s="6">
+        <v>1323.7280698969307</v>
+      </c>
+      <c r="DE13" s="6">
         <f t="shared" si="39"/>
-        <v>2031.7824144923172</v>
-      </c>
-      <c r="AT13" s="6">
+        <v>1310.4907891979615</v>
+      </c>
+      <c r="DF13" s="6">
         <f t="shared" si="39"/>
-        <v>2011.4645903473941</v>
-      </c>
-      <c r="AU13" s="6">
+        <v>1297.3858813059819</v>
+      </c>
+      <c r="DG13" s="6">
         <f t="shared" si="39"/>
-        <v>1991.3499444439201</v>
-      </c>
-      <c r="AV13" s="6">
+        <v>1284.412022492922</v>
+      </c>
+      <c r="DH13" s="6">
         <f t="shared" si="39"/>
-        <v>1971.436444999481</v>
-      </c>
-      <c r="AW13" s="6">
+        <v>1271.5679022679928</v>
+      </c>
+      <c r="DI13" s="6">
         <f t="shared" si="39"/>
-        <v>1951.7220805494862</v>
-      </c>
-      <c r="AX13" s="6">
+        <v>1258.8522232453129</v>
+      </c>
+      <c r="DJ13" s="6">
         <f t="shared" si="39"/>
-        <v>1932.2048597439914</v>
-      </c>
-      <c r="AY13" s="6">
+        <v>1246.2637010128597</v>
+      </c>
+      <c r="DK13" s="6">
         <f t="shared" si="39"/>
-        <v>1912.8828111465514</v>
-      </c>
-      <c r="AZ13" s="6">
+        <v>1233.801064002731</v>
+      </c>
+      <c r="DL13" s="6">
         <f t="shared" si="39"/>
-        <v>1893.7539830350859</v>
-      </c>
-      <c r="BA13" s="6">
+        <v>1221.4630533627037</v>
+      </c>
+      <c r="DM13" s="6">
         <f t="shared" si="39"/>
-        <v>1874.8164432047349</v>
-      </c>
-      <c r="BB13" s="6">
+        <v>1209.2484228290766</v>
+      </c>
+      <c r="DN13" s="6">
         <f t="shared" si="39"/>
-        <v>1856.0682787726876</v>
-      </c>
-      <c r="BC13" s="6">
+        <v>1197.1559386007859</v>
+      </c>
+      <c r="DO13" s="6">
         <f t="shared" si="39"/>
-        <v>1837.5075959849607</v>
-      </c>
-      <c r="BD13" s="6">
+        <v>1185.1843792147781</v>
+      </c>
+      <c r="DP13" s="6">
         <f t="shared" si="39"/>
-        <v>1819.132520025111</v>
-      </c>
-      <c r="BE13" s="6">
+        <v>1173.3325354226304</v>
+      </c>
+      <c r="DQ13" s="6">
         <f t="shared" si="39"/>
-        <v>1800.9411948248598</v>
-      </c>
-      <c r="BF13" s="6">
+        <v>1161.5992100684041</v>
+      </c>
+      <c r="DR13" s="6">
         <f t="shared" si="39"/>
-        <v>1782.9317828766111</v>
-      </c>
-      <c r="BG13" s="6">
+        <v>1149.9832179677201</v>
+      </c>
+      <c r="DS13" s="6">
         <f t="shared" si="39"/>
-        <v>1765.102465047845</v>
-      </c>
-      <c r="BH13" s="6">
+        <v>1138.4833857880428</v>
+      </c>
+      <c r="DT13" s="6">
         <f t="shared" si="39"/>
-        <v>1747.4514403973665</v>
-      </c>
-      <c r="BI13" s="6">
+        <v>1127.0985519301623</v>
+      </c>
+      <c r="DU13" s="6">
         <f t="shared" si="39"/>
-        <v>1729.9769259933928</v>
-      </c>
-      <c r="BJ13" s="6">
+        <v>1115.8275664108608</v>
+      </c>
+      <c r="DV13" s="6">
         <f t="shared" si="39"/>
-        <v>1712.6771567334588</v>
-      </c>
-      <c r="BK13" s="6">
+        <v>1104.669290746752</v>
+      </c>
+      <c r="DW13" s="6">
         <f t="shared" si="39"/>
-        <v>1695.5503851661242</v>
-      </c>
-      <c r="BL13" s="6">
+        <v>1093.6225978392845</v>
+      </c>
+      <c r="DX13" s="6">
         <f t="shared" si="39"/>
-        <v>1678.594881314463</v>
-      </c>
-      <c r="BM13" s="6">
+        <v>1082.6863718608915</v>
+      </c>
+      <c r="DY13" s="6">
         <f t="shared" si="39"/>
-        <v>1661.8089325013184</v>
-      </c>
-      <c r="BN13" s="6">
+        <v>1071.8595081422827</v>
+      </c>
+      <c r="DZ13" s="6">
         <f t="shared" si="39"/>
-        <v>1645.1908431763052</v>
-      </c>
-      <c r="BO13" s="6">
+        <v>1061.1409130608599</v>
+      </c>
+      <c r="EA13" s="6">
         <f t="shared" si="39"/>
-        <v>1628.7389347445421</v>
-      </c>
-      <c r="BP13" s="6">
+        <v>1050.5295039302514</v>
+      </c>
+      <c r="EB13" s="6">
         <f t="shared" si="39"/>
-        <v>1612.4515453970967</v>
-      </c>
-      <c r="BQ13" s="6">
+        <v>1040.0242088909488</v>
+      </c>
+      <c r="EC13" s="6">
         <f t="shared" si="39"/>
-        <v>1596.3270299431256</v>
-      </c>
-      <c r="BR13" s="6">
+        <v>1029.6239668020394</v>
+      </c>
+      <c r="ED13" s="6">
         <f t="shared" si="39"/>
-        <v>1580.3637596436943</v>
-      </c>
-      <c r="BS13" s="6">
+        <v>1019.327727134019</v>
+      </c>
+      <c r="EE13" s="6">
         <f t="shared" si="39"/>
-        <v>1564.5601220472572</v>
-      </c>
-      <c r="BT13" s="6">
+        <v>1009.1344498626788</v>
+      </c>
+      <c r="EF13" s="6">
         <f t="shared" si="39"/>
-        <v>1548.9145208267846</v>
-      </c>
-      <c r="BU13" s="6">
+        <v>999.04310536405205</v>
+      </c>
+      <c r="EG13" s="6">
         <f t="shared" si="39"/>
-        <v>1533.4253756185167</v>
-      </c>
-      <c r="BV13" s="6">
+        <v>989.05267431041148</v>
+      </c>
+      <c r="EH13" s="6">
         <f t="shared" si="39"/>
-        <v>1518.0911218623314</v>
-      </c>
-      <c r="BW13" s="6">
+        <v>979.16214756730733</v>
+      </c>
+      <c r="EI13" s="6">
         <f t="shared" si="39"/>
-        <v>1502.9102106437081</v>
-      </c>
-      <c r="BX13" s="6">
+        <v>969.37052609163425</v>
+      </c>
+      <c r="EJ13" s="6">
         <f t="shared" si="39"/>
-        <v>1487.8811085372711</v>
-      </c>
-      <c r="BY13" s="6">
+        <v>959.67682083071793</v>
+      </c>
+      <c r="EK13" s="6">
         <f t="shared" si="39"/>
-        <v>1473.0022974518984</v>
-      </c>
-      <c r="BZ13" s="6">
+        <v>950.08005262241079</v>
+      </c>
+      <c r="EL13" s="6">
         <f t="shared" si="39"/>
-        <v>1458.2722744773794</v>
-      </c>
-      <c r="CA13" s="6">
+        <v>940.57925209618668</v>
+      </c>
+      <c r="EM13" s="6">
         <f t="shared" si="39"/>
-        <v>1443.6895517326057</v>
-      </c>
-      <c r="CB13" s="6">
-        <f t="shared" si="39"/>
-        <v>1429.2526562152796</v>
-      </c>
-      <c r="CC13" s="6">
-        <f t="shared" si="39"/>
-        <v>1414.9601296531268</v>
-      </c>
-      <c r="CD13" s="6">
-        <f t="shared" si="39"/>
-        <v>1400.8105283565956</v>
-      </c>
-      <c r="CE13" s="6">
-        <f t="shared" si="39"/>
-        <v>1386.8024230730296</v>
-      </c>
-      <c r="CF13" s="6">
-        <f t="shared" si="39"/>
-        <v>1372.9343988422993</v>
-      </c>
-      <c r="CG13" s="6">
-        <f t="shared" si="39"/>
-        <v>1359.2050548538764</v>
-      </c>
-      <c r="CH13" s="6">
-        <f t="shared" si="39"/>
-        <v>1345.6130043053377</v>
-      </c>
-      <c r="CI13" s="6">
-        <f t="shared" si="39"/>
-        <v>1332.1568742622842</v>
-      </c>
-      <c r="CJ13" s="6">
-        <f t="shared" si="39"/>
-        <v>1318.8353055196612</v>
-      </c>
-      <c r="CK13" s="6">
-        <f t="shared" si="39"/>
-        <v>1305.6469524644647</v>
-      </c>
-      <c r="CL13" s="6">
-        <f t="shared" si="39"/>
-        <v>1292.59048293982</v>
-      </c>
-      <c r="CM13" s="6">
-        <f t="shared" si="39"/>
-        <v>1279.6645781104219</v>
-      </c>
-      <c r="CN13" s="6">
-        <f t="shared" si="39"/>
-        <v>1266.8679323293177</v>
-      </c>
-      <c r="CO13" s="6">
-        <f t="shared" si="39"/>
-        <v>1254.1992530060245</v>
-      </c>
-      <c r="CP13" s="6">
-        <f t="shared" si="39"/>
-        <v>1241.6572604759642</v>
-      </c>
-      <c r="CQ13" s="6">
-        <f t="shared" si="39"/>
-        <v>1229.2406878712045</v>
-      </c>
-      <c r="CR13" s="6">
-        <f t="shared" si="39"/>
-        <v>1216.9482809924925</v>
-      </c>
-      <c r="CS13" s="6">
-        <f t="shared" si="39"/>
-        <v>1204.7787981825677</v>
-      </c>
-      <c r="CT13" s="6">
-        <f t="shared" si="39"/>
-        <v>1192.731010200742</v>
-      </c>
-      <c r="CU13" s="6">
-        <f t="shared" ref="CU13:EM13" si="40">CT13*(1+$AJ$18)</f>
-        <v>1180.8037000987347</v>
-      </c>
-      <c r="CV13" s="6">
-        <f t="shared" si="40"/>
-        <v>1168.9956630977474</v>
-      </c>
-      <c r="CW13" s="6">
-        <f t="shared" si="40"/>
-        <v>1157.3057064667698</v>
-      </c>
-      <c r="CX13" s="6">
-        <f t="shared" si="40"/>
-        <v>1145.7326494021022</v>
-      </c>
-      <c r="CY13" s="6">
-        <f t="shared" si="40"/>
-        <v>1134.2753229080811</v>
-      </c>
-      <c r="CZ13" s="6">
-        <f t="shared" si="40"/>
-        <v>1122.9325696790002</v>
-      </c>
-      <c r="DA13" s="6">
-        <f t="shared" si="40"/>
-        <v>1111.7032439822101</v>
-      </c>
-      <c r="DB13" s="6">
-        <f t="shared" si="40"/>
-        <v>1100.5862115423879</v>
-      </c>
-      <c r="DC13" s="6">
-        <f t="shared" si="40"/>
-        <v>1089.5803494269639</v>
-      </c>
-      <c r="DD13" s="6">
-        <f t="shared" si="40"/>
-        <v>1078.6845459326944</v>
-      </c>
-      <c r="DE13" s="6">
-        <f t="shared" si="40"/>
-        <v>1067.8977004733674</v>
-      </c>
-      <c r="DF13" s="6">
-        <f t="shared" si="40"/>
-        <v>1057.2187234686337</v>
-      </c>
-      <c r="DG13" s="6">
-        <f t="shared" si="40"/>
-        <v>1046.6465362339472</v>
-      </c>
-      <c r="DH13" s="6">
-        <f t="shared" si="40"/>
-        <v>1036.1800708716078</v>
-      </c>
-      <c r="DI13" s="6">
-        <f t="shared" si="40"/>
-        <v>1025.8182701628916</v>
-      </c>
-      <c r="DJ13" s="6">
-        <f t="shared" si="40"/>
-        <v>1015.5600874612627</v>
-      </c>
-      <c r="DK13" s="6">
-        <f t="shared" si="40"/>
-        <v>1005.40448658665</v>
-      </c>
-      <c r="DL13" s="6">
-        <f t="shared" si="40"/>
-        <v>995.35044172078346</v>
-      </c>
-      <c r="DM13" s="6">
-        <f t="shared" si="40"/>
-        <v>985.39693730357567</v>
-      </c>
-      <c r="DN13" s="6">
-        <f t="shared" si="40"/>
-        <v>975.54296793053993</v>
-      </c>
-      <c r="DO13" s="6">
-        <f t="shared" si="40"/>
-        <v>965.78753825123454</v>
-      </c>
-      <c r="DP13" s="6">
-        <f t="shared" si="40"/>
-        <v>956.12966286872222</v>
-      </c>
-      <c r="DQ13" s="6">
-        <f t="shared" si="40"/>
-        <v>946.56836624003495</v>
-      </c>
-      <c r="DR13" s="6">
-        <f t="shared" si="40"/>
-        <v>937.1026825776346</v>
-      </c>
-      <c r="DS13" s="6">
-        <f t="shared" si="40"/>
-        <v>927.73165575185828</v>
-      </c>
-      <c r="DT13" s="6">
-        <f t="shared" si="40"/>
-        <v>918.4543391943397</v>
-      </c>
-      <c r="DU13" s="6">
-        <f t="shared" si="40"/>
-        <v>909.26979580239629</v>
-      </c>
-      <c r="DV13" s="6">
-        <f t="shared" si="40"/>
-        <v>900.17709784437227</v>
-      </c>
-      <c r="DW13" s="6">
-        <f t="shared" si="40"/>
-        <v>891.17532686592858</v>
-      </c>
-      <c r="DX13" s="6">
-        <f t="shared" si="40"/>
-        <v>882.26357359726933</v>
-      </c>
-      <c r="DY13" s="6">
-        <f t="shared" si="40"/>
-        <v>873.44093786129667</v>
-      </c>
-      <c r="DZ13" s="6">
-        <f t="shared" si="40"/>
-        <v>864.70652848268367</v>
-      </c>
-      <c r="EA13" s="6">
-        <f t="shared" si="40"/>
-        <v>856.05946319785687</v>
-      </c>
-      <c r="EB13" s="6">
-        <f t="shared" si="40"/>
-        <v>847.4988685658783</v>
-      </c>
-      <c r="EC13" s="6">
-        <f t="shared" si="40"/>
-        <v>839.02387988021951</v>
-      </c>
-      <c r="ED13" s="6">
-        <f t="shared" si="40"/>
-        <v>830.6336410814173</v>
-      </c>
-      <c r="EE13" s="6">
-        <f t="shared" si="40"/>
-        <v>822.3273046706031</v>
-      </c>
-      <c r="EF13" s="6">
-        <f t="shared" si="40"/>
-        <v>814.10403162389707</v>
-      </c>
-      <c r="EG13" s="6">
-        <f t="shared" si="40"/>
-        <v>805.96299130765806</v>
-      </c>
-      <c r="EH13" s="6">
-        <f t="shared" si="40"/>
-        <v>797.90336139458145</v>
-      </c>
-      <c r="EI13" s="6">
-        <f t="shared" si="40"/>
-        <v>789.92432778063562</v>
-      </c>
-      <c r="EJ13" s="6">
-        <f t="shared" si="40"/>
-        <v>782.02508450282926</v>
-      </c>
-      <c r="EK13" s="6">
-        <f t="shared" si="40"/>
-        <v>774.20483365780092</v>
-      </c>
-      <c r="EL13" s="6">
-        <f t="shared" si="40"/>
-        <v>766.4627853212229</v>
-      </c>
-      <c r="EM13" s="6">
-        <f t="shared" si="40"/>
-        <v>758.79815746801069</v>
+        <v>931.1734595752248</v>
       </c>
     </row>
     <row r="14" spans="1:143" x14ac:dyDescent="0.3">
@@ -2529,12 +2525,12 @@
         <v>185.4</v>
       </c>
       <c r="Q14" s="2">
-        <f>185.4</f>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="R14" s="2">
-        <f>185.4</f>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="T14" s="2">
         <v>164</v>
@@ -2546,48 +2542,48 @@
         <v>164</v>
       </c>
       <c r="W14" s="2">
-        <f t="shared" ref="W14:AG14" si="41">185.4</f>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="X14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="Y14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="Z14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="AA14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="AB14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="AD14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="AE14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="AF14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
       <c r="AG14" s="2">
-        <f t="shared" si="41"/>
-        <v>185.4</v>
+        <f>188</f>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:143" x14ac:dyDescent="0.3">
@@ -2599,15 +2595,15 @@
         <v>-1.0499139414802068</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" ref="H15" si="42">H13/H14</f>
+        <f t="shared" ref="H15" si="40">H13/H14</f>
         <v>-0.70085470085470147</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" ref="I15" si="43">I13/I14</f>
+        <f t="shared" ref="I15" si="41">I13/I14</f>
         <v>-0.12563667232597614</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" ref="J15" si="44">J13/J14</f>
+        <f t="shared" ref="J15" si="42">J13/J14</f>
         <v>0.30655737704918024</v>
       </c>
       <c r="K15" s="5">
@@ -2615,32 +2611,32 @@
         <v>-8.1908831908831914</v>
       </c>
       <c r="L15" s="5">
-        <f t="shared" ref="L15:N15" si="45">L13/L14</f>
+        <f t="shared" ref="L15:N15" si="43">L13/L14</f>
         <v>-6.2043795620438102E-2</v>
       </c>
       <c r="M15" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0.1767139479905436</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0.39303482587064642</v>
       </c>
       <c r="O15" s="5">
-        <f t="shared" ref="O15:R15" si="46">O13/O14</f>
+        <f t="shared" ref="O15:R15" si="44">O13/O14</f>
         <v>0.14146341463414622</v>
       </c>
       <c r="P15" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0.481121898597627</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="46"/>
-        <v>0.61046386192017288</v>
+        <f t="shared" si="44"/>
+        <v>0.86489361702127632</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="46"/>
-        <v>0.65351132686084146</v>
+        <f t="shared" si="44"/>
+        <v>0.88038829787234063</v>
       </c>
       <c r="T15" s="5">
         <f>T13/T14</f>
@@ -2655,48 +2651,48 @@
         <v>-2.9524390243902445</v>
       </c>
       <c r="W15" s="5">
-        <f t="shared" ref="W15" si="47">W13/W14</f>
-        <v>1.8858737864077693</v>
+        <f t="shared" ref="W15" si="45">W13/W14</f>
+        <v>2.3585797872340439</v>
       </c>
       <c r="X15" s="5">
-        <f t="shared" ref="X15" si="48">X13/X14</f>
-        <v>4.0798580124056087</v>
+        <f t="shared" ref="X15" si="46">X13/X14</f>
+        <v>4.5209076143617031</v>
       </c>
       <c r="Y15" s="5">
-        <f t="shared" ref="Y15" si="49">Y13/Y14</f>
-        <v>6.7232289577400213</v>
+        <f t="shared" ref="Y15" si="47">Y13/Y14</f>
+        <v>7.2753252433244704</v>
       </c>
       <c r="Z15" s="5">
-        <f t="shared" ref="Z15" si="50">Z13/Z14</f>
-        <v>8.5029948554635943</v>
+        <f t="shared" ref="Z15" si="48">Z13/Z14</f>
+        <v>9.1324460536827115</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" ref="AA15" si="51">AA13/AA14</f>
-        <v>9.6756261614136871</v>
+        <f t="shared" ref="AA15" si="49">AA13/AA14</f>
+        <v>10.356914927962396</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" ref="AB15" si="52">AB13/AB14</f>
-        <v>10.435811090220497</v>
+        <f t="shared" ref="AB15" si="50">AB13/AB14</f>
+        <v>11.153873107145078</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" ref="AC15" si="53">AC13/AC14</f>
-        <v>10.924958571867895</v>
+        <f t="shared" ref="AC15" si="51">AC13/AC14</f>
+        <v>11.836656818708519</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" ref="AD15" si="54">AD13/AD14</f>
-        <v>11.26836968448521</v>
+        <f t="shared" ref="AD15" si="52">AD13/AD14</f>
+        <v>12.556888033769603</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" ref="AE15" si="55">AE13/AE14</f>
-        <v>11.622396377590267</v>
+        <f t="shared" ref="AE15" si="53">AE13/AE14</f>
+        <v>13.316529489365459</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" ref="AF15" si="56">AF13/AF14</f>
-        <v>11.98736338353989</v>
+        <f t="shared" ref="AF15" si="54">AF13/AF14</f>
+        <v>14.117644592487444</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" ref="AG15" si="57">AG13/AG14</f>
-        <v>12.363605301960444</v>
+        <f t="shared" ref="AG15" si="55">AG13/AG14</f>
+        <v>14.962402526016836</v>
       </c>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.3">
@@ -2712,32 +2708,32 @@
         <v>0.48442272449602952</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" ref="L17:N17" si="58">L3/H3-1</f>
+        <f t="shared" ref="L17:N17" si="56">L3/H3-1</f>
         <v>0.53661202185792334</v>
       </c>
       <c r="M17" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>0.67903614457831307</v>
       </c>
       <c r="N17" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>0.71216973578863074</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" ref="O17" si="59">O3/K3-1</f>
+        <f t="shared" ref="O17" si="57">O3/K3-1</f>
         <v>0.6148148148148147</v>
       </c>
       <c r="P17" s="8">
-        <f t="shared" ref="P17" si="60">P3/L3-1</f>
+        <f t="shared" ref="P17" si="58">P3/L3-1</f>
         <v>0.77667140825035585</v>
       </c>
       <c r="Q17" s="8">
-        <f t="shared" ref="Q17" si="61">Q3/M3-1</f>
-        <v>0.54994259471871421</v>
+        <f t="shared" ref="Q17" si="59">Q3/M3-1</f>
+        <v>0.67881745120551096</v>
       </c>
       <c r="R17" s="8">
-        <f t="shared" ref="R17" si="62">R3/N3-1</f>
-        <v>0.40285246668225394</v>
+        <f t="shared" ref="R17" si="60">R3/N3-1</f>
+        <v>0.54313771335047933</v>
       </c>
       <c r="T17" s="8"/>
       <c r="U17" s="8">
@@ -2745,52 +2741,52 @@
         <v>0.2059397030148491</v>
       </c>
       <c r="V17" s="8">
-        <f t="shared" ref="V17:AG17" si="63">V3/U3-1</f>
+        <f t="shared" ref="V17:AG17" si="61">V3/U3-1</f>
         <v>0.61728855721393039</v>
       </c>
       <c r="W17" s="8">
-        <f t="shared" si="63"/>
-        <v>0.56271629623932951</v>
+        <f t="shared" si="61"/>
+        <v>0.64338998692609417</v>
       </c>
       <c r="X17" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="Z17" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AA17" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AB17" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AC17" s="8">
-        <f t="shared" si="63"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="61"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="61"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE17" s="8">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="61"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF17" s="8">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="61"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG17" s="8">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="61"/>
+        <v>5.0000000000000044E-2</v>
       </c>
     </row>
     <row r="18" spans="2:36" x14ac:dyDescent="0.3">
@@ -2798,19 +2794,19 @@
         <v>35</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" ref="G18:J18" si="64">G5/G3</f>
+        <f t="shared" ref="G18:J18" si="62">G5/G3</f>
         <v>0.83567501527183863</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.84262295081967209</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.8727710843373494</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.88430744595676536</v>
       </c>
       <c r="K18" s="8">
@@ -2818,31 +2814,31 @@
         <v>0.88641975308641974</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" ref="L18:N18" si="65">L5/L3</f>
+        <f t="shared" ref="L18:N18" si="63">L5/L3</f>
         <v>0.89509246088193462</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.90068886337543042</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.92564881926584053</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" ref="O18:R18" si="66">O5/O3</f>
+        <f t="shared" ref="O18:R18" si="64">O5/O3</f>
         <v>0.90545361875637098</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.90812650120096083</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" si="66"/>
-        <v>0.91</v>
+        <f t="shared" si="64"/>
+        <v>0.91024106684903405</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.92</v>
       </c>
       <c r="T18" s="8">
@@ -2854,52 +2850,52 @@
         <v>0.86194029850746268</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" ref="V18:AG18" si="67">V5/V3</f>
+        <f t="shared" ref="V18:AG18" si="65">V5/V3</f>
         <v>0.90502191801891874</v>
       </c>
       <c r="W18" s="8">
-        <f t="shared" si="67"/>
-        <v>0.91161417322834648</v>
+        <f t="shared" si="65"/>
+        <v>0.91188169778651318</v>
       </c>
       <c r="X18" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
+        <v>0.92000000000000015</v>
+      </c>
+      <c r="Y18" s="8">
+        <f t="shared" si="65"/>
         <v>0.92</v>
       </c>
-      <c r="Y18" s="8">
-        <f t="shared" si="67"/>
+      <c r="Z18" s="8">
+        <f t="shared" si="65"/>
+        <v>0.91999999999999993</v>
+      </c>
+      <c r="AA18" s="8">
+        <f t="shared" si="65"/>
         <v>0.92</v>
       </c>
-      <c r="Z18" s="8">
-        <f t="shared" si="67"/>
+      <c r="AB18" s="8">
+        <f t="shared" si="65"/>
         <v>0.92</v>
       </c>
-      <c r="AA18" s="8">
-        <f t="shared" si="67"/>
+      <c r="AC18" s="8">
+        <f t="shared" si="65"/>
+        <v>0.92000000000000015</v>
+      </c>
+      <c r="AD18" s="8">
+        <f t="shared" si="65"/>
+        <v>0.92000000000000015</v>
+      </c>
+      <c r="AE18" s="8">
+        <f t="shared" si="65"/>
+        <v>0.92000000000000015</v>
+      </c>
+      <c r="AF18" s="8">
+        <f t="shared" si="65"/>
         <v>0.92</v>
       </c>
-      <c r="AB18" s="8">
-        <f t="shared" si="67"/>
+      <c r="AG18" s="8">
+        <f t="shared" si="65"/>
         <v>0.91999999999999993</v>
-      </c>
-      <c r="AC18" s="8">
-        <f t="shared" si="67"/>
-        <v>0.92</v>
-      </c>
-      <c r="AD18" s="8">
-        <f t="shared" si="67"/>
-        <v>0.92</v>
-      </c>
-      <c r="AE18" s="8">
-        <f t="shared" si="67"/>
-        <v>0.91999999999999993</v>
-      </c>
-      <c r="AF18" s="8">
-        <f t="shared" si="67"/>
-        <v>0.92</v>
-      </c>
-      <c r="AG18" s="8">
-        <f t="shared" si="67"/>
-        <v>0.92</v>
       </c>
       <c r="AI18" t="s">
         <v>41</v>
@@ -2921,31 +2917,31 @@
         <v>3.0165441176470589</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" ref="L19:N19" si="68">L6/H6-1</f>
+        <f t="shared" ref="L19:N19" si="66">L6/H6-1</f>
         <v>0.30173199635369197</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0.53924284395198518</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0.68996415770609332</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" ref="O19" si="69">O6/K6-1</f>
+        <f t="shared" ref="O19" si="67">O6/K6-1</f>
         <v>-0.56224256292906172</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" ref="P19" si="70">P6/L6-1</f>
+        <f t="shared" ref="P19" si="68">P6/L6-1</f>
         <v>0.37675070028011182</v>
       </c>
       <c r="Q19" s="8">
-        <f t="shared" ref="Q19" si="71">Q6/M6-1</f>
-        <v>0.19999999999999996</v>
+        <f t="shared" ref="Q19" si="69">Q6/M6-1</f>
+        <v>0.17816436712657491</v>
       </c>
       <c r="R19" s="8">
-        <f t="shared" ref="R19" si="72">R6/N6-1</f>
+        <f t="shared" ref="R19" si="70">R6/N6-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="T19" s="8"/>
@@ -2954,51 +2950,51 @@
         <v>0.20016429353778764</v>
       </c>
       <c r="V19" s="8">
-        <f t="shared" ref="V19:AG19" si="73">V6/U6-1</f>
+        <f t="shared" ref="V19:AG19" si="71">V6/U6-1</f>
         <v>1.1334702258726899</v>
       </c>
       <c r="W19" s="8">
-        <f t="shared" si="73"/>
-        <v>-0.12922682066089186</v>
+        <f t="shared" si="71"/>
+        <v>-0.13311945246497714</v>
       </c>
       <c r="X19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Y19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Z19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AA19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG19" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI19" t="s">
@@ -3013,19 +3009,19 @@
         <v>37</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" ref="G20:J20" si="74">G7/G3</f>
+        <f t="shared" ref="G20:J20" si="72">G7/G3</f>
         <v>0.3536957849725107</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>0.32349726775956283</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>0.26554216867469882</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>0.23178542834267413</v>
       </c>
       <c r="K20" s="8">
@@ -3033,31 +3029,31 @@
         <v>0.51069958847736618</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" ref="L20:N20" si="75">L7/L3</f>
+        <f t="shared" ref="L20:N20" si="73">L7/L3</f>
         <v>0.25426742532005692</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>0.21383467278989668</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>0.18821603927986907</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" ref="O20:R20" si="76">O7/O3</f>
+        <f t="shared" ref="O20:R20" si="74">O7/O3</f>
         <v>0.2311416921508665</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>0.24139311449159326</v>
       </c>
       <c r="Q20" s="8">
-        <f t="shared" si="76"/>
-        <v>0.24</v>
+        <f t="shared" si="74"/>
+        <v>0.22003761326722515</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>0.23</v>
       </c>
       <c r="T20" s="8">
@@ -3069,51 +3065,51 @@
         <v>0.28631840796019897</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" ref="V20:AG20" si="77">V7/V3</f>
+        <f t="shared" ref="V20:AG20" si="75">V7/V3</f>
         <v>0.26963008536491584</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" si="77"/>
-        <v>0.23567913385826769</v>
+        <f t="shared" si="75"/>
+        <v>0.2301464738640086</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" si="77"/>
-        <v>0.23</v>
+        <f t="shared" si="75"/>
+        <v>0.23000000000000004</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.22</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.21</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.2</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.2</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.2</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.2</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.2</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" si="77"/>
-        <v>0.2</v>
+        <f t="shared" si="75"/>
+        <v>0.20000000000000004</v>
       </c>
       <c r="AG20" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.2</v>
       </c>
       <c r="AI20" t="s">
@@ -3121,7 +3117,7 @@
       </c>
       <c r="AJ20" s="2">
         <f>NPV(AJ19,W13:EM13)</f>
-        <v>21774.856271998346</v>
+        <v>25665.261872429706</v>
       </c>
     </row>
     <row r="21" spans="2:36" x14ac:dyDescent="0.3">
@@ -3133,36 +3129,36 @@
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8">
-        <f t="shared" ref="K21" si="78">K8/G8-1</f>
+        <f t="shared" ref="K21" si="76">K8/G8-1</f>
         <v>4.9681372549019613</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" ref="L21" si="79">L8/H8-1</f>
+        <f t="shared" ref="L21" si="77">L8/H8-1</f>
         <v>0.79319371727748678</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" ref="M21" si="80">M8/I8-1</f>
+        <f t="shared" ref="M21" si="78">M8/I8-1</f>
         <v>0.76139410187667589</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" ref="N21" si="81">N8/J8-1</f>
+        <f t="shared" ref="N21" si="79">N8/J8-1</f>
         <v>0.52795031055900621</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" ref="O21" si="82">O8/K8-1</f>
+        <f t="shared" ref="O21" si="80">O8/K8-1</f>
         <v>-0.71498973305954827</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21" si="83">P8/L8-1</f>
+        <f t="shared" ref="P21" si="81">P8/L8-1</f>
         <v>4.3795620437956373E-3</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" ref="Q21" si="84">Q8/M8-1</f>
+        <f t="shared" ref="Q21" si="82">Q8/M8-1</f>
+        <v>4.7184170471841647E-2</v>
+      </c>
+      <c r="R21" s="8">
+        <f t="shared" ref="R21" si="83">R8/N8-1</f>
         <v>0.10000000000000009</v>
-      </c>
-      <c r="R21" s="8">
-        <f t="shared" ref="R21" si="85">R8/N8-1</f>
-        <v>0.1399999999999999</v>
       </c>
       <c r="T21" s="8"/>
       <c r="U21" s="8">
@@ -3170,51 +3166,51 @@
         <v>0.14534075104311528</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" ref="V21:AG21" si="86">V8/U8-1</f>
+        <f t="shared" ref="V21:AG21" si="84">V8/U8-1</f>
         <v>1.7413479052823315</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" si="86"/>
-        <v>-0.34750387596899235</v>
+        <f t="shared" si="84"/>
+        <v>-0.36172757475083051</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI21" t="s">
@@ -3230,19 +3226,19 @@
         <v>39</v>
       </c>
       <c r="G22" s="8">
-        <f t="shared" ref="G22:J22" si="87">G9/G3</f>
+        <f t="shared" ref="G22:J22" si="85">G9/G3</f>
         <v>-0.43188759926695186</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>-0.28907103825136632</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>-9.4457831325301181E-2</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>1.2409927942353859E-2</v>
       </c>
       <c r="K22" s="8">
@@ -3250,32 +3246,32 @@
         <v>-2.4246913580246914</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" ref="L22:N22" si="88">L9/L3</f>
+        <f t="shared" ref="L22:N22" si="86">L9/L3</f>
         <v>-0.11059743954480805</v>
       </c>
       <c r="M22" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>1.9804822043627948E-2</v>
       </c>
       <c r="N22" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>0.12391863455693231</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" ref="O22:R22" si="89">O9/O3</f>
+        <f t="shared" ref="O22:R22" si="87">O9/O3</f>
         <v>9.9388379204892394E-3</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>0.13550840672538039</v>
       </c>
       <c r="Q22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.16572222222222235</v>
+        <f t="shared" si="87"/>
+        <v>0.23679261412207206</v>
       </c>
       <c r="R22" s="8">
-        <f t="shared" si="89"/>
-        <v>0.17258000000000001</v>
+        <f t="shared" si="87"/>
+        <v>0.22409090909090915</v>
       </c>
       <c r="T22" s="8">
         <f>T9/T3</f>
@@ -3286,59 +3282,59 @@
         <v>-0.17437810945273638</v>
       </c>
       <c r="V22" s="8">
-        <f t="shared" ref="V22:AG22" si="90">V9/V3</f>
+        <f t="shared" ref="V22:AG22" si="88">V9/V3</f>
         <v>-0.43097746673844506</v>
       </c>
       <c r="W22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.13023523622047262</v>
+        <f t="shared" si="88"/>
+        <v>0.16753240675745248</v>
       </c>
       <c r="X22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.2827963090551181</v>
+        <f t="shared" si="88"/>
+        <v>0.30627444295140499</v>
       </c>
       <c r="Y22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.37274570828285886</v>
+        <f t="shared" si="88"/>
+        <v>0.39159424430686551</v>
       </c>
       <c r="Z22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.41478317402825704</v>
+        <f t="shared" si="88"/>
+        <v>0.43177749822097405</v>
       </c>
       <c r="AA22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.43915147871203086</v>
+        <f t="shared" si="88"/>
+        <v>0.45531009563926994</v>
       </c>
       <c r="AB22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.44777443329345673</v>
+        <f t="shared" si="88"/>
+        <v>0.46342864440460202</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.45105342889316247</v>
+        <f t="shared" si="88"/>
+        <v>0.46892511932846648</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.45170844919913783</v>
+        <f t="shared" si="88"/>
+        <v>0.47429948802090632</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.45235711008466684</v>
+        <f t="shared" si="88"/>
+        <v>0.47955457378550009</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.45299947329169565</v>
+        <f t="shared" si="88"/>
+        <v>0.48469313193517</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="90"/>
-        <v>0.45363559996273389</v>
+        <f t="shared" si="88"/>
+        <v>0.48971785149333952</v>
       </c>
       <c r="AI22" t="s">
         <v>44</v>
       </c>
       <c r="AJ22" s="2">
         <f>AJ20+AJ21</f>
-        <v>23834.856271998346</v>
+        <v>27725.261872429706</v>
       </c>
     </row>
     <row r="23" spans="2:36" x14ac:dyDescent="0.3">
@@ -3346,19 +3342,19 @@
         <v>19</v>
       </c>
       <c r="G23" s="8">
-        <f t="shared" ref="G23:J23" si="91">G12/G11</f>
+        <f t="shared" ref="G23:J23" si="89">G12/G11</f>
         <v>-1.6666666666666663E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>-3.5353535353535318E-2</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>-5.714285714285719E-2</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>4.5918367346938792E-2</v>
       </c>
       <c r="K23" s="8">
@@ -3366,31 +3362,31 @@
         <v>-6.9613644274277764E-4</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" ref="L23:N23" si="92">L12/L11</f>
+        <f t="shared" ref="L23:N23" si="90">L12/L11</f>
         <v>1.923076923076919E-2</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="N23" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-1.4265335235378044E-2</v>
       </c>
       <c r="O23" s="8">
-        <f t="shared" ref="O23:R23" si="93">O12/O11</f>
+        <f t="shared" ref="O23:R23" si="91">O12/O11</f>
         <v>-6.9672131147541047E-2</v>
       </c>
       <c r="P23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>-4.5045045045045027E-3</v>
       </c>
       <c r="Q23" s="8">
-        <f t="shared" si="93"/>
-        <v>0</v>
+        <f t="shared" si="91"/>
+        <v>-1.3084112149532716E-2</v>
       </c>
       <c r="R23" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="T23" s="8">
@@ -3402,51 +3398,51 @@
         <v>-4.362801377726748E-2</v>
       </c>
       <c r="V23" s="8">
-        <f t="shared" ref="V23:AG23" si="94">V12/V11</f>
+        <f t="shared" ref="V23:AG23" si="92">V12/V11</f>
         <v>1.6494845360824739E-3</v>
       </c>
       <c r="W23" s="8">
-        <f t="shared" si="94"/>
-        <v>-6.0424525451673265E-3</v>
+        <f t="shared" si="92"/>
+        <v>-9.5625584852907317E-3</v>
       </c>
       <c r="X23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="Y23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="Z23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="AA23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="AB23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="AC23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="AD23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="AE23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="AF23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="AG23" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
       <c r="AI23" t="s">
@@ -3454,7 +3450,7 @@
       </c>
       <c r="AJ23" s="1">
         <f>AJ22/AG14</f>
-        <v>128.55909531822192</v>
+        <v>147.47479719377503</v>
       </c>
     </row>
     <row r="24" spans="2:36" x14ac:dyDescent="0.3">
@@ -3462,19 +3458,19 @@
         <v>40</v>
       </c>
       <c r="G24" s="8">
-        <f t="shared" ref="G24:J24" si="95">G13/G3</f>
+        <f t="shared" ref="G24:J24" si="93">G13/G3</f>
         <v>-0.37263286499694576</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>-0.22404371584699473</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>-3.5662650602409612E-2</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>7.4859887910328243E-2</v>
       </c>
       <c r="K24" s="8">
@@ -3482,32 +3478,32 @@
         <v>-2.3662551440329218</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" ref="L24:N24" si="96">L13/L3</f>
+        <f t="shared" ref="L24:N24" si="94">L13/L3</f>
         <v>-3.627311522048373E-2</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>8.5820895522388002E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.16623801730184695</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" ref="O24:R24" si="97">O13/O3</f>
+        <f t="shared" ref="O24:R24" si="95">O13/O3</f>
         <v>6.6513761467889856E-2</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>0.17854283426741402</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.20959259259259272</v>
+        <f t="shared" si="95"/>
+        <v>0.27799623867327738</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" si="97"/>
-        <v>0.201935</v>
+        <f t="shared" si="95"/>
+        <v>0.25077727272727279</v>
       </c>
       <c r="T24" s="8">
         <f>T13/T3</f>
@@ -3518,59 +3514,59 @@
         <v>-0.11305970149253737</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" ref="V24:AG24" si="98">V13/V3</f>
+        <f t="shared" ref="V24:AG24" si="96">V13/V3</f>
         <v>-0.3723756056294702</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.17206742125984273</v>
+        <f t="shared" si="96"/>
+        <v>0.2075029247976041</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.26589063396372326</v>
+        <f t="shared" si="96"/>
+        <v>0.28410000852369599</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.33704860927495239</v>
+        <f t="shared" si="96"/>
+        <v>0.35168567225733705</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.37067108918624292</v>
+        <f t="shared" si="96"/>
+        <v>0.38387650960469438</v>
       </c>
       <c r="AA24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.39054593560901429</v>
+        <f t="shared" si="96"/>
+        <v>0.40309840092335397</v>
       </c>
       <c r="AB24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.39738675326632661</v>
+        <f t="shared" si="96"/>
+        <v>0.40954393662964161</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.4000125679398564</v>
+        <f t="shared" si="96"/>
+        <v>0.41391823385996018</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.40056933519993548</v>
+        <f t="shared" si="96"/>
+        <v>0.41819441139270996</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.40112069695263508</v>
+        <f t="shared" si="96"/>
+        <v>0.42237476102452054</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.40166670567860957</v>
+        <f t="shared" si="96"/>
+        <v>0.4264615188173238</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="98"/>
-        <v>0.40220741334899218</v>
+        <f t="shared" si="96"/>
+        <v>0.4304568665051503</v>
       </c>
       <c r="AI24" t="s">
         <v>46</v>
       </c>
       <c r="AJ24" s="1">
         <f>Main!D3</f>
-        <v>203.63</v>
+        <v>218.54</v>
       </c>
     </row>
     <row r="25" spans="2:36" x14ac:dyDescent="0.3">
@@ -3579,7 +3575,7 @@
       </c>
       <c r="AJ25" s="9">
         <f>AJ23/AJ24-1</f>
-        <v>-0.36866328478995269</v>
+        <v>-0.32518167294877354</v>
       </c>
     </row>
     <row r="26" spans="2:36" x14ac:dyDescent="0.3">
@@ -3607,48 +3603,48 @@
         <v>-484.2000000000001</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" ref="W27:AG27" si="99">W13</f>
-        <v>349.64100000000042</v>
+        <f t="shared" ref="W27:AG27" si="97">W13</f>
+        <v>443.41300000000024</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="99"/>
-        <v>756.40567549999992</v>
+        <f t="shared" si="97"/>
+        <v>849.93063150000023</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="99"/>
-        <v>1246.4866487649999</v>
+        <f t="shared" si="97"/>
+        <v>1367.7611457450005</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="99"/>
-        <v>1576.4552462029505</v>
+        <f t="shared" si="97"/>
+        <v>1716.8998580923499</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" si="99"/>
-        <v>1793.8610903260976</v>
+        <f t="shared" si="97"/>
+        <v>1947.1000064569305</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="99"/>
-        <v>1934.7993761268801</v>
+        <f t="shared" si="97"/>
+        <v>2096.9281441432745</v>
       </c>
       <c r="AC27" s="7">
-        <f t="shared" si="99"/>
-        <v>2025.4873192243078</v>
+        <f t="shared" si="97"/>
+        <v>2225.2914819172015</v>
       </c>
       <c r="AD27" s="7">
-        <f t="shared" si="99"/>
-        <v>2089.1557395035579</v>
+        <f t="shared" si="97"/>
+        <v>2360.6949503486853</v>
       </c>
       <c r="AE27" s="7">
-        <f t="shared" si="99"/>
-        <v>2154.7922884052355</v>
+        <f t="shared" si="97"/>
+        <v>2503.5075440007063</v>
       </c>
       <c r="AF27" s="7">
-        <f t="shared" si="99"/>
-        <v>2222.4571713082955</v>
+        <f t="shared" si="97"/>
+        <v>2654.1171833876397</v>
       </c>
       <c r="AG27" s="7">
-        <f t="shared" si="99"/>
-        <v>2292.2124229834662</v>
+        <f t="shared" si="97"/>
+        <v>2812.9316748911651</v>
       </c>
     </row>
     <row r="28" spans="2:36" x14ac:dyDescent="0.3">
@@ -3669,15 +3665,15 @@
         <v>18.72</v>
       </c>
       <c r="X28">
-        <f t="shared" ref="X28:Z28" si="100">W28*1.2</f>
+        <f t="shared" ref="X28:Z28" si="98">W28*1.2</f>
         <v>22.463999999999999</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>26.956799999999998</v>
       </c>
       <c r="Z28">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>32.348159999999993</v>
       </c>
       <c r="AA28">
@@ -3685,27 +3681,27 @@
         <v>33.965567999999998</v>
       </c>
       <c r="AB28">
-        <f t="shared" ref="AB28:AG28" si="101">AA28*1.05</f>
+        <f t="shared" ref="AB28:AG28" si="99">AA28*1.05</f>
         <v>35.663846399999997</v>
       </c>
       <c r="AC28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>37.447038720000002</v>
       </c>
       <c r="AD28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>39.319390656000003</v>
       </c>
       <c r="AE28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>41.285360188800006</v>
       </c>
       <c r="AF28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>43.349628198240005</v>
       </c>
       <c r="AG28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>45.517109608152005</v>
       </c>
     </row>
@@ -3821,44 +3817,44 @@
         <v>320.64000000000004</v>
       </c>
       <c r="X31">
-        <f>W31*0.7</f>
-        <v>224.44800000000001</v>
+        <f>W31*0.8</f>
+        <v>256.51200000000006</v>
       </c>
       <c r="Y31">
-        <f t="shared" ref="Y31" si="102">X31*0.7</f>
-        <v>157.11359999999999</v>
+        <f>X31*0.8</f>
+        <v>205.20960000000005</v>
       </c>
       <c r="Z31">
         <f>Y31*0.95</f>
-        <v>149.25791999999998</v>
+        <v>194.94912000000005</v>
       </c>
       <c r="AA31">
-        <f t="shared" ref="AA31:AG31" si="103">Z31*0.95</f>
-        <v>141.79502399999998</v>
+        <f>Z31*1.03</f>
+        <v>200.79759360000006</v>
       </c>
       <c r="AB31">
-        <f t="shared" si="103"/>
-        <v>134.70527279999999</v>
+        <f t="shared" ref="AB31:AG31" si="100">AA31*1.03</f>
+        <v>206.82152140800005</v>
       </c>
       <c r="AC31">
-        <f t="shared" si="103"/>
-        <v>127.97000915999999</v>
+        <f t="shared" si="100"/>
+        <v>213.02616705024005</v>
       </c>
       <c r="AD31">
-        <f t="shared" si="103"/>
-        <v>121.57150870199999</v>
+        <f t="shared" si="100"/>
+        <v>219.41695206174725</v>
       </c>
       <c r="AE31">
-        <f t="shared" si="103"/>
-        <v>115.49293326689998</v>
+        <f t="shared" si="100"/>
+        <v>225.99946062359967</v>
       </c>
       <c r="AF31">
-        <f t="shared" si="103"/>
-        <v>109.71828660355497</v>
+        <f t="shared" si="100"/>
+        <v>232.77944444230766</v>
       </c>
       <c r="AG31">
-        <f t="shared" si="103"/>
-        <v>104.23237227337722</v>
+        <f t="shared" si="100"/>
+        <v>239.76282777557691</v>
       </c>
     </row>
     <row r="32" spans="2:36" x14ac:dyDescent="0.3">
@@ -4160,48 +4156,48 @@
         <v>221.99999999999983</v>
       </c>
       <c r="W38" s="7">
-        <f t="shared" ref="W38" si="104">W27+SUM(W28:W37)</f>
-        <v>699.00100000000043</v>
+        <f t="shared" ref="W38" si="101">W27+SUM(W28:W37)</f>
+        <v>792.77300000000025</v>
       </c>
       <c r="X38" s="7">
-        <f t="shared" ref="X38" si="105">X27+SUM(X28:X37)</f>
-        <v>1013.3176755</v>
+        <f t="shared" ref="X38" si="102">X27+SUM(X28:X37)</f>
+        <v>1138.9066315000002</v>
       </c>
       <c r="Y38" s="7">
-        <f t="shared" ref="Y38" si="106">Y27+SUM(Y28:Y37)</f>
-        <v>1440.557048765</v>
+        <f t="shared" ref="Y38" si="103">Y27+SUM(Y28:Y37)</f>
+        <v>1609.9275457450005</v>
       </c>
       <c r="Z38" s="7">
-        <f t="shared" ref="Z38" si="107">Z27+SUM(Z28:Z37)</f>
-        <v>1768.0613262029506</v>
+        <f t="shared" ref="Z38" si="104">Z27+SUM(Z28:Z37)</f>
+        <v>1954.1971380923499</v>
       </c>
       <c r="AA38" s="7">
-        <f t="shared" ref="AA38" si="108">AA27+SUM(AA28:AA37)</f>
-        <v>1979.6216823260975</v>
+        <f t="shared" ref="AA38" si="105">AA27+SUM(AA28:AA37)</f>
+        <v>2191.8631680569306</v>
       </c>
       <c r="AB38" s="7">
-        <f t="shared" ref="AB38" si="109">AB27+SUM(AB28:AB37)</f>
-        <v>2115.16849532688</v>
+        <f t="shared" ref="AB38" si="106">AB27+SUM(AB28:AB37)</f>
+        <v>2349.4135119512744</v>
       </c>
       <c r="AC38" s="7">
-        <f t="shared" ref="AC38" si="110">AC27+SUM(AC28:AC37)</f>
-        <v>2200.9043671043078</v>
+        <f t="shared" ref="AC38" si="107">AC27+SUM(AC28:AC37)</f>
+        <v>2485.7646876874414</v>
       </c>
       <c r="AD38" s="7">
-        <f t="shared" ref="AD38" si="111">AD27+SUM(AD28:AD37)</f>
-        <v>2260.0466388615578</v>
+        <f t="shared" ref="AD38" si="108">AD27+SUM(AD28:AD37)</f>
+        <v>2629.4312930664328</v>
       </c>
       <c r="AE38" s="7">
-        <f t="shared" ref="AE38" si="112">AE27+SUM(AE28:AE37)</f>
-        <v>2321.5705818609354</v>
+        <f t="shared" ref="AE38" si="109">AE27+SUM(AE28:AE37)</f>
+        <v>2780.7923648131059</v>
       </c>
       <c r="AF38" s="7">
-        <f t="shared" ref="AF38" si="113">AF27+SUM(AF28:AF37)</f>
-        <v>2385.5250861100903</v>
+        <f t="shared" ref="AF38" si="110">AF27+SUM(AF28:AF37)</f>
+        <v>2940.2462560281874</v>
       </c>
       <c r="AG38" s="7">
-        <f t="shared" ref="AG38" si="114">AG27+SUM(AG28:AG37)</f>
-        <v>2451.9619048649956</v>
+        <f t="shared" ref="AG38" si="111">AG27+SUM(AG28:AG37)</f>
+        <v>3108.2116122748939</v>
       </c>
     </row>
     <row r="39" spans="2:144" x14ac:dyDescent="0.3">
@@ -4268,498 +4264,498 @@
         <v>215.79999999999984</v>
       </c>
       <c r="W40" s="7">
-        <f t="shared" ref="W40" si="115">W38-W39</f>
-        <v>692.80100000000039</v>
+        <f t="shared" ref="W40" si="112">W38-W39</f>
+        <v>786.57300000000021</v>
       </c>
       <c r="X40" s="7">
-        <f t="shared" ref="X40" si="116">X38-X39</f>
-        <v>1007.1176754999999</v>
+        <f t="shared" ref="X40" si="113">X38-X39</f>
+        <v>1132.7066315000002</v>
       </c>
       <c r="Y40" s="7">
-        <f t="shared" ref="Y40" si="117">Y38-Y39</f>
-        <v>1434.3570487649999</v>
+        <f t="shared" ref="Y40" si="114">Y38-Y39</f>
+        <v>1603.7275457450005</v>
       </c>
       <c r="Z40" s="7">
-        <f t="shared" ref="Z40" si="118">Z38-Z39</f>
-        <v>1761.8613262029505</v>
+        <f t="shared" ref="Z40" si="115">Z38-Z39</f>
+        <v>1947.9971380923498</v>
       </c>
       <c r="AA40" s="7">
-        <f t="shared" ref="AA40" si="119">AA38-AA39</f>
-        <v>1973.4216823260974</v>
+        <f t="shared" ref="AA40" si="116">AA38-AA39</f>
+        <v>2185.6631680569308</v>
       </c>
       <c r="AB40" s="7">
-        <f t="shared" ref="AB40" si="120">AB38-AB39</f>
-        <v>2108.9684953268802</v>
+        <f t="shared" ref="AB40" si="117">AB38-AB39</f>
+        <v>2343.2135119512745</v>
       </c>
       <c r="AC40" s="7">
-        <f t="shared" ref="AC40" si="121">AC38-AC39</f>
-        <v>2194.7043671043079</v>
+        <f t="shared" ref="AC40" si="118">AC38-AC39</f>
+        <v>2479.5646876874416</v>
       </c>
       <c r="AD40" s="7">
-        <f t="shared" ref="AD40" si="122">AD38-AD39</f>
-        <v>2253.8466388615579</v>
+        <f t="shared" ref="AD40" si="119">AD38-AD39</f>
+        <v>2623.231293066433</v>
       </c>
       <c r="AE40" s="7">
-        <f t="shared" ref="AE40" si="123">AE38-AE39</f>
-        <v>2315.3705818609355</v>
+        <f t="shared" ref="AE40" si="120">AE38-AE39</f>
+        <v>2774.5923648131061</v>
       </c>
       <c r="AF40" s="7">
-        <f t="shared" ref="AF40" si="124">AF38-AF39</f>
-        <v>2379.3250861100905</v>
+        <f t="shared" ref="AF40" si="121">AF38-AF39</f>
+        <v>2934.0462560281876</v>
       </c>
       <c r="AG40" s="7">
-        <f t="shared" ref="AG40" si="125">AG38-AG39</f>
-        <v>2445.7619048649958</v>
+        <f t="shared" ref="AG40" si="122">AG38-AG39</f>
+        <v>3102.0116122748941</v>
       </c>
       <c r="AH40" s="6">
         <f>AG40*(1+$AJ$18)</f>
-        <v>2421.3042858163458</v>
+        <v>3070.9914961521449</v>
       </c>
       <c r="AI40" s="6">
-        <f t="shared" ref="AI40:CT40" si="126">AH40*(1+$AJ$18)</f>
-        <v>2397.0912429581822</v>
+        <f t="shared" ref="AI40:CT40" si="123">AH40*(1+$AJ$18)</f>
+        <v>3040.2815811906235</v>
       </c>
       <c r="AJ40" s="6">
-        <f t="shared" si="126"/>
-        <v>2373.1203305286003</v>
+        <f t="shared" si="123"/>
+        <v>3009.8787653787172</v>
       </c>
       <c r="AK40" s="6">
-        <f t="shared" si="126"/>
-        <v>2349.3891272233145</v>
+        <f t="shared" si="123"/>
+        <v>2979.7799777249302</v>
       </c>
       <c r="AL40" s="6">
-        <f t="shared" si="126"/>
-        <v>2325.8952359510813</v>
+        <f t="shared" si="123"/>
+        <v>2949.9821779476811</v>
       </c>
       <c r="AM40" s="6">
-        <f t="shared" si="126"/>
-        <v>2302.6362835915706</v>
+        <f t="shared" si="123"/>
+        <v>2920.4823561682042</v>
       </c>
       <c r="AN40" s="6">
-        <f t="shared" si="126"/>
-        <v>2279.6099207556549</v>
+        <f t="shared" si="123"/>
+        <v>2891.2775326065221</v>
       </c>
       <c r="AO40" s="6">
-        <f t="shared" si="126"/>
-        <v>2256.8138215480985</v>
+        <f t="shared" si="123"/>
+        <v>2862.3647572804566</v>
       </c>
       <c r="AP40" s="6">
-        <f t="shared" si="126"/>
-        <v>2234.2456833326173</v>
+        <f t="shared" si="123"/>
+        <v>2833.741109707652</v>
       </c>
       <c r="AQ40" s="6">
-        <f t="shared" si="126"/>
-        <v>2211.9032264992911</v>
+        <f t="shared" si="123"/>
+        <v>2805.4036986105752</v>
       </c>
       <c r="AR40" s="6">
-        <f t="shared" si="126"/>
-        <v>2189.7841942342984</v>
+        <f t="shared" si="123"/>
+        <v>2777.3496616244693</v>
       </c>
       <c r="AS40" s="6">
-        <f t="shared" si="126"/>
-        <v>2167.8863522919555</v>
+        <f t="shared" si="123"/>
+        <v>2749.5761650082245</v>
       </c>
       <c r="AT40" s="6">
-        <f t="shared" si="126"/>
-        <v>2146.207488769036</v>
+        <f t="shared" si="123"/>
+        <v>2722.0804033581421</v>
       </c>
       <c r="AU40" s="6">
-        <f t="shared" si="126"/>
-        <v>2124.7454138813455</v>
+        <f t="shared" si="123"/>
+        <v>2694.8595993245608</v>
       </c>
       <c r="AV40" s="6">
-        <f t="shared" si="126"/>
-        <v>2103.4979597425322</v>
+        <f t="shared" si="123"/>
+        <v>2667.911003331315</v>
       </c>
       <c r="AW40" s="6">
-        <f t="shared" si="126"/>
-        <v>2082.4629801451069</v>
+        <f t="shared" si="123"/>
+        <v>2641.231893298002</v>
       </c>
       <c r="AX40" s="6">
-        <f t="shared" si="126"/>
-        <v>2061.6383503436559</v>
+        <f t="shared" si="123"/>
+        <v>2614.8195743650217</v>
       </c>
       <c r="AY40" s="6">
-        <f t="shared" si="126"/>
-        <v>2041.0219668402194</v>
+        <f t="shared" si="123"/>
+        <v>2588.6713786213713</v>
       </c>
       <c r="AZ40" s="6">
-        <f t="shared" si="126"/>
-        <v>2020.6117471718171</v>
+        <f t="shared" si="123"/>
+        <v>2562.7846648351574</v>
       </c>
       <c r="BA40" s="6">
-        <f t="shared" si="126"/>
-        <v>2000.4056297000989</v>
+        <f t="shared" si="123"/>
+        <v>2537.1568181868056</v>
       </c>
       <c r="BB40" s="6">
-        <f t="shared" si="126"/>
-        <v>1980.4015734030979</v>
+        <f t="shared" si="123"/>
+        <v>2511.7852500049376</v>
       </c>
       <c r="BC40" s="6">
-        <f t="shared" si="126"/>
-        <v>1960.5975576690669</v>
+        <f t="shared" si="123"/>
+        <v>2486.667397504888</v>
       </c>
       <c r="BD40" s="6">
-        <f t="shared" si="126"/>
-        <v>1940.9915820923761</v>
+        <f t="shared" si="123"/>
+        <v>2461.8007235298392</v>
       </c>
       <c r="BE40" s="6">
-        <f t="shared" si="126"/>
-        <v>1921.5816662714524</v>
+        <f t="shared" si="123"/>
+        <v>2437.1827162945406</v>
       </c>
       <c r="BF40" s="6">
-        <f t="shared" si="126"/>
-        <v>1902.3658496087378</v>
+        <f t="shared" si="123"/>
+        <v>2412.8108891315951</v>
       </c>
       <c r="BG40" s="6">
-        <f t="shared" si="126"/>
-        <v>1883.3421911126504</v>
+        <f t="shared" si="123"/>
+        <v>2388.682780240279</v>
       </c>
       <c r="BH40" s="6">
-        <f t="shared" si="126"/>
-        <v>1864.5087692015238</v>
+        <f t="shared" si="123"/>
+        <v>2364.7959524378762</v>
       </c>
       <c r="BI40" s="6">
-        <f t="shared" si="126"/>
-        <v>1845.8636815095085</v>
+        <f t="shared" si="123"/>
+        <v>2341.1479929134975</v>
       </c>
       <c r="BJ40" s="6">
-        <f t="shared" si="126"/>
-        <v>1827.4050446944134</v>
+        <f t="shared" si="123"/>
+        <v>2317.7365129843624</v>
       </c>
       <c r="BK40" s="6">
-        <f t="shared" si="126"/>
-        <v>1809.1309942474693</v>
+        <f t="shared" si="123"/>
+        <v>2294.5591478545189</v>
       </c>
       <c r="BL40" s="6">
-        <f t="shared" si="126"/>
-        <v>1791.0396843049946</v>
+        <f t="shared" si="123"/>
+        <v>2271.6135563759735</v>
       </c>
       <c r="BM40" s="6">
-        <f t="shared" si="126"/>
-        <v>1773.1292874619446</v>
+        <f t="shared" si="123"/>
+        <v>2248.8974208122136</v>
       </c>
       <c r="BN40" s="6">
-        <f t="shared" si="126"/>
-        <v>1755.3979945873252</v>
+        <f t="shared" si="123"/>
+        <v>2226.4084466040913</v>
       </c>
       <c r="BO40" s="6">
-        <f t="shared" si="126"/>
-        <v>1737.8440146414518</v>
+        <f t="shared" si="123"/>
+        <v>2204.1443621380504</v>
       </c>
       <c r="BP40" s="6">
-        <f t="shared" si="126"/>
-        <v>1720.4655744950373</v>
+        <f t="shared" si="123"/>
+        <v>2182.1029185166699</v>
       </c>
       <c r="BQ40" s="6">
-        <f t="shared" si="126"/>
-        <v>1703.2609187500871</v>
+        <f t="shared" si="123"/>
+        <v>2160.281889331503</v>
       </c>
       <c r="BR40" s="6">
-        <f t="shared" si="126"/>
-        <v>1686.2283095625862</v>
+        <f t="shared" si="123"/>
+        <v>2138.6790704381879</v>
       </c>
       <c r="BS40" s="6">
-        <f t="shared" si="126"/>
-        <v>1669.3660264669604</v>
+        <f t="shared" si="123"/>
+        <v>2117.292279733806</v>
       </c>
       <c r="BT40" s="6">
-        <f t="shared" si="126"/>
-        <v>1652.6723662022907</v>
+        <f t="shared" si="123"/>
+        <v>2096.1193569364677</v>
       </c>
       <c r="BU40" s="6">
-        <f t="shared" si="126"/>
-        <v>1636.1456425402678</v>
+        <f t="shared" si="123"/>
+        <v>2075.158163367103</v>
       </c>
       <c r="BV40" s="6">
-        <f t="shared" si="126"/>
-        <v>1619.7841861148652</v>
+        <f t="shared" si="123"/>
+        <v>2054.4065817334322</v>
       </c>
       <c r="BW40" s="6">
-        <f t="shared" si="126"/>
-        <v>1603.5863442537166</v>
+        <f t="shared" si="123"/>
+        <v>2033.8625159160979</v>
       </c>
       <c r="BX40" s="6">
-        <f t="shared" si="126"/>
-        <v>1587.5504808111793</v>
+        <f t="shared" si="123"/>
+        <v>2013.5238907569369</v>
       </c>
       <c r="BY40" s="6">
-        <f t="shared" si="126"/>
-        <v>1571.6749760030675</v>
+        <f t="shared" si="123"/>
+        <v>1993.3886518493675</v>
       </c>
       <c r="BZ40" s="6">
-        <f t="shared" si="126"/>
-        <v>1555.9582262430367</v>
+        <f t="shared" si="123"/>
+        <v>1973.4547653308739</v>
       </c>
       <c r="CA40" s="6">
-        <f t="shared" si="126"/>
-        <v>1540.3986439806063</v>
+        <f t="shared" si="123"/>
+        <v>1953.7202176775652</v>
       </c>
       <c r="CB40" s="6">
-        <f t="shared" si="126"/>
-        <v>1524.9946575408003</v>
+        <f t="shared" si="123"/>
+        <v>1934.1830155007895</v>
       </c>
       <c r="CC40" s="6">
-        <f t="shared" si="126"/>
-        <v>1509.7447109653922</v>
+        <f t="shared" si="123"/>
+        <v>1914.8411853457815</v>
       </c>
       <c r="CD40" s="6">
-        <f t="shared" si="126"/>
-        <v>1494.6472638557382</v>
+        <f t="shared" si="123"/>
+        <v>1895.6927734923236</v>
       </c>
       <c r="CE40" s="6">
-        <f t="shared" si="126"/>
-        <v>1479.7007912171807</v>
+        <f t="shared" si="123"/>
+        <v>1876.7358457574003</v>
       </c>
       <c r="CF40" s="6">
-        <f t="shared" si="126"/>
-        <v>1464.9037833050088</v>
+        <f t="shared" si="123"/>
+        <v>1857.9684872998262</v>
       </c>
       <c r="CG40" s="6">
-        <f t="shared" si="126"/>
-        <v>1450.2547454719588</v>
+        <f t="shared" si="123"/>
+        <v>1839.3888024268279</v>
       </c>
       <c r="CH40" s="6">
-        <f t="shared" si="126"/>
-        <v>1435.7521980172392</v>
+        <f t="shared" si="123"/>
+        <v>1820.9949144025595</v>
       </c>
       <c r="CI40" s="6">
-        <f t="shared" si="126"/>
-        <v>1421.3946760370668</v>
+        <f t="shared" si="123"/>
+        <v>1802.7849652585339</v>
       </c>
       <c r="CJ40" s="6">
-        <f t="shared" si="126"/>
-        <v>1407.1807292766962</v>
+        <f t="shared" si="123"/>
+        <v>1784.7571156059487</v>
       </c>
       <c r="CK40" s="6">
-        <f t="shared" si="126"/>
-        <v>1393.1089219839291</v>
+        <f t="shared" si="123"/>
+        <v>1766.9095444498892</v>
       </c>
       <c r="CL40" s="6">
-        <f t="shared" si="126"/>
-        <v>1379.1778327640898</v>
+        <f t="shared" si="123"/>
+        <v>1749.2404490053902</v>
       </c>
       <c r="CM40" s="6">
-        <f t="shared" si="126"/>
-        <v>1365.3860544364488</v>
+        <f t="shared" si="123"/>
+        <v>1731.7480445153362</v>
       </c>
       <c r="CN40" s="6">
-        <f t="shared" si="126"/>
-        <v>1351.7321938920843</v>
+        <f t="shared" si="123"/>
+        <v>1714.4305640701828</v>
       </c>
       <c r="CO40" s="6">
-        <f t="shared" si="126"/>
-        <v>1338.2148719531635</v>
+        <f t="shared" si="123"/>
+        <v>1697.286258429481</v>
       </c>
       <c r="CP40" s="6">
-        <f t="shared" si="126"/>
-        <v>1324.8327232336319</v>
+        <f t="shared" si="123"/>
+        <v>1680.3133958451863</v>
       </c>
       <c r="CQ40" s="6">
-        <f t="shared" si="126"/>
-        <v>1311.5843960012955</v>
+        <f t="shared" si="123"/>
+        <v>1663.5102618867345</v>
       </c>
       <c r="CR40" s="6">
-        <f t="shared" si="126"/>
-        <v>1298.4685520412825</v>
+        <f t="shared" si="123"/>
+        <v>1646.875159267867</v>
       </c>
       <c r="CS40" s="6">
-        <f t="shared" si="126"/>
-        <v>1285.4838665208697</v>
+        <f t="shared" si="123"/>
+        <v>1630.4064076751883</v>
       </c>
       <c r="CT40" s="6">
-        <f t="shared" si="126"/>
-        <v>1272.629027855661</v>
+        <f t="shared" si="123"/>
+        <v>1614.1023435984364</v>
       </c>
       <c r="CU40" s="6">
-        <f t="shared" ref="CU40:EN40" si="127">CT40*(1+$AJ$18)</f>
-        <v>1259.9027375771043</v>
+        <f t="shared" ref="CU40:EN40" si="124">CT40*(1+$AJ$18)</f>
+        <v>1597.961320162452</v>
       </c>
       <c r="CV40" s="6">
-        <f t="shared" si="127"/>
-        <v>1247.3037102013332</v>
+        <f t="shared" si="124"/>
+        <v>1581.9817069608275</v>
       </c>
       <c r="CW40" s="6">
-        <f t="shared" si="127"/>
-        <v>1234.8306730993197</v>
+        <f t="shared" si="124"/>
+        <v>1566.1618898912193</v>
       </c>
       <c r="CX40" s="6">
-        <f t="shared" si="127"/>
-        <v>1222.4823663683264</v>
+        <f t="shared" si="124"/>
+        <v>1550.5002709923072</v>
       </c>
       <c r="CY40" s="6">
-        <f t="shared" si="127"/>
-        <v>1210.2575427046431</v>
+        <f t="shared" si="124"/>
+        <v>1534.9952682823841</v>
       </c>
       <c r="CZ40" s="6">
-        <f t="shared" si="127"/>
-        <v>1198.1549672775966</v>
+        <f t="shared" si="124"/>
+        <v>1519.6453155995603</v>
       </c>
       <c r="DA40" s="6">
-        <f t="shared" si="127"/>
-        <v>1186.1734176048205</v>
+        <f t="shared" si="124"/>
+        <v>1504.4488624435646</v>
       </c>
       <c r="DB40" s="6">
-        <f t="shared" si="127"/>
-        <v>1174.3116834287723</v>
+        <f t="shared" si="124"/>
+        <v>1489.404373819129</v>
       </c>
       <c r="DC40" s="6">
-        <f t="shared" si="127"/>
-        <v>1162.5685665944845</v>
+        <f t="shared" si="124"/>
+        <v>1474.5103300809376</v>
       </c>
       <c r="DD40" s="6">
-        <f t="shared" si="127"/>
-        <v>1150.9428809285396</v>
+        <f t="shared" si="124"/>
+        <v>1459.7652267801282</v>
       </c>
       <c r="DE40" s="6">
-        <f t="shared" si="127"/>
-        <v>1139.4334521192541</v>
+        <f t="shared" si="124"/>
+        <v>1445.1675745123268</v>
       </c>
       <c r="DF40" s="6">
-        <f t="shared" si="127"/>
-        <v>1128.0391175980615</v>
+        <f t="shared" si="124"/>
+        <v>1430.7158987672035</v>
       </c>
       <c r="DG40" s="6">
-        <f t="shared" si="127"/>
-        <v>1116.7587264220808</v>
+        <f t="shared" si="124"/>
+        <v>1416.4087397795315</v>
       </c>
       <c r="DH40" s="6">
-        <f t="shared" si="127"/>
-        <v>1105.59113915786</v>
+        <f t="shared" si="124"/>
+        <v>1402.2446523817362</v>
       </c>
       <c r="DI40" s="6">
-        <f t="shared" si="127"/>
-        <v>1094.5352277662814</v>
+        <f t="shared" si="124"/>
+        <v>1388.2222058579189</v>
       </c>
       <c r="DJ40" s="6">
-        <f t="shared" si="127"/>
-        <v>1083.5898754886186</v>
+        <f t="shared" si="124"/>
+        <v>1374.3399837993397</v>
       </c>
       <c r="DK40" s="6">
-        <f t="shared" si="127"/>
-        <v>1072.7539767337325</v>
+        <f t="shared" si="124"/>
+        <v>1360.5965839613464</v>
       </c>
       <c r="DL40" s="6">
-        <f t="shared" si="127"/>
-        <v>1062.0264369663953</v>
+        <f t="shared" si="124"/>
+        <v>1346.990618121733</v>
       </c>
       <c r="DM40" s="6">
-        <f t="shared" si="127"/>
-        <v>1051.4061725967313</v>
+        <f t="shared" si="124"/>
+        <v>1333.5207119405156</v>
       </c>
       <c r="DN40" s="6">
-        <f t="shared" si="127"/>
-        <v>1040.8921108707639</v>
+        <f t="shared" si="124"/>
+        <v>1320.1855048211105</v>
       </c>
       <c r="DO40" s="6">
-        <f t="shared" si="127"/>
-        <v>1030.4831897620563</v>
+        <f t="shared" si="124"/>
+        <v>1306.9836497728993</v>
       </c>
       <c r="DP40" s="6">
-        <f t="shared" si="127"/>
-        <v>1020.1783578644357</v>
+        <f t="shared" si="124"/>
+        <v>1293.9138132751702</v>
       </c>
       <c r="DQ40" s="6">
-        <f t="shared" si="127"/>
-        <v>1009.9765742857913</v>
+        <f t="shared" si="124"/>
+        <v>1280.9746751424186</v>
       </c>
       <c r="DR40" s="6">
-        <f t="shared" si="127"/>
-        <v>999.87680854293342</v>
+        <f t="shared" si="124"/>
+        <v>1268.1649283909944</v>
       </c>
       <c r="DS40" s="6">
-        <f t="shared" si="127"/>
-        <v>989.87804045750408</v>
+        <f t="shared" si="124"/>
+        <v>1255.4832791070844</v>
       </c>
       <c r="DT40" s="6">
-        <f t="shared" si="127"/>
-        <v>979.97926005292902</v>
+        <f t="shared" si="124"/>
+        <v>1242.9284463160136</v>
       </c>
       <c r="DU40" s="6">
-        <f t="shared" si="127"/>
-        <v>970.17946745239976</v>
+        <f t="shared" si="124"/>
+        <v>1230.4991618528534</v>
       </c>
       <c r="DV40" s="6">
-        <f t="shared" si="127"/>
-        <v>960.4776727778758</v>
+        <f t="shared" si="124"/>
+        <v>1218.1941702343249</v>
       </c>
       <c r="DW40" s="6">
-        <f t="shared" si="127"/>
-        <v>950.87289605009698</v>
+        <f t="shared" si="124"/>
+        <v>1206.0122285319817</v>
       </c>
       <c r="DX40" s="6">
-        <f t="shared" si="127"/>
-        <v>941.36416708959598</v>
+        <f t="shared" si="124"/>
+        <v>1193.952106246662</v>
       </c>
       <c r="DY40" s="6">
-        <f t="shared" si="127"/>
-        <v>931.95052541870007</v>
+        <f t="shared" si="124"/>
+        <v>1182.0125851841954</v>
       </c>
       <c r="DZ40" s="6">
-        <f t="shared" si="127"/>
-        <v>922.63102016451307</v>
+        <f t="shared" si="124"/>
+        <v>1170.1924593323533</v>
       </c>
       <c r="EA40" s="6">
-        <f t="shared" si="127"/>
-        <v>913.40470996286797</v>
+        <f t="shared" si="124"/>
+        <v>1158.4905347390297</v>
       </c>
       <c r="EB40" s="6">
-        <f t="shared" si="127"/>
-        <v>904.27066286323929</v>
+        <f t="shared" si="124"/>
+        <v>1146.9056293916394</v>
       </c>
       <c r="EC40" s="6">
-        <f t="shared" si="127"/>
-        <v>895.22795623460695</v>
+        <f t="shared" si="124"/>
+        <v>1135.4365730977231</v>
       </c>
       <c r="ED40" s="6">
-        <f t="shared" si="127"/>
-        <v>886.27567667226083</v>
+        <f t="shared" si="124"/>
+        <v>1124.0822073667459</v>
       </c>
       <c r="EE40" s="6">
-        <f t="shared" si="127"/>
-        <v>877.41291990553816</v>
+        <f t="shared" si="124"/>
+        <v>1112.8413852930785</v>
       </c>
       <c r="EF40" s="6">
-        <f t="shared" si="127"/>
-        <v>868.63879070648272</v>
+        <f t="shared" si="124"/>
+        <v>1101.7129714401476</v>
       </c>
       <c r="EG40" s="6">
-        <f t="shared" si="127"/>
-        <v>859.95240279941788</v>
+        <f t="shared" si="124"/>
+        <v>1090.695841725746</v>
       </c>
       <c r="EH40" s="6">
-        <f t="shared" si="127"/>
-        <v>851.35287877142366</v>
+        <f t="shared" si="124"/>
+        <v>1079.7888833084885</v>
       </c>
       <c r="EI40" s="6">
-        <f t="shared" si="127"/>
-        <v>842.83934998370944</v>
+        <f t="shared" si="124"/>
+        <v>1068.9909944754036</v>
       </c>
       <c r="EJ40" s="6">
-        <f t="shared" si="127"/>
-        <v>834.41095648387238</v>
+        <f t="shared" si="124"/>
+        <v>1058.3010845306496</v>
       </c>
       <c r="EK40" s="6">
-        <f t="shared" si="127"/>
-        <v>826.06684691903365</v>
+        <f t="shared" si="124"/>
+        <v>1047.7180736853431</v>
       </c>
       <c r="EL40" s="6">
-        <f t="shared" si="127"/>
-        <v>817.80617844984329</v>
+        <f t="shared" si="124"/>
+        <v>1037.2408929484898</v>
       </c>
       <c r="EM40" s="6">
-        <f t="shared" si="127"/>
-        <v>809.62811666534481</v>
+        <f t="shared" si="124"/>
+        <v>1026.8684840190049</v>
       </c>
       <c r="EN40" s="6">
-        <f t="shared" si="127"/>
-        <v>801.53183549869129</v>
+        <f t="shared" si="124"/>
+        <v>1016.5997991788148</v>
       </c>
     </row>
     <row r="43" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ43" s="10">
         <f>NPV(AJ19,W40:EN40)</f>
-        <v>23955.897369809136</v>
+        <v>28943.426750104489</v>
       </c>
     </row>
     <row r="44" spans="2:144" x14ac:dyDescent="0.3">
@@ -4771,25 +4767,25 @@
     <row r="45" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ45" s="10">
         <f>AJ43+AJ44</f>
-        <v>26015.897369809136</v>
+        <v>31003.426750104489</v>
       </c>
     </row>
     <row r="46" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ46" s="1">
         <f>AJ45/AG14</f>
-        <v>140.32307103456924</v>
+        <v>164.91184441544939</v>
       </c>
     </row>
     <row r="47" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ47" s="1">
         <f>Main!D3</f>
-        <v>203.63</v>
+        <v>218.54</v>
       </c>
     </row>
     <row r="48" spans="2:144" x14ac:dyDescent="0.3">
       <c r="AJ48" s="9">
         <f>AJ46/AJ47-1</f>
-        <v>-0.31089195582885998</v>
+        <v>-0.24539285981765624</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RDDT.xlsx
+++ b/Financial Analysis/RDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CE598A-7AC2-4041-9AEF-A394DF77AC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797C84A0-A977-4E79-8F53-C9796FB882CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{36256194-E29F-4FBF-A799-FCE3EDFD57DF}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
   <si>
     <t>Price</t>
   </si>
@@ -229,15 +229,29 @@
     <t>NPV</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Q425 8K</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="8" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -291,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -306,7 +320,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -331,14 +344,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
@@ -355,7 +368,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13914120" y="7620"/>
+          <a:off x="16954500" y="7620"/>
           <a:ext cx="0" cy="9997440"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -381,14 +394,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -405,7 +418,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10843260" y="7620"/>
+          <a:off x="11468100" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -753,17 +766,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>218.54</v>
-      </c>
-      <c r="E3" s="11">
-        <v>45961</v>
-      </c>
-      <c r="F3" s="11">
+        <v>165.1</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46059</v>
+      </c>
+      <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45961</v>
-      </c>
-      <c r="G3" s="11">
-        <v>46071</v>
+        <v>46059</v>
+      </c>
+      <c r="G3" s="10">
+        <v>46154</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -771,11 +784,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <f>188</f>
-        <v>188</v>
+        <f>190</f>
+        <v>190</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -784,7 +797,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>41085.519999999997</v>
+        <v>31369</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -792,11 +805,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <f>734.1+1325.9</f>
-        <v>2060</v>
+        <f>953.6+1523.2</f>
+        <v>2476.8000000000002</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -804,10 +817,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="2">
+        <f>0</f>
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -816,7 +830,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>2060</v>
+        <v>2476.8000000000002</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -825,7 +839,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>39025.519999999997</v>
+        <v>28892.2</v>
       </c>
     </row>
   </sheetData>
@@ -835,15 +849,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD7A926-C368-443C-82AB-009CB4B745BA}">
-  <dimension ref="A2:EN48"/>
+  <dimension ref="A2:ER48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="35" max="35" width="14.88671875" customWidth="1"/>
-    <col min="36" max="36" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.88671875" customWidth="1"/>
+    <col min="40" max="40" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:143" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:147" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
         <v>22</v>
       </c>
@@ -892,50 +906,62 @@
       <c r="R2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="T2">
+      <c r="S2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="X2">
         <v>2022</v>
       </c>
-      <c r="U2">
+      <c r="Y2">
         <v>2023</v>
       </c>
-      <c r="V2">
+      <c r="Z2">
         <v>2024</v>
       </c>
-      <c r="W2">
+      <c r="AA2">
         <v>2025</v>
       </c>
-      <c r="X2">
+      <c r="AB2">
         <v>2026</v>
       </c>
-      <c r="Y2">
+      <c r="AC2">
         <v>2027</v>
       </c>
-      <c r="Z2">
+      <c r="AD2">
         <v>2028</v>
       </c>
-      <c r="AA2">
+      <c r="AE2">
         <v>2029</v>
       </c>
-      <c r="AB2">
+      <c r="AF2">
         <v>2030</v>
       </c>
-      <c r="AC2">
+      <c r="AG2">
         <v>2031</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2032</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2033</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2034</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:147" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3"/>
       <c r="B3" s="6" t="s">
         <v>10</v>
@@ -975,64 +1001,68 @@
         <v>584.9</v>
       </c>
       <c r="R3" s="7">
-        <v>660</v>
-      </c>
-      <c r="T3" s="7">
+        <v>725.6</v>
+      </c>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="X3" s="7">
         <v>666.7</v>
       </c>
-      <c r="U3" s="7">
+      <c r="Y3" s="7">
         <v>804</v>
       </c>
-      <c r="V3" s="7">
+      <c r="Z3" s="7">
         <f>SUM(K3:N3)</f>
         <v>1300.3</v>
       </c>
-      <c r="W3" s="7">
+      <c r="AA3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>2136.9</v>
-      </c>
-      <c r="X3" s="7">
-        <f>W3*1.4</f>
-        <v>2991.66</v>
-      </c>
-      <c r="Y3" s="7">
-        <f>X3*1.3</f>
-        <v>3889.1579999999999</v>
-      </c>
-      <c r="Z3" s="7">
-        <f>Y3*1.15</f>
-        <v>4472.5316999999995</v>
-      </c>
-      <c r="AA3" s="7">
-        <f>Z3*1.08</f>
-        <v>4830.3342359999997</v>
+        <v>2202.5</v>
       </c>
       <c r="AB3" s="7">
-        <f>AA3*1.06</f>
-        <v>5120.1542901599996</v>
+        <f>AA3*1.4</f>
+        <v>3083.5</v>
       </c>
       <c r="AC3" s="7">
-        <f>AB3*1.05</f>
-        <v>5376.162004668</v>
+        <f>AB3*1.3</f>
+        <v>4008.55</v>
       </c>
       <c r="AD3" s="7">
-        <f t="shared" ref="AD3:AG3" si="0">AC3*1.05</f>
-        <v>5644.9701049014002</v>
+        <f>AC3*1.15</f>
+        <v>4609.8324999999995</v>
       </c>
       <c r="AE3" s="7">
+        <f>AD3*1.08</f>
+        <v>4978.6190999999999</v>
+      </c>
+      <c r="AF3" s="7">
+        <f>AE3*1.06</f>
+        <v>5277.3362459999998</v>
+      </c>
+      <c r="AG3" s="7">
+        <f>AF3*1.05</f>
+        <v>5541.2030583000005</v>
+      </c>
+      <c r="AH3" s="7">
+        <f t="shared" ref="AH3:AK3" si="0">AG3*1.05</f>
+        <v>5818.2632112150004</v>
+      </c>
+      <c r="AI3" s="7">
         <f t="shared" si="0"/>
-        <v>5927.2186101464704</v>
-      </c>
-      <c r="AF3" s="7">
+        <v>6109.1763717757503</v>
+      </c>
+      <c r="AJ3" s="7">
         <f t="shared" si="0"/>
-        <v>6223.5795406537945</v>
-      </c>
-      <c r="AG3" s="7">
+        <v>6414.6351903645382</v>
+      </c>
+      <c r="AK3" s="7">
         <f t="shared" si="0"/>
-        <v>6534.758517686485</v>
-      </c>
-    </row>
-    <row r="4" spans="1:143" x14ac:dyDescent="0.3">
+        <v>6735.3669498827658</v>
+      </c>
+    </row>
+    <row r="4" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -1070,175 +1100,182 @@
         <v>52.5</v>
       </c>
       <c r="R4" s="2">
-        <f t="shared" ref="Q4:R4" si="1">R3-R5</f>
-        <v>52.799999999999955</v>
-      </c>
-      <c r="T4" s="2">
+        <v>58.7</v>
+      </c>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="X4" s="2">
         <v>104.8</v>
       </c>
-      <c r="U4" s="2">
+      <c r="Y4" s="2">
         <v>111</v>
       </c>
-      <c r="V4" s="2">
+      <c r="Z4" s="2">
         <f>SUM(K4:N4)</f>
         <v>123.5</v>
       </c>
-      <c r="W4" s="2">
+      <c r="AA4" s="2">
         <f>SUM(O4:R4)</f>
-        <v>188.29999999999995</v>
-      </c>
-      <c r="X4" s="2">
-        <f>SUM(M4:T4)</f>
-        <v>359.49999999999994</v>
-      </c>
-      <c r="Y4" s="2">
-        <f>SUM(N4:U4)</f>
-        <v>435.9</v>
-      </c>
-      <c r="Z4" s="2">
-        <f t="shared" ref="Z4:AG4" si="2">SUM(S4:V4)</f>
+        <v>194.2</v>
+      </c>
+      <c r="AB4" s="2">
+        <f>SUM(M4:X4)</f>
+        <v>365.40000000000003</v>
+      </c>
+      <c r="AC4" s="2">
+        <f>SUM(N4:Y4)</f>
+        <v>441.8</v>
+      </c>
+      <c r="AD4" s="2">
+        <f t="shared" ref="AD4:AK4" si="1">SUM(W4:Z4)</f>
         <v>339.3</v>
       </c>
-      <c r="AA4" s="2">
-        <f t="shared" si="2"/>
-        <v>527.59999999999991</v>
-      </c>
-      <c r="AB4" s="2">
-        <f t="shared" si="2"/>
-        <v>782.3</v>
-      </c>
-      <c r="AC4" s="2">
-        <f t="shared" si="2"/>
-        <v>1107.1999999999998</v>
-      </c>
-      <c r="AD4" s="2">
-        <f t="shared" si="2"/>
-        <v>1323</v>
-      </c>
       <c r="AE4" s="2">
-        <f t="shared" si="2"/>
-        <v>1662.2999999999997</v>
+        <f t="shared" si="1"/>
+        <v>533.5</v>
       </c>
       <c r="AF4" s="2">
-        <f t="shared" si="2"/>
-        <v>2085.1</v>
+        <f t="shared" si="1"/>
+        <v>794.1</v>
       </c>
       <c r="AG4" s="2">
-        <f t="shared" si="2"/>
-        <v>2756.3999999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>1124.9000000000001</v>
+      </c>
+      <c r="AH4" s="2">
+        <f t="shared" si="1"/>
+        <v>1340.7</v>
+      </c>
+      <c r="AI4" s="2">
+        <f t="shared" si="1"/>
+        <v>1680</v>
+      </c>
+      <c r="AJ4" s="2">
+        <f t="shared" si="1"/>
+        <v>2108.6999999999998</v>
+      </c>
+      <c r="AK4" s="2">
+        <f t="shared" si="1"/>
+        <v>2791.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:147" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" ref="G5:Q5" si="3">G3-G4</f>
+        <f t="shared" ref="G5:R5" si="2">G3-G4</f>
         <v>136.79999999999998</v>
       </c>
       <c r="H5" s="7">
+        <f t="shared" si="2"/>
+        <v>154.19999999999999</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="2"/>
+        <v>181.1</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="2"/>
+        <v>220.9</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="2"/>
+        <v>215.4</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="2"/>
+        <v>251.7</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="2"/>
+        <v>313.79999999999995</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="2"/>
+        <v>395.9</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="2"/>
+        <v>355.29999999999995</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="2"/>
+        <v>453.70000000000005</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="2"/>
+        <v>532.4</v>
+      </c>
+      <c r="R5" s="7">
+        <f t="shared" si="2"/>
+        <v>666.9</v>
+      </c>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="X5" s="7">
+        <f>X3-X4</f>
+        <v>561.90000000000009</v>
+      </c>
+      <c r="Y5" s="7">
+        <f>Y3-Y4</f>
+        <v>693</v>
+      </c>
+      <c r="Z5" s="7">
+        <f>Z3-Z4</f>
+        <v>1176.8</v>
+      </c>
+      <c r="AA5" s="7">
+        <f>AA3-AA4</f>
+        <v>2008.3</v>
+      </c>
+      <c r="AB5" s="7">
+        <f>AB3*0.92</f>
+        <v>2836.82</v>
+      </c>
+      <c r="AC5" s="7">
+        <f t="shared" ref="AC5:AK5" si="3">AC3*0.92</f>
+        <v>3687.8660000000004</v>
+      </c>
+      <c r="AD5" s="7">
         <f t="shared" si="3"/>
-        <v>154.19999999999999</v>
-      </c>
-      <c r="I5" s="7">
+        <v>4241.0459000000001</v>
+      </c>
+      <c r="AE5" s="7">
         <f t="shared" si="3"/>
-        <v>181.1</v>
-      </c>
-      <c r="J5" s="7">
+        <v>4580.3295719999996</v>
+      </c>
+      <c r="AF5" s="7">
         <f t="shared" si="3"/>
-        <v>220.9</v>
-      </c>
-      <c r="K5" s="7">
+        <v>4855.1493463200004</v>
+      </c>
+      <c r="AG5" s="7">
         <f t="shared" si="3"/>
-        <v>215.4</v>
-      </c>
-      <c r="L5" s="7">
+        <v>5097.9068136360011</v>
+      </c>
+      <c r="AH5" s="7">
         <f t="shared" si="3"/>
-        <v>251.7</v>
-      </c>
-      <c r="M5" s="7">
+        <v>5352.8021543178002</v>
+      </c>
+      <c r="AI5" s="7">
         <f t="shared" si="3"/>
-        <v>313.79999999999995</v>
-      </c>
-      <c r="N5" s="7">
+        <v>5620.4422620336909</v>
+      </c>
+      <c r="AJ5" s="7">
         <f t="shared" si="3"/>
-        <v>395.9</v>
-      </c>
-      <c r="O5" s="7">
+        <v>5901.4643751353751</v>
+      </c>
+      <c r="AK5" s="7">
         <f t="shared" si="3"/>
-        <v>355.29999999999995</v>
-      </c>
-      <c r="P5" s="7">
-        <f t="shared" si="3"/>
-        <v>453.70000000000005</v>
-      </c>
-      <c r="Q5" s="7">
-        <f t="shared" si="3"/>
-        <v>532.4</v>
-      </c>
-      <c r="R5" s="7">
-        <f>R3*0.92</f>
-        <v>607.20000000000005</v>
-      </c>
-      <c r="T5" s="7">
-        <f>T3-T4</f>
-        <v>561.90000000000009</v>
-      </c>
-      <c r="U5" s="7">
-        <f>U3-U4</f>
-        <v>693</v>
-      </c>
-      <c r="V5" s="7">
-        <f>V3-V4</f>
-        <v>1176.8</v>
-      </c>
-      <c r="W5" s="7">
-        <f>W3-W4</f>
-        <v>1948.6000000000001</v>
-      </c>
-      <c r="X5" s="7">
-        <f>X3*0.92</f>
-        <v>2752.3272000000002</v>
-      </c>
-      <c r="Y5" s="7">
-        <f t="shared" ref="Y5:AG5" si="4">Y3*0.92</f>
-        <v>3578.0253600000001</v>
-      </c>
-      <c r="Z5" s="7">
-        <f t="shared" si="4"/>
-        <v>4114.7291639999994</v>
-      </c>
-      <c r="AA5" s="7">
-        <f t="shared" si="4"/>
-        <v>4443.9074971199998</v>
-      </c>
-      <c r="AB5" s="7">
-        <f t="shared" si="4"/>
-        <v>4710.5419469471999</v>
-      </c>
-      <c r="AC5" s="7">
-        <f t="shared" si="4"/>
-        <v>4946.0690442945606</v>
-      </c>
-      <c r="AD5" s="7">
-        <f t="shared" si="4"/>
-        <v>5193.3724965092888</v>
-      </c>
-      <c r="AE5" s="7">
-        <f t="shared" si="4"/>
-        <v>5453.0411213347534</v>
-      </c>
-      <c r="AF5" s="7">
-        <f t="shared" si="4"/>
-        <v>5725.6931774014911</v>
-      </c>
-      <c r="AG5" s="7">
-        <f t="shared" si="4"/>
-        <v>6011.977836271566</v>
-      </c>
-    </row>
-    <row r="6" spans="1:143" x14ac:dyDescent="0.3">
+        <v>6196.5375938921452</v>
+      </c>
+    </row>
+    <row r="6" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -1276,65 +1313,68 @@
         <v>196.4</v>
       </c>
       <c r="R6" s="2">
-        <f>N6*1.2</f>
-        <v>226.32</v>
-      </c>
-      <c r="T6" s="2">
+        <v>198.9</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="X6" s="2">
         <v>365.2</v>
       </c>
-      <c r="U6" s="2">
+      <c r="Y6" s="2">
         <v>438.3</v>
       </c>
-      <c r="V6" s="2">
+      <c r="Z6" s="2">
         <f>SUM(K6:N6)</f>
         <v>935.1</v>
       </c>
-      <c r="W6" s="2">
+      <c r="AA6" s="2">
         <f>SUM(O6:R6)</f>
-        <v>810.61999999999989</v>
-      </c>
-      <c r="X6" s="2">
-        <f t="shared" ref="X6:Y6" si="5">W6*1.05</f>
-        <v>851.15099999999995</v>
-      </c>
-      <c r="Y6" s="2">
+        <v>783.19999999999993</v>
+      </c>
+      <c r="AB6" s="2">
+        <f t="shared" ref="AB6:AC6" si="4">AA6*1.05</f>
+        <v>822.36</v>
+      </c>
+      <c r="AC6" s="2">
+        <f t="shared" si="4"/>
+        <v>863.47800000000007</v>
+      </c>
+      <c r="AD6" s="2">
+        <f>AC6*1.04</f>
+        <v>898.01712000000009</v>
+      </c>
+      <c r="AE6" s="2">
+        <f>AD6*1.03</f>
+        <v>924.95763360000012</v>
+      </c>
+      <c r="AF6" s="2">
+        <f t="shared" ref="AF6:AK6" si="5">AE6*1.03</f>
+        <v>952.70636260800018</v>
+      </c>
+      <c r="AG6" s="2">
         <f t="shared" si="5"/>
-        <v>893.70854999999995</v>
-      </c>
-      <c r="Z6" s="2">
-        <f>Y6*1.04</f>
-        <v>929.45689199999993</v>
-      </c>
-      <c r="AA6" s="2">
-        <f>Z6*1.03</f>
-        <v>957.34059875999992</v>
-      </c>
-      <c r="AB6" s="2">
-        <f t="shared" ref="AB6:AG6" si="6">AA6*1.03</f>
-        <v>986.06081672279993</v>
-      </c>
-      <c r="AC6" s="2">
-        <f t="shared" si="6"/>
-        <v>1015.6426412244839</v>
-      </c>
-      <c r="AD6" s="2">
-        <f t="shared" si="6"/>
-        <v>1046.1119204612185</v>
-      </c>
-      <c r="AE6" s="2">
-        <f t="shared" si="6"/>
-        <v>1077.495278075055</v>
-      </c>
-      <c r="AF6" s="2">
-        <f t="shared" si="6"/>
-        <v>1109.8201364173067</v>
-      </c>
-      <c r="AG6" s="2">
-        <f t="shared" si="6"/>
-        <v>1143.1147405098259</v>
-      </c>
-    </row>
-    <row r="7" spans="1:143" x14ac:dyDescent="0.3">
+        <v>981.2875534862402</v>
+      </c>
+      <c r="AH6" s="2">
+        <f t="shared" si="5"/>
+        <v>1010.7261800908275</v>
+      </c>
+      <c r="AI6" s="2">
+        <f t="shared" si="5"/>
+        <v>1041.0479654935523</v>
+      </c>
+      <c r="AJ6" s="2">
+        <f t="shared" si="5"/>
+        <v>1072.2794044583588</v>
+      </c>
+      <c r="AK6" s="2">
+        <f t="shared" si="5"/>
+        <v>1104.4477865921097</v>
+      </c>
+    </row>
+    <row r="7" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>14</v>
       </c>
@@ -1372,65 +1412,68 @@
         <v>128.69999999999999</v>
       </c>
       <c r="R7" s="2">
-        <f>R3*0.23</f>
-        <v>151.80000000000001</v>
-      </c>
-      <c r="T7" s="2">
+        <v>163.9</v>
+      </c>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="X7" s="2">
         <v>225.1</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>230.2</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <f>SUM(K7:N7)</f>
         <v>350.6</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <f>SUM(O7:R7)</f>
-        <v>491.8</v>
-      </c>
-      <c r="X7" s="2">
-        <f>X3*0.23</f>
-        <v>688.08180000000004</v>
-      </c>
-      <c r="Y7" s="2">
-        <f>Y3*0.22</f>
-        <v>855.61475999999993</v>
-      </c>
-      <c r="Z7" s="2">
-        <f>Z3*0.21</f>
-        <v>939.23165699999981</v>
-      </c>
-      <c r="AA7" s="2">
-        <f>AA3*0.2</f>
-        <v>966.06684719999998</v>
+        <v>503.9</v>
       </c>
       <c r="AB7" s="2">
-        <f t="shared" ref="AB7:AG7" si="7">AB3*0.2</f>
-        <v>1024.030858032</v>
+        <f>AB3*0.23</f>
+        <v>709.20500000000004</v>
       </c>
       <c r="AC7" s="2">
-        <f t="shared" si="7"/>
-        <v>1075.2324009336</v>
+        <f>AC3*0.22</f>
+        <v>881.88100000000009</v>
       </c>
       <c r="AD7" s="2">
-        <f t="shared" si="7"/>
-        <v>1128.9940209802801</v>
+        <f>AD3*0.21</f>
+        <v>968.06482499999981</v>
       </c>
       <c r="AE7" s="2">
-        <f t="shared" si="7"/>
-        <v>1185.4437220292941</v>
+        <f>AE3*0.2</f>
+        <v>995.72382000000005</v>
       </c>
       <c r="AF7" s="2">
-        <f t="shared" si="7"/>
-        <v>1244.7159081307591</v>
+        <f t="shared" ref="AF7:AK7" si="6">AF3*0.2</f>
+        <v>1055.4672492</v>
       </c>
       <c r="AG7" s="2">
-        <f t="shared" si="7"/>
-        <v>1306.9517035372971</v>
-      </c>
-    </row>
-    <row r="8" spans="1:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v>1108.2406116600002</v>
+      </c>
+      <c r="AH7" s="2">
+        <f t="shared" si="6"/>
+        <v>1163.6526422430002</v>
+      </c>
+      <c r="AI7" s="2">
+        <f t="shared" si="6"/>
+        <v>1221.8352743551502</v>
+      </c>
+      <c r="AJ7" s="2">
+        <f t="shared" si="6"/>
+        <v>1282.9270380729076</v>
+      </c>
+      <c r="AK7" s="2">
+        <f t="shared" si="6"/>
+        <v>1347.0733899765532</v>
+      </c>
+    </row>
+    <row r="8" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>15</v>
       </c>
@@ -1468,65 +1511,68 @@
         <v>68.8</v>
       </c>
       <c r="R8" s="2">
-        <f>N8*1.1</f>
-        <v>81.180000000000007</v>
-      </c>
-      <c r="T8" s="2">
+        <v>72.3</v>
+      </c>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="X8" s="2">
         <v>143.80000000000001</v>
       </c>
-      <c r="U8" s="2">
+      <c r="Y8" s="2">
         <v>164.7</v>
       </c>
-      <c r="V8" s="2">
+      <c r="Z8" s="2">
         <f>SUM(K8:N8)</f>
         <v>451.5</v>
       </c>
-      <c r="W8" s="2">
+      <c r="AA8" s="2">
         <f>SUM(O8:R8)</f>
-        <v>288.18</v>
-      </c>
-      <c r="X8" s="2">
-        <f>W8*1.03</f>
-        <v>296.8254</v>
-      </c>
-      <c r="Y8" s="2">
-        <f>X8*1.03</f>
-        <v>305.73016200000001</v>
-      </c>
-      <c r="Z8" s="2">
-        <f>Y8*1.03</f>
-        <v>314.90206685999999</v>
-      </c>
-      <c r="AA8" s="2">
-        <f>Z8*1.02</f>
-        <v>321.2001081972</v>
+        <v>279.3</v>
       </c>
       <c r="AB8" s="2">
-        <f>AA8*1.02</f>
-        <v>327.62411036114401</v>
+        <f>AA8*1.03</f>
+        <v>287.67900000000003</v>
       </c>
       <c r="AC8" s="2">
-        <f t="shared" ref="AC8:AG8" si="8">AB8*1.02</f>
-        <v>334.17659256836691</v>
+        <f>AB8*1.03</f>
+        <v>296.30937000000006</v>
       </c>
       <c r="AD8" s="2">
-        <f t="shared" si="8"/>
-        <v>340.86012441973423</v>
+        <f>AC8*1.03</f>
+        <v>305.19865110000006</v>
       </c>
       <c r="AE8" s="2">
-        <f t="shared" si="8"/>
-        <v>347.67732690812892</v>
+        <f>AD8*1.02</f>
+        <v>311.30262412200005</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" si="8"/>
-        <v>354.6308734462915</v>
+        <f>AE8*1.02</f>
+        <v>317.52867660444008</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" si="8"/>
-        <v>361.72349091521733</v>
-      </c>
-    </row>
-    <row r="9" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AG8:AK8" si="7">AF8*1.02</f>
+        <v>323.87925013652887</v>
+      </c>
+      <c r="AH8" s="2">
+        <f t="shared" si="7"/>
+        <v>330.35683513925943</v>
+      </c>
+      <c r="AI8" s="2">
+        <f t="shared" si="7"/>
+        <v>336.9639718420446</v>
+      </c>
+      <c r="AJ8" s="2">
+        <f t="shared" si="7"/>
+        <v>343.70325127888549</v>
+      </c>
+      <c r="AK8" s="2">
+        <f t="shared" si="7"/>
+        <v>350.57731630446318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:147" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
       <c r="B9" s="6" t="s">
         <v>16</v>
@@ -1536,15 +1582,15 @@
         <v>-70.700000000000017</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" ref="H9" si="9">H5-SUM(H6:H8)</f>
+        <f t="shared" ref="H9" si="8">H5-SUM(H6:H8)</f>
         <v>-52.900000000000034</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" ref="I9" si="10">I5-SUM(I6:I8)</f>
+        <f t="shared" ref="I9" si="9">I5-SUM(I6:I8)</f>
         <v>-19.599999999999994</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" ref="J9" si="11">J5-SUM(J6:J8)</f>
+        <f t="shared" ref="J9" si="10">J5-SUM(J6:J8)</f>
         <v>3.0999999999999943</v>
       </c>
       <c r="K9" s="7">
@@ -1552,91 +1598,95 @@
         <v>-589.20000000000005</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" ref="L9:R9" si="12">L5-SUM(L6:L8)</f>
+        <f t="shared" ref="L9:R9" si="11">L5-SUM(L6:L8)</f>
         <v>-31.100000000000023</v>
       </c>
       <c r="M9" s="7">
+        <f t="shared" si="11"/>
+        <v>6.8999999999999773</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="11"/>
+        <v>52.999999999999943</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="11"/>
+        <v>3.8999999999999773</v>
+      </c>
+      <c r="P9" s="7">
+        <f t="shared" si="11"/>
+        <v>67.700000000000045</v>
+      </c>
+      <c r="Q9" s="7">
+        <f t="shared" si="11"/>
+        <v>138.49999999999994</v>
+      </c>
+      <c r="R9" s="7">
+        <f t="shared" si="11"/>
+        <v>231.79999999999995</v>
+      </c>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="X9" s="7">
+        <f>X5-SUM(X6:X8)</f>
+        <v>-172.19999999999982</v>
+      </c>
+      <c r="Y9" s="7">
+        <f>Y5-SUM(Y6:Y8)</f>
+        <v>-140.20000000000005</v>
+      </c>
+      <c r="Z9" s="7">
+        <f>Z5-SUM(Z6:Z8)</f>
+        <v>-560.40000000000009</v>
+      </c>
+      <c r="AA9" s="7">
+        <f>AA5-SUM(AA6:AA8)</f>
+        <v>441.90000000000009</v>
+      </c>
+      <c r="AB9" s="7">
+        <f t="shared" ref="AB9:AK9" si="12">AB5-SUM(AB6:AB8)</f>
+        <v>1017.576</v>
+      </c>
+      <c r="AC9" s="7">
         <f t="shared" si="12"/>
-        <v>6.8999999999999773</v>
-      </c>
-      <c r="N9" s="7">
+        <v>1646.1976300000001</v>
+      </c>
+      <c r="AD9" s="7">
         <f t="shared" si="12"/>
-        <v>52.999999999999943</v>
-      </c>
-      <c r="O9" s="7">
+        <v>2069.7653039000002</v>
+      </c>
+      <c r="AE9" s="7">
         <f t="shared" si="12"/>
-        <v>3.8999999999999773</v>
-      </c>
-      <c r="P9" s="7">
+        <v>2348.3454942779995</v>
+      </c>
+      <c r="AF9" s="7">
         <f t="shared" si="12"/>
-        <v>67.700000000000045</v>
-      </c>
-      <c r="Q9" s="7">
+        <v>2529.4470579075601</v>
+      </c>
+      <c r="AG9" s="7">
         <f t="shared" si="12"/>
-        <v>138.49999999999994</v>
-      </c>
-      <c r="R9" s="7">
+        <v>2684.4993983532318</v>
+      </c>
+      <c r="AH9" s="7">
         <f t="shared" si="12"/>
-        <v>147.90000000000003</v>
-      </c>
-      <c r="T9" s="7">
-        <f>T5-SUM(T6:T8)</f>
-        <v>-172.19999999999982</v>
-      </c>
-      <c r="U9" s="7">
-        <f>U5-SUM(U6:U8)</f>
-        <v>-140.20000000000005</v>
-      </c>
-      <c r="V9" s="7">
-        <f>V5-SUM(V6:V8)</f>
-        <v>-560.40000000000009</v>
-      </c>
-      <c r="W9" s="7">
-        <f>W5-SUM(W6:W8)</f>
-        <v>358.00000000000023</v>
-      </c>
-      <c r="X9" s="7">
-        <f t="shared" ref="X9:AG9" si="13">X5-SUM(X6:X8)</f>
-        <v>916.26900000000023</v>
-      </c>
-      <c r="Y9" s="7">
-        <f t="shared" si="13"/>
-        <v>1522.9718880000005</v>
-      </c>
-      <c r="Z9" s="7">
-        <f t="shared" si="13"/>
-        <v>1931.1385481399998</v>
-      </c>
-      <c r="AA9" s="7">
-        <f t="shared" si="13"/>
-        <v>2199.2999429627998</v>
-      </c>
-      <c r="AB9" s="7">
-        <f t="shared" si="13"/>
-        <v>2372.8261618312558</v>
-      </c>
-      <c r="AC9" s="7">
-        <f t="shared" si="13"/>
-        <v>2521.0174095681095</v>
-      </c>
-      <c r="AD9" s="7">
-        <f t="shared" si="13"/>
-        <v>2677.4064306480559</v>
-      </c>
-      <c r="AE9" s="7">
-        <f t="shared" si="13"/>
-        <v>2842.4247943222749</v>
-      </c>
-      <c r="AF9" s="7">
-        <f t="shared" si="13"/>
-        <v>3016.5262594071341</v>
-      </c>
-      <c r="AG9" s="7">
-        <f t="shared" si="13"/>
-        <v>3200.1879013092257</v>
-      </c>
-    </row>
-    <row r="10" spans="1:143" x14ac:dyDescent="0.3">
+        <v>2848.0664968447127</v>
+      </c>
+      <c r="AI9" s="7">
+        <f t="shared" si="12"/>
+        <v>3020.595050342944</v>
+      </c>
+      <c r="AJ9" s="7">
+        <f t="shared" si="12"/>
+        <v>3202.5546813252231</v>
+      </c>
+      <c r="AK9" s="7">
+        <f t="shared" si="12"/>
+        <v>3394.4391010190193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -1674,65 +1724,68 @@
         <v>-22</v>
       </c>
       <c r="R10" s="2">
-        <f t="shared" ref="Q10:R10" si="14">N10*1.03</f>
-        <v>-17.613000000000003</v>
-      </c>
-      <c r="T10" s="2">
+        <v>-23</v>
+      </c>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="X10" s="2">
         <v>-14.2</v>
       </c>
-      <c r="U10" s="2">
+      <c r="Y10" s="2">
         <v>-53.1</v>
       </c>
-      <c r="V10" s="2">
+      <c r="Z10" s="2">
         <f>SUM(K10:N10)</f>
         <v>-75.400000000000006</v>
       </c>
-      <c r="W10" s="2">
+      <c r="AA10" s="2">
         <f>SUM(O10:R10)</f>
-        <v>-81.213000000000008</v>
-      </c>
-      <c r="X10" s="2">
-        <f t="shared" ref="X10:AG10" si="15">W10*1.03</f>
-        <v>-83.649390000000011</v>
-      </c>
-      <c r="Y10" s="2">
-        <f t="shared" si="15"/>
-        <v>-86.15887170000002</v>
-      </c>
-      <c r="Z10" s="2">
-        <f t="shared" si="15"/>
-        <v>-88.743637851000017</v>
-      </c>
-      <c r="AA10" s="2">
-        <f t="shared" si="15"/>
-        <v>-91.405946986530026</v>
+        <v>-86.6</v>
       </c>
       <c r="AB10" s="2">
-        <f t="shared" si="15"/>
-        <v>-94.148125396125934</v>
+        <f t="shared" ref="AB10:AK10" si="13">AA10*1.03</f>
+        <v>-89.197999999999993</v>
       </c>
       <c r="AC10" s="2">
-        <f t="shared" si="15"/>
-        <v>-96.972569158009719</v>
+        <f t="shared" si="13"/>
+        <v>-91.87393999999999</v>
       </c>
       <c r="AD10" s="2">
-        <f t="shared" si="15"/>
-        <v>-99.881746232750018</v>
+        <f t="shared" si="13"/>
+        <v>-94.630158199999997</v>
       </c>
       <c r="AE10" s="2">
-        <f t="shared" si="15"/>
-        <v>-102.87819861973252</v>
+        <f t="shared" si="13"/>
+        <v>-97.469062945999994</v>
       </c>
       <c r="AF10" s="2">
-        <f t="shared" si="15"/>
-        <v>-105.96454457832449</v>
+        <f t="shared" si="13"/>
+        <v>-100.39313483437999</v>
       </c>
       <c r="AG10" s="2">
-        <f t="shared" si="15"/>
-        <v>-109.14348091567423</v>
-      </c>
-    </row>
-    <row r="11" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="13"/>
+        <v>-103.4049288794114</v>
+      </c>
+      <c r="AH10" s="2">
+        <f t="shared" si="13"/>
+        <v>-106.50707674579374</v>
+      </c>
+      <c r="AI10" s="2">
+        <f t="shared" si="13"/>
+        <v>-109.70228904816756</v>
+      </c>
+      <c r="AJ10" s="2">
+        <f t="shared" si="13"/>
+        <v>-112.99335771961259</v>
+      </c>
+      <c r="AK10" s="2">
+        <f t="shared" si="13"/>
+        <v>-116.38315845120097</v>
+      </c>
+    </row>
+    <row r="11" spans="1:147" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11"/>
       <c r="B11" s="6" t="s">
         <v>18</v>
@@ -1742,15 +1795,15 @@
         <v>-60.000000000000014</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" ref="H11" si="16">H9-H10</f>
+        <f t="shared" ref="H11" si="14">H9-H10</f>
         <v>-39.600000000000037</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" ref="I11" si="17">I9-I10</f>
+        <f t="shared" ref="I11" si="15">I9-I10</f>
         <v>-6.9999999999999947</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" ref="J11" si="18">J9-J10</f>
+        <f t="shared" ref="J11" si="16">J9-J10</f>
         <v>19.599999999999994</v>
       </c>
       <c r="K11" s="7">
@@ -1758,91 +1811,95 @@
         <v>-574.6</v>
       </c>
       <c r="L11" s="7">
-        <f t="shared" ref="L11:R11" si="19">L9-L10</f>
+        <f t="shared" ref="L11:R11" si="17">L9-L10</f>
         <v>-10.400000000000023</v>
       </c>
       <c r="M11" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>29.899999999999977</v>
       </c>
       <c r="N11" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>70.099999999999937</v>
       </c>
       <c r="O11" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>24.399999999999977</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>88.80000000000004</v>
       </c>
       <c r="Q11" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>160.49999999999994</v>
       </c>
       <c r="R11" s="7">
-        <f t="shared" si="19"/>
-        <v>165.51300000000003</v>
-      </c>
-      <c r="T11" s="7">
-        <f>T9-T10</f>
+        <f t="shared" si="17"/>
+        <v>254.79999999999995</v>
+      </c>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="X11" s="7">
+        <f>X9-X10</f>
         <v>-157.99999999999983</v>
       </c>
-      <c r="U11" s="7">
-        <f>U9-U10</f>
+      <c r="Y11" s="7">
+        <f>Y9-Y10</f>
         <v>-87.100000000000051</v>
       </c>
-      <c r="V11" s="7">
-        <f>V9-V10</f>
+      <c r="Z11" s="7">
+        <f>Z9-Z10</f>
         <v>-485.00000000000011</v>
       </c>
-      <c r="W11" s="7">
-        <f>W9-W10</f>
-        <v>439.21300000000025</v>
-      </c>
-      <c r="X11" s="7">
-        <f t="shared" ref="X11:AG11" si="20">X9-X10</f>
-        <v>999.91839000000027</v>
-      </c>
-      <c r="Y11" s="7">
-        <f t="shared" si="20"/>
-        <v>1609.1307597000005</v>
-      </c>
-      <c r="Z11" s="7">
-        <f t="shared" si="20"/>
-        <v>2019.8821859909999</v>
-      </c>
       <c r="AA11" s="7">
-        <f t="shared" si="20"/>
-        <v>2290.70588994933</v>
+        <f>AA9-AA10</f>
+        <v>528.50000000000011</v>
       </c>
       <c r="AB11" s="7">
-        <f t="shared" si="20"/>
-        <v>2466.9742872273819</v>
+        <f t="shared" ref="AB11:AK11" si="18">AB9-AB10</f>
+        <v>1106.7740000000001</v>
       </c>
       <c r="AC11" s="7">
-        <f t="shared" si="20"/>
-        <v>2617.9899787261193</v>
+        <f t="shared" si="18"/>
+        <v>1738.0715700000001</v>
       </c>
       <c r="AD11" s="7">
-        <f t="shared" si="20"/>
-        <v>2777.2881768808061</v>
+        <f t="shared" si="18"/>
+        <v>2164.3954621000003</v>
       </c>
       <c r="AE11" s="7">
-        <f t="shared" si="20"/>
-        <v>2945.3029929420072</v>
+        <f t="shared" si="18"/>
+        <v>2445.8145572239996</v>
       </c>
       <c r="AF11" s="7">
-        <f t="shared" si="20"/>
-        <v>3122.4908039854586</v>
+        <f t="shared" si="18"/>
+        <v>2629.84019274194</v>
       </c>
       <c r="AG11" s="7">
-        <f t="shared" si="20"/>
-        <v>3309.3313822249002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>2787.904327232643</v>
+      </c>
+      <c r="AH11" s="7">
+        <f t="shared" si="18"/>
+        <v>2954.5735735905064</v>
+      </c>
+      <c r="AI11" s="7">
+        <f t="shared" si="18"/>
+        <v>3130.2973393911116</v>
+      </c>
+      <c r="AJ11" s="7">
+        <f t="shared" si="18"/>
+        <v>3315.5480390448356</v>
+      </c>
+      <c r="AK11" s="7">
+        <f t="shared" si="18"/>
+        <v>3510.8222594702202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>19</v>
       </c>
@@ -1880,64 +1937,68 @@
         <v>-2.1</v>
       </c>
       <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="X12" s="2">
         <v>0.6</v>
       </c>
-      <c r="U12" s="2">
+      <c r="Y12" s="2">
         <v>3.8</v>
       </c>
-      <c r="V12" s="2">
+      <c r="Z12" s="2">
         <f>SUM(K12:N12)</f>
         <v>-0.8</v>
       </c>
-      <c r="W12" s="2">
+      <c r="AA12" s="2">
         <f>SUM(O12:R12)</f>
-        <v>-4.2</v>
-      </c>
-      <c r="X12" s="2">
-        <f t="shared" ref="X12:AG12" si="21">X11*0.15</f>
-        <v>149.98775850000004</v>
-      </c>
-      <c r="Y12" s="2">
-        <f t="shared" si="21"/>
-        <v>241.36961395500006</v>
-      </c>
-      <c r="Z12" s="2">
-        <f t="shared" si="21"/>
-        <v>302.98232789865</v>
-      </c>
-      <c r="AA12" s="2">
-        <f t="shared" si="21"/>
-        <v>343.60588349239947</v>
+        <v>-1</v>
       </c>
       <c r="AB12" s="2">
-        <f t="shared" si="21"/>
-        <v>370.04614308410726</v>
+        <f t="shared" ref="AB12:AK12" si="19">AB11*0.15</f>
+        <v>166.01610000000002</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" si="21"/>
-        <v>392.69849680891787</v>
+        <f t="shared" si="19"/>
+        <v>260.7107355</v>
       </c>
       <c r="AD12" s="2">
-        <f t="shared" si="21"/>
-        <v>416.59322653212092</v>
+        <f t="shared" si="19"/>
+        <v>324.659319315</v>
       </c>
       <c r="AE12" s="2">
-        <f t="shared" si="21"/>
-        <v>441.79544894130106</v>
+        <f t="shared" si="19"/>
+        <v>366.87218358359991</v>
       </c>
       <c r="AF12" s="2">
-        <f t="shared" si="21"/>
-        <v>468.37362059781879</v>
+        <f t="shared" si="19"/>
+        <v>394.476028911291</v>
       </c>
       <c r="AG12" s="2">
-        <f t="shared" si="21"/>
-        <v>496.39970733373502</v>
-      </c>
-    </row>
-    <row r="13" spans="1:143" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="19"/>
+        <v>418.18564908489645</v>
+      </c>
+      <c r="AH12" s="2">
+        <f t="shared" si="19"/>
+        <v>443.18603603857593</v>
+      </c>
+      <c r="AI12" s="2">
+        <f t="shared" si="19"/>
+        <v>469.54460090866672</v>
+      </c>
+      <c r="AJ12" s="2">
+        <f t="shared" si="19"/>
+        <v>497.3322058567253</v>
+      </c>
+      <c r="AK12" s="2">
+        <f t="shared" si="19"/>
+        <v>526.623338920533</v>
+      </c>
+    </row>
+    <row r="13" spans="1:147" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13"/>
       <c r="B13" s="6" t="s">
         <v>20</v>
@@ -1947,15 +2008,15 @@
         <v>-61.000000000000014</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" ref="H13" si="22">H11-H12</f>
+        <f t="shared" ref="H13" si="20">H11-H12</f>
         <v>-41.000000000000036</v>
       </c>
       <c r="I13" s="7">
-        <f t="shared" ref="I13" si="23">I11-I12</f>
+        <f t="shared" ref="I13" si="21">I11-I12</f>
         <v>-7.399999999999995</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" ref="J13" si="24">J11-J12</f>
+        <f t="shared" ref="J13" si="22">J11-J12</f>
         <v>18.699999999999996</v>
       </c>
       <c r="K13" s="7">
@@ -1963,531 +2024,535 @@
         <v>-575</v>
       </c>
       <c r="L13" s="7">
-        <f t="shared" ref="L13:N13" si="25">L11-L12</f>
+        <f t="shared" ref="L13:N13" si="23">L11-L12</f>
         <v>-10.200000000000024</v>
       </c>
       <c r="M13" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>29.899999999999977</v>
       </c>
       <c r="N13" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>71.099999999999937</v>
       </c>
       <c r="O13" s="7">
-        <f t="shared" ref="O13:R13" si="26">O11-O12</f>
+        <f t="shared" ref="O13:R13" si="24">O11-O12</f>
         <v>26.099999999999977</v>
       </c>
       <c r="P13" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>89.200000000000045</v>
       </c>
       <c r="Q13" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>162.59999999999994</v>
       </c>
       <c r="R13" s="7">
-        <f t="shared" si="26"/>
-        <v>165.51300000000003</v>
-      </c>
-      <c r="T13" s="7">
-        <f>T11-T12</f>
+        <f t="shared" si="24"/>
+        <v>251.59999999999997</v>
+      </c>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="X13" s="7">
+        <f>X11-X12</f>
         <v>-158.59999999999982</v>
       </c>
-      <c r="U13" s="7">
-        <f>U11-U12</f>
+      <c r="Y13" s="7">
+        <f>Y11-Y12</f>
         <v>-90.900000000000048</v>
       </c>
-      <c r="V13" s="7">
-        <f>V11-V12</f>
+      <c r="Z13" s="7">
+        <f>Z11-Z12</f>
         <v>-484.2000000000001</v>
       </c>
-      <c r="W13" s="7">
-        <f t="shared" ref="W13" si="27">W11-W12</f>
-        <v>443.41300000000024</v>
-      </c>
-      <c r="X13" s="7">
-        <f t="shared" ref="X13" si="28">X11-X12</f>
-        <v>849.93063150000023</v>
-      </c>
-      <c r="Y13" s="7">
-        <f t="shared" ref="Y13" si="29">Y11-Y12</f>
-        <v>1367.7611457450005</v>
-      </c>
-      <c r="Z13" s="7">
-        <f t="shared" ref="Z13" si="30">Z11-Z12</f>
-        <v>1716.8998580923499</v>
-      </c>
       <c r="AA13" s="7">
-        <f t="shared" ref="AA13" si="31">AA11-AA12</f>
-        <v>1947.1000064569305</v>
+        <f t="shared" ref="AA13" si="25">AA11-AA12</f>
+        <v>529.50000000000011</v>
       </c>
       <c r="AB13" s="7">
-        <f t="shared" ref="AB13" si="32">AB11-AB12</f>
-        <v>2096.9281441432745</v>
+        <f t="shared" ref="AB13" si="26">AB11-AB12</f>
+        <v>940.75790000000006</v>
       </c>
       <c r="AC13" s="7">
-        <f t="shared" ref="AC13" si="33">AC11-AC12</f>
-        <v>2225.2914819172015</v>
+        <f t="shared" ref="AC13" si="27">AC11-AC12</f>
+        <v>1477.3608345</v>
       </c>
       <c r="AD13" s="7">
-        <f t="shared" ref="AD13" si="34">AD11-AD12</f>
-        <v>2360.6949503486853</v>
+        <f t="shared" ref="AD13" si="28">AD11-AD12</f>
+        <v>1839.7361427850003</v>
       </c>
       <c r="AE13" s="7">
-        <f t="shared" ref="AE13" si="35">AE11-AE12</f>
-        <v>2503.5075440007063</v>
+        <f t="shared" ref="AE13" si="29">AE11-AE12</f>
+        <v>2078.9423736403996</v>
       </c>
       <c r="AF13" s="7">
-        <f t="shared" ref="AF13" si="36">AF11-AF12</f>
-        <v>2654.1171833876397</v>
+        <f t="shared" ref="AF13" si="30">AF11-AF12</f>
+        <v>2235.364163830649</v>
       </c>
       <c r="AG13" s="7">
-        <f t="shared" ref="AG13" si="37">AG11-AG12</f>
-        <v>2812.9316748911651</v>
-      </c>
-      <c r="AH13" s="6">
-        <f>AG13*(1+$AJ$18)</f>
-        <v>2784.8023581422535</v>
-      </c>
-      <c r="AI13" s="6">
-        <f t="shared" ref="AI13:CT13" si="38">AH13*(1+$AJ$18)</f>
-        <v>2756.9543345608308</v>
-      </c>
-      <c r="AJ13" s="6">
-        <f t="shared" si="38"/>
-        <v>2729.3847912152223</v>
-      </c>
-      <c r="AK13" s="6">
-        <f t="shared" si="38"/>
-        <v>2702.0909433030702</v>
+        <f t="shared" ref="AG13" si="31">AG11-AG12</f>
+        <v>2369.7186781477467</v>
+      </c>
+      <c r="AH13" s="7">
+        <f t="shared" ref="AH13" si="32">AH11-AH12</f>
+        <v>2511.3875375519306</v>
+      </c>
+      <c r="AI13" s="7">
+        <f t="shared" ref="AI13" si="33">AI11-AI12</f>
+        <v>2660.7527384824448</v>
+      </c>
+      <c r="AJ13" s="7">
+        <f t="shared" ref="AJ13" si="34">AJ11-AJ12</f>
+        <v>2818.2158331881101</v>
+      </c>
+      <c r="AK13" s="7">
+        <f t="shared" ref="AK13" si="35">AK11-AK12</f>
+        <v>2984.198920549687</v>
       </c>
       <c r="AL13" s="6">
-        <f t="shared" si="38"/>
-        <v>2675.0700338700394</v>
+        <f>AK13*(1+$AN$18)</f>
+        <v>2954.3569313441903</v>
       </c>
       <c r="AM13" s="6">
-        <f t="shared" si="38"/>
-        <v>2648.319333531339</v>
+        <f t="shared" ref="AM13:CX13" si="36">AL13*(1+$AN$18)</f>
+        <v>2924.8133620307485</v>
       </c>
       <c r="AN13" s="6">
-        <f t="shared" si="38"/>
-        <v>2621.8361401960256</v>
+        <f t="shared" si="36"/>
+        <v>2895.5652284104408</v>
       </c>
       <c r="AO13" s="6">
-        <f t="shared" si="38"/>
-        <v>2595.6177787940651</v>
+        <f t="shared" si="36"/>
+        <v>2866.6095761263364</v>
       </c>
       <c r="AP13" s="6">
-        <f t="shared" si="38"/>
-        <v>2569.6616010061243</v>
+        <f t="shared" si="36"/>
+        <v>2837.9434803650729</v>
       </c>
       <c r="AQ13" s="6">
-        <f t="shared" si="38"/>
-        <v>2543.9649849960629</v>
+        <f t="shared" si="36"/>
+        <v>2809.5640455614221</v>
       </c>
       <c r="AR13" s="6">
-        <f t="shared" si="38"/>
-        <v>2518.5253351461024</v>
+        <f t="shared" si="36"/>
+        <v>2781.468405105808</v>
       </c>
       <c r="AS13" s="6">
-        <f t="shared" si="38"/>
-        <v>2493.3400817946413</v>
+        <f t="shared" si="36"/>
+        <v>2753.6537210547499</v>
       </c>
       <c r="AT13" s="6">
-        <f t="shared" si="38"/>
-        <v>2468.406680976695</v>
+        <f t="shared" si="36"/>
+        <v>2726.1171838442024</v>
       </c>
       <c r="AU13" s="6">
-        <f t="shared" si="38"/>
-        <v>2443.722614166928</v>
+        <f t="shared" si="36"/>
+        <v>2698.8560120057605</v>
       </c>
       <c r="AV13" s="6">
-        <f t="shared" si="38"/>
-        <v>2419.2853880252587</v>
+        <f t="shared" si="36"/>
+        <v>2671.8674518857028</v>
       </c>
       <c r="AW13" s="6">
-        <f t="shared" si="38"/>
-        <v>2395.0925341450061</v>
+        <f t="shared" si="36"/>
+        <v>2645.1487773668459</v>
       </c>
       <c r="AX13" s="6">
-        <f t="shared" si="38"/>
-        <v>2371.1416088035562</v>
+        <f t="shared" si="36"/>
+        <v>2618.6972895931776</v>
       </c>
       <c r="AY13" s="6">
-        <f t="shared" si="38"/>
-        <v>2347.4301927155207</v>
+        <f t="shared" si="36"/>
+        <v>2592.5103166972458</v>
       </c>
       <c r="AZ13" s="6">
-        <f t="shared" si="38"/>
-        <v>2323.9558907883657</v>
+        <f t="shared" si="36"/>
+        <v>2566.5852135302734</v>
       </c>
       <c r="BA13" s="6">
-        <f t="shared" si="38"/>
-        <v>2300.7163318804819</v>
+        <f t="shared" si="36"/>
+        <v>2540.9193613949706</v>
       </c>
       <c r="BB13" s="6">
-        <f t="shared" si="38"/>
-        <v>2277.709168561677</v>
+        <f t="shared" si="36"/>
+        <v>2515.5101677810208</v>
       </c>
       <c r="BC13" s="6">
-        <f t="shared" si="38"/>
-        <v>2254.9320768760604</v>
+        <f t="shared" si="36"/>
+        <v>2490.3550661032104</v>
       </c>
       <c r="BD13" s="6">
-        <f t="shared" si="38"/>
-        <v>2232.3827561072999</v>
+        <f t="shared" si="36"/>
+        <v>2465.4515154421783</v>
       </c>
       <c r="BE13" s="6">
-        <f t="shared" si="38"/>
-        <v>2210.058928546227</v>
+        <f t="shared" si="36"/>
+        <v>2440.7970002877564</v>
       </c>
       <c r="BF13" s="6">
-        <f t="shared" si="38"/>
-        <v>2187.9583392607647</v>
+        <f t="shared" si="36"/>
+        <v>2416.389030284879</v>
       </c>
       <c r="BG13" s="6">
-        <f t="shared" si="38"/>
-        <v>2166.0787558681568</v>
+        <f t="shared" si="36"/>
+        <v>2392.2251399820302</v>
       </c>
       <c r="BH13" s="6">
-        <f t="shared" si="38"/>
-        <v>2144.4179683094753</v>
+        <f t="shared" si="36"/>
+        <v>2368.30288858221</v>
       </c>
       <c r="BI13" s="6">
-        <f t="shared" si="38"/>
-        <v>2122.9737886263806</v>
+        <f t="shared" si="36"/>
+        <v>2344.6198596963877</v>
       </c>
       <c r="BJ13" s="6">
-        <f t="shared" si="38"/>
-        <v>2101.7440507401166</v>
+        <f t="shared" si="36"/>
+        <v>2321.173661099424</v>
       </c>
       <c r="BK13" s="6">
-        <f t="shared" si="38"/>
-        <v>2080.7266102327153</v>
+        <f t="shared" si="36"/>
+        <v>2297.9619244884298</v>
       </c>
       <c r="BL13" s="6">
-        <f t="shared" si="38"/>
-        <v>2059.9193441303883</v>
+        <f t="shared" si="36"/>
+        <v>2274.9823052435454</v>
       </c>
       <c r="BM13" s="6">
-        <f t="shared" si="38"/>
-        <v>2039.3201506890844</v>
+        <f t="shared" si="36"/>
+        <v>2252.2324821911097</v>
       </c>
       <c r="BN13" s="6">
-        <f t="shared" si="38"/>
-        <v>2018.9269491821935</v>
+        <f t="shared" si="36"/>
+        <v>2229.7101573691984</v>
       </c>
       <c r="BO13" s="6">
-        <f t="shared" si="38"/>
-        <v>1998.7376796903716</v>
+        <f t="shared" si="36"/>
+        <v>2207.4130557955064</v>
       </c>
       <c r="BP13" s="6">
-        <f t="shared" si="38"/>
-        <v>1978.7503028934677</v>
+        <f t="shared" si="36"/>
+        <v>2185.3389252375514</v>
       </c>
       <c r="BQ13" s="6">
-        <f t="shared" si="38"/>
-        <v>1958.9627998645331</v>
+        <f t="shared" si="36"/>
+        <v>2163.4855359851758</v>
       </c>
       <c r="BR13" s="6">
-        <f t="shared" si="38"/>
-        <v>1939.3731718658878</v>
+        <f t="shared" si="36"/>
+        <v>2141.850680625324</v>
       </c>
       <c r="BS13" s="6">
-        <f t="shared" si="38"/>
-        <v>1919.9794401472288</v>
+        <f t="shared" si="36"/>
+        <v>2120.4321738190706</v>
       </c>
       <c r="BT13" s="6">
-        <f t="shared" si="38"/>
-        <v>1900.7796457457566</v>
+        <f t="shared" si="36"/>
+        <v>2099.22785208088</v>
       </c>
       <c r="BU13" s="6">
-        <f t="shared" si="38"/>
-        <v>1881.7718492882991</v>
+        <f t="shared" si="36"/>
+        <v>2078.2355735600713</v>
       </c>
       <c r="BV13" s="6">
-        <f t="shared" si="38"/>
-        <v>1862.9541307954162</v>
+        <f t="shared" si="36"/>
+        <v>2057.4532178244704</v>
       </c>
       <c r="BW13" s="6">
-        <f t="shared" si="38"/>
-        <v>1844.3245894874619</v>
+        <f t="shared" si="36"/>
+        <v>2036.8786856462257</v>
       </c>
       <c r="BX13" s="6">
-        <f t="shared" si="38"/>
-        <v>1825.8813435925872</v>
+        <f t="shared" si="36"/>
+        <v>2016.5098987897634</v>
       </c>
       <c r="BY13" s="6">
-        <f t="shared" si="38"/>
-        <v>1807.6225301566612</v>
+        <f t="shared" si="36"/>
+        <v>1996.3447998018657</v>
       </c>
       <c r="BZ13" s="6">
-        <f t="shared" si="38"/>
-        <v>1789.5463048550946</v>
+        <f t="shared" si="36"/>
+        <v>1976.3813518038471</v>
       </c>
       <c r="CA13" s="6">
-        <f t="shared" si="38"/>
-        <v>1771.6508418065437</v>
+        <f t="shared" si="36"/>
+        <v>1956.6175382858087</v>
       </c>
       <c r="CB13" s="6">
-        <f t="shared" si="38"/>
-        <v>1753.9343333884783</v>
+        <f t="shared" si="36"/>
+        <v>1937.0513629029506</v>
       </c>
       <c r="CC13" s="6">
-        <f t="shared" si="38"/>
-        <v>1736.3949900545936</v>
+        <f t="shared" si="36"/>
+        <v>1917.680849273921</v>
       </c>
       <c r="CD13" s="6">
-        <f t="shared" si="38"/>
-        <v>1719.0310401540476</v>
+        <f t="shared" si="36"/>
+        <v>1898.5040407811819</v>
       </c>
       <c r="CE13" s="6">
-        <f t="shared" si="38"/>
-        <v>1701.8407297525071</v>
+        <f t="shared" si="36"/>
+        <v>1879.5190003733701</v>
       </c>
       <c r="CF13" s="6">
-        <f t="shared" si="38"/>
-        <v>1684.822322454982</v>
+        <f t="shared" si="36"/>
+        <v>1860.7238103696363</v>
       </c>
       <c r="CG13" s="6">
-        <f t="shared" si="38"/>
-        <v>1667.9740992304321</v>
+        <f t="shared" si="36"/>
+        <v>1842.11657226594</v>
       </c>
       <c r="CH13" s="6">
-        <f t="shared" si="38"/>
-        <v>1651.2943582381279</v>
+        <f t="shared" si="36"/>
+        <v>1823.6954065432806</v>
       </c>
       <c r="CI13" s="6">
-        <f t="shared" si="38"/>
-        <v>1634.7814146557466</v>
+        <f t="shared" si="36"/>
+        <v>1805.4584524778477</v>
       </c>
       <c r="CJ13" s="6">
-        <f t="shared" si="38"/>
-        <v>1618.4336005091891</v>
+        <f t="shared" si="36"/>
+        <v>1787.4038679530693</v>
       </c>
       <c r="CK13" s="6">
-        <f t="shared" si="38"/>
-        <v>1602.2492645040973</v>
+        <f t="shared" si="36"/>
+        <v>1769.5298292735386</v>
       </c>
       <c r="CL13" s="6">
-        <f t="shared" si="38"/>
-        <v>1586.2267718590563</v>
+        <f t="shared" si="36"/>
+        <v>1751.8345309808033</v>
       </c>
       <c r="CM13" s="6">
-        <f t="shared" si="38"/>
-        <v>1570.3645041404657</v>
+        <f t="shared" si="36"/>
+        <v>1734.3161856709953</v>
       </c>
       <c r="CN13" s="6">
-        <f t="shared" si="38"/>
-        <v>1554.6608590990611</v>
+        <f t="shared" si="36"/>
+        <v>1716.9730238142854</v>
       </c>
       <c r="CO13" s="6">
-        <f t="shared" si="38"/>
-        <v>1539.1142505080704</v>
+        <f t="shared" si="36"/>
+        <v>1699.8032935761426</v>
       </c>
       <c r="CP13" s="6">
-        <f t="shared" si="38"/>
-        <v>1523.7231080029896</v>
+        <f t="shared" si="36"/>
+        <v>1682.8052606403812</v>
       </c>
       <c r="CQ13" s="6">
-        <f t="shared" si="38"/>
-        <v>1508.4858769229597</v>
+        <f t="shared" si="36"/>
+        <v>1665.9772080339774</v>
       </c>
       <c r="CR13" s="6">
-        <f t="shared" si="38"/>
-        <v>1493.4010181537301</v>
+        <f t="shared" si="36"/>
+        <v>1649.3174359536376</v>
       </c>
       <c r="CS13" s="6">
-        <f t="shared" si="38"/>
-        <v>1478.4670079721927</v>
+        <f t="shared" si="36"/>
+        <v>1632.8242615941012</v>
       </c>
       <c r="CT13" s="6">
-        <f t="shared" si="38"/>
-        <v>1463.6823378924707</v>
+        <f t="shared" si="36"/>
+        <v>1616.4960189781602</v>
       </c>
       <c r="CU13" s="6">
-        <f t="shared" ref="CU13:EM13" si="39">CT13*(1+$AJ$18)</f>
-        <v>1449.0455145135461</v>
+        <f t="shared" si="36"/>
+        <v>1600.3310587883786</v>
       </c>
       <c r="CV13" s="6">
-        <f t="shared" si="39"/>
-        <v>1434.5550593684106</v>
+        <f t="shared" si="36"/>
+        <v>1584.3277482004949</v>
       </c>
       <c r="CW13" s="6">
-        <f t="shared" si="39"/>
-        <v>1420.2095087747266</v>
+        <f t="shared" si="36"/>
+        <v>1568.48447071849</v>
       </c>
       <c r="CX13" s="6">
-        <f t="shared" si="39"/>
-        <v>1406.0074136869794</v>
+        <f t="shared" si="36"/>
+        <v>1552.799626011305</v>
       </c>
       <c r="CY13" s="6">
-        <f t="shared" si="39"/>
-        <v>1391.9473395501095</v>
+        <f t="shared" ref="CY13:EQ13" si="37">CX13*(1+$AN$18)</f>
+        <v>1537.271629751192</v>
       </c>
       <c r="CZ13" s="6">
-        <f t="shared" si="39"/>
-        <v>1378.0278661546083</v>
+        <f t="shared" si="37"/>
+        <v>1521.8989134536801</v>
       </c>
       <c r="DA13" s="6">
-        <f t="shared" si="39"/>
-        <v>1364.2475874930622</v>
+        <f t="shared" si="37"/>
+        <v>1506.6799243191433</v>
       </c>
       <c r="DB13" s="6">
-        <f t="shared" si="39"/>
-        <v>1350.6051116181316</v>
+        <f t="shared" si="37"/>
+        <v>1491.6131250759518</v>
       </c>
       <c r="DC13" s="6">
-        <f t="shared" si="39"/>
-        <v>1337.0990605019501</v>
+        <f t="shared" si="37"/>
+        <v>1476.6969938251923</v>
       </c>
       <c r="DD13" s="6">
-        <f t="shared" si="39"/>
-        <v>1323.7280698969307</v>
+        <f t="shared" si="37"/>
+        <v>1461.9300238869403</v>
       </c>
       <c r="DE13" s="6">
-        <f t="shared" si="39"/>
-        <v>1310.4907891979615</v>
+        <f t="shared" si="37"/>
+        <v>1447.3107236480707</v>
       </c>
       <c r="DF13" s="6">
-        <f t="shared" si="39"/>
-        <v>1297.3858813059819</v>
+        <f t="shared" si="37"/>
+        <v>1432.83761641159</v>
       </c>
       <c r="DG13" s="6">
-        <f t="shared" si="39"/>
-        <v>1284.412022492922</v>
+        <f t="shared" si="37"/>
+        <v>1418.5092402474741</v>
       </c>
       <c r="DH13" s="6">
-        <f t="shared" si="39"/>
-        <v>1271.5679022679928</v>
+        <f t="shared" si="37"/>
+        <v>1404.3241478449993</v>
       </c>
       <c r="DI13" s="6">
-        <f t="shared" si="39"/>
-        <v>1258.8522232453129</v>
+        <f t="shared" si="37"/>
+        <v>1390.2809063665493</v>
       </c>
       <c r="DJ13" s="6">
-        <f t="shared" si="39"/>
-        <v>1246.2637010128597</v>
+        <f t="shared" si="37"/>
+        <v>1376.3780973028838</v>
       </c>
       <c r="DK13" s="6">
-        <f t="shared" si="39"/>
-        <v>1233.801064002731</v>
+        <f t="shared" si="37"/>
+        <v>1362.614316329855</v>
       </c>
       <c r="DL13" s="6">
-        <f t="shared" si="39"/>
-        <v>1221.4630533627037</v>
+        <f t="shared" si="37"/>
+        <v>1348.9881731665564</v>
       </c>
       <c r="DM13" s="6">
-        <f t="shared" si="39"/>
-        <v>1209.2484228290766</v>
+        <f t="shared" si="37"/>
+        <v>1335.4982914348909</v>
       </c>
       <c r="DN13" s="6">
-        <f t="shared" si="39"/>
-        <v>1197.1559386007859</v>
+        <f t="shared" si="37"/>
+        <v>1322.143308520542</v>
       </c>
       <c r="DO13" s="6">
-        <f t="shared" si="39"/>
-        <v>1185.1843792147781</v>
+        <f t="shared" si="37"/>
+        <v>1308.9218754353365</v>
       </c>
       <c r="DP13" s="6">
-        <f t="shared" si="39"/>
-        <v>1173.3325354226304</v>
+        <f t="shared" si="37"/>
+        <v>1295.8326566809831</v>
       </c>
       <c r="DQ13" s="6">
-        <f t="shared" si="39"/>
-        <v>1161.5992100684041</v>
+        <f t="shared" si="37"/>
+        <v>1282.8743301141733</v>
       </c>
       <c r="DR13" s="6">
-        <f t="shared" si="39"/>
-        <v>1149.9832179677201</v>
+        <f t="shared" si="37"/>
+        <v>1270.0455868130316</v>
       </c>
       <c r="DS13" s="6">
-        <f t="shared" si="39"/>
-        <v>1138.4833857880428</v>
+        <f t="shared" si="37"/>
+        <v>1257.3451309449013</v>
       </c>
       <c r="DT13" s="6">
-        <f t="shared" si="39"/>
-        <v>1127.0985519301623</v>
+        <f t="shared" si="37"/>
+        <v>1244.7716796354523</v>
       </c>
       <c r="DU13" s="6">
-        <f t="shared" si="39"/>
-        <v>1115.8275664108608</v>
+        <f t="shared" si="37"/>
+        <v>1232.3239628390977</v>
       </c>
       <c r="DV13" s="6">
-        <f t="shared" si="39"/>
-        <v>1104.669290746752</v>
+        <f t="shared" si="37"/>
+        <v>1220.0007232107066</v>
       </c>
       <c r="DW13" s="6">
-        <f t="shared" si="39"/>
-        <v>1093.6225978392845</v>
+        <f t="shared" si="37"/>
+        <v>1207.8007159785996</v>
       </c>
       <c r="DX13" s="6">
-        <f t="shared" si="39"/>
-        <v>1082.6863718608915</v>
+        <f t="shared" si="37"/>
+        <v>1195.7227088188135</v>
       </c>
       <c r="DY13" s="6">
-        <f t="shared" si="39"/>
-        <v>1071.8595081422827</v>
+        <f t="shared" si="37"/>
+        <v>1183.7654817306254</v>
       </c>
       <c r="DZ13" s="6">
-        <f t="shared" si="39"/>
-        <v>1061.1409130608599</v>
+        <f t="shared" si="37"/>
+        <v>1171.9278269133192</v>
       </c>
       <c r="EA13" s="6">
-        <f t="shared" si="39"/>
-        <v>1050.5295039302514</v>
+        <f t="shared" si="37"/>
+        <v>1160.2085486441861</v>
       </c>
       <c r="EB13" s="6">
-        <f t="shared" si="39"/>
-        <v>1040.0242088909488</v>
+        <f t="shared" si="37"/>
+        <v>1148.6064631577442</v>
       </c>
       <c r="EC13" s="6">
-        <f t="shared" si="39"/>
-        <v>1029.6239668020394</v>
+        <f t="shared" si="37"/>
+        <v>1137.1203985261668</v>
       </c>
       <c r="ED13" s="6">
-        <f t="shared" si="39"/>
-        <v>1019.327727134019</v>
+        <f t="shared" si="37"/>
+        <v>1125.7491945409051</v>
       </c>
       <c r="EE13" s="6">
-        <f t="shared" si="39"/>
-        <v>1009.1344498626788</v>
+        <f t="shared" si="37"/>
+        <v>1114.491702595496</v>
       </c>
       <c r="EF13" s="6">
-        <f t="shared" si="39"/>
-        <v>999.04310536405205</v>
+        <f t="shared" si="37"/>
+        <v>1103.346785569541</v>
       </c>
       <c r="EG13" s="6">
-        <f t="shared" si="39"/>
-        <v>989.05267431041148</v>
+        <f t="shared" si="37"/>
+        <v>1092.3133177138457</v>
       </c>
       <c r="EH13" s="6">
-        <f t="shared" si="39"/>
-        <v>979.16214756730733</v>
+        <f t="shared" si="37"/>
+        <v>1081.3901845367072</v>
       </c>
       <c r="EI13" s="6">
-        <f t="shared" si="39"/>
-        <v>969.37052609163425</v>
+        <f t="shared" si="37"/>
+        <v>1070.5762826913401</v>
       </c>
       <c r="EJ13" s="6">
-        <f t="shared" si="39"/>
-        <v>959.67682083071793</v>
+        <f t="shared" si="37"/>
+        <v>1059.8705198644268</v>
       </c>
       <c r="EK13" s="6">
-        <f t="shared" si="39"/>
-        <v>950.08005262241079</v>
+        <f t="shared" si="37"/>
+        <v>1049.2718146657826</v>
       </c>
       <c r="EL13" s="6">
-        <f t="shared" si="39"/>
-        <v>940.57925209618668</v>
+        <f t="shared" si="37"/>
+        <v>1038.7790965191248</v>
       </c>
       <c r="EM13" s="6">
-        <f t="shared" si="39"/>
-        <v>931.1734595752248</v>
-      </c>
-    </row>
-    <row r="14" spans="1:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="37"/>
+        <v>1028.3913055539335</v>
+      </c>
+      <c r="EN13" s="6">
+        <f t="shared" si="37"/>
+        <v>1018.1073924983942</v>
+      </c>
+      <c r="EO13" s="6">
+        <f t="shared" si="37"/>
+        <v>1007.9263185734103</v>
+      </c>
+      <c r="EP13" s="6">
+        <f t="shared" si="37"/>
+        <v>997.84705538767616</v>
+      </c>
+      <c r="EQ13" s="6">
+        <f t="shared" si="37"/>
+        <v>987.86858483379945</v>
+      </c>
+    </row>
+    <row r="14" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>1</v>
       </c>
@@ -2529,64 +2594,68 @@
         <v>188</v>
       </c>
       <c r="R14" s="2">
-        <f>188</f>
-        <v>188</v>
-      </c>
-      <c r="T14" s="2">
+        <f>190</f>
+        <v>190</v>
+      </c>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="X14" s="2">
         <v>164</v>
       </c>
-      <c r="U14" s="2">
+      <c r="Y14" s="2">
         <v>164</v>
       </c>
-      <c r="V14" s="2">
+      <c r="Z14" s="2">
         <v>164</v>
       </c>
-      <c r="W14" s="2">
-        <f>188</f>
-        <v>188</v>
-      </c>
-      <c r="X14" s="2">
-        <f>188</f>
-        <v>188</v>
-      </c>
-      <c r="Y14" s="2">
-        <f>188</f>
-        <v>188</v>
-      </c>
-      <c r="Z14" s="2">
-        <f>188</f>
-        <v>188</v>
-      </c>
       <c r="AA14" s="2">
-        <f>188</f>
-        <v>188</v>
+        <f>190</f>
+        <v>190</v>
       </c>
       <c r="AB14" s="2">
-        <f>188</f>
-        <v>188</v>
+        <f>190</f>
+        <v>190</v>
       </c>
       <c r="AC14" s="2">
-        <f>188</f>
-        <v>188</v>
+        <f>190</f>
+        <v>190</v>
       </c>
       <c r="AD14" s="2">
-        <f>188</f>
-        <v>188</v>
+        <f>190</f>
+        <v>190</v>
       </c>
       <c r="AE14" s="2">
-        <f>188</f>
-        <v>188</v>
+        <f>190</f>
+        <v>190</v>
       </c>
       <c r="AF14" s="2">
-        <f>188</f>
-        <v>188</v>
+        <f>190</f>
+        <v>190</v>
       </c>
       <c r="AG14" s="2">
-        <f>188</f>
-        <v>188</v>
-      </c>
-    </row>
-    <row r="15" spans="1:143" x14ac:dyDescent="0.3">
+        <f>190</f>
+        <v>190</v>
+      </c>
+      <c r="AH14" s="2">
+        <f>190</f>
+        <v>190</v>
+      </c>
+      <c r="AI14" s="2">
+        <f>190</f>
+        <v>190</v>
+      </c>
+      <c r="AJ14" s="2">
+        <f>190</f>
+        <v>190</v>
+      </c>
+      <c r="AK14" s="2">
+        <f>190</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>21</v>
       </c>
@@ -2595,15 +2664,15 @@
         <v>-1.0499139414802068</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" ref="H15" si="40">H13/H14</f>
+        <f t="shared" ref="H15" si="38">H13/H14</f>
         <v>-0.70085470085470147</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" ref="I15" si="41">I13/I14</f>
+        <f t="shared" ref="I15" si="39">I13/I14</f>
         <v>-0.12563667232597614</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" ref="J15" si="42">J13/J14</f>
+        <f t="shared" ref="J15" si="40">J13/J14</f>
         <v>0.30655737704918024</v>
       </c>
       <c r="K15" s="5">
@@ -2611,91 +2680,95 @@
         <v>-8.1908831908831914</v>
       </c>
       <c r="L15" s="5">
-        <f t="shared" ref="L15:N15" si="43">L13/L14</f>
+        <f t="shared" ref="L15:N15" si="41">L13/L14</f>
         <v>-6.2043795620438102E-2</v>
       </c>
       <c r="M15" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>0.1767139479905436</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>0.39303482587064642</v>
       </c>
       <c r="O15" s="5">
-        <f t="shared" ref="O15:R15" si="44">O13/O14</f>
+        <f t="shared" ref="O15:R15" si="42">O13/O14</f>
         <v>0.14146341463414622</v>
       </c>
       <c r="P15" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>0.481121898597627</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>0.86489361702127632</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="44"/>
-        <v>0.88038829787234063</v>
-      </c>
-      <c r="T15" s="5">
-        <f>T13/T14</f>
+        <f t="shared" si="42"/>
+        <v>1.3242105263157893</v>
+      </c>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="X15" s="5">
+        <f>X13/X14</f>
         <v>-0.96707317073170629</v>
       </c>
-      <c r="U15" s="5">
-        <f>U13/U14</f>
+      <c r="Y15" s="5">
+        <f>Y13/Y14</f>
         <v>-0.5542682926829271</v>
       </c>
-      <c r="V15" s="5">
-        <f>V13/V14</f>
+      <c r="Z15" s="5">
+        <f>Z13/Z14</f>
         <v>-2.9524390243902445</v>
       </c>
-      <c r="W15" s="5">
-        <f t="shared" ref="W15" si="45">W13/W14</f>
-        <v>2.3585797872340439</v>
-      </c>
-      <c r="X15" s="5">
-        <f t="shared" ref="X15" si="46">X13/X14</f>
-        <v>4.5209076143617031</v>
-      </c>
-      <c r="Y15" s="5">
-        <f t="shared" ref="Y15" si="47">Y13/Y14</f>
-        <v>7.2753252433244704</v>
-      </c>
-      <c r="Z15" s="5">
-        <f t="shared" ref="Z15" si="48">Z13/Z14</f>
-        <v>9.1324460536827115</v>
-      </c>
       <c r="AA15" s="5">
-        <f t="shared" ref="AA15" si="49">AA13/AA14</f>
-        <v>10.356914927962396</v>
+        <f t="shared" ref="AA15" si="43">AA13/AA14</f>
+        <v>2.7868421052631587</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" ref="AB15" si="50">AB13/AB14</f>
-        <v>11.153873107145078</v>
+        <f t="shared" ref="AB15" si="44">AB13/AB14</f>
+        <v>4.9513573684210526</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" ref="AC15" si="51">AC13/AC14</f>
-        <v>11.836656818708519</v>
+        <f t="shared" ref="AC15" si="45">AC13/AC14</f>
+        <v>7.775583339473684</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" ref="AD15" si="52">AD13/AD14</f>
-        <v>12.556888033769603</v>
+        <f t="shared" ref="AD15" si="46">AD13/AD14</f>
+        <v>9.6828218041315814</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" ref="AE15" si="53">AE13/AE14</f>
-        <v>13.316529489365459</v>
+        <f t="shared" ref="AE15" si="47">AE13/AE14</f>
+        <v>10.94180196652842</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" ref="AF15" si="54">AF13/AF14</f>
-        <v>14.117644592487444</v>
+        <f t="shared" ref="AF15" si="48">AF13/AF14</f>
+        <v>11.7650745464771</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" ref="AG15" si="55">AG13/AG14</f>
-        <v>14.962402526016836</v>
-      </c>
-    </row>
-    <row r="17" spans="2:36" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AG15" si="49">AG13/AG14</f>
+        <v>12.472203569198667</v>
+      </c>
+      <c r="AH15" s="5">
+        <f t="shared" ref="AH15" si="50">AH13/AH14</f>
+        <v>13.21782914501016</v>
+      </c>
+      <c r="AI15" s="5">
+        <f t="shared" ref="AI15" si="51">AI13/AI14</f>
+        <v>14.003961781486552</v>
+      </c>
+      <c r="AJ15" s="5">
+        <f t="shared" ref="AJ15" si="52">AJ13/AJ14</f>
+        <v>14.832714911516369</v>
+      </c>
+      <c r="AK15" s="5">
+        <f t="shared" ref="AK15" si="53">AK13/AK14</f>
+        <v>15.706310108156247</v>
+      </c>
+    </row>
+    <row r="17" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -2708,105 +2781,109 @@
         <v>0.48442272449602952</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" ref="L17:N17" si="56">L3/H3-1</f>
+        <f t="shared" ref="L17:N17" si="54">L3/H3-1</f>
         <v>0.53661202185792334</v>
       </c>
       <c r="M17" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.67903614457831307</v>
       </c>
       <c r="N17" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.71216973578863074</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" ref="O17" si="57">O3/K3-1</f>
+        <f t="shared" ref="O17" si="55">O3/K3-1</f>
         <v>0.6148148148148147</v>
       </c>
       <c r="P17" s="8">
-        <f t="shared" ref="P17" si="58">P3/L3-1</f>
+        <f t="shared" ref="P17" si="56">P3/L3-1</f>
         <v>0.77667140825035585</v>
       </c>
       <c r="Q17" s="8">
-        <f t="shared" ref="Q17" si="59">Q3/M3-1</f>
+        <f t="shared" ref="Q17" si="57">Q3/M3-1</f>
         <v>0.67881745120551096</v>
       </c>
       <c r="R17" s="8">
-        <f t="shared" ref="R17" si="60">R3/N3-1</f>
-        <v>0.54313771335047933</v>
-      </c>
+        <f t="shared" ref="R17" si="58">R3/N3-1</f>
+        <v>0.69651624970773907</v>
+      </c>
+      <c r="S17" s="8"/>
       <c r="T17" s="8"/>
-      <c r="U17" s="8">
-        <f>U3/T3-1</f>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8">
+        <f>Y3/X3-1</f>
         <v>0.2059397030148491</v>
       </c>
-      <c r="V17" s="8">
-        <f t="shared" ref="V17:AG17" si="61">V3/U3-1</f>
+      <c r="Z17" s="8">
+        <f t="shared" ref="Z17:AK17" si="59">Z3/Y3-1</f>
         <v>0.61728855721393039</v>
       </c>
-      <c r="W17" s="8">
-        <f t="shared" si="61"/>
-        <v>0.64338998692609417</v>
-      </c>
-      <c r="X17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AA17" s="8">
+        <f t="shared" si="59"/>
+        <v>0.69383988310389921</v>
+      </c>
+      <c r="AB17" s="8">
+        <f t="shared" si="59"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="Y17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AC17" s="8">
+        <f t="shared" si="59"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="Z17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AD17" s="8">
+        <f t="shared" si="59"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AA17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AE17" s="8">
+        <f t="shared" si="59"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AB17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AF17" s="8">
+        <f t="shared" si="59"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AC17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AG17" s="8">
+        <f t="shared" si="59"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AH17" s="8">
+        <f t="shared" si="59"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AI17" s="8">
+        <f t="shared" si="59"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AF17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AJ17" s="8">
+        <f t="shared" si="59"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AG17" s="8">
-        <f t="shared" si="61"/>
+      <c r="AK17" s="8">
+        <f t="shared" si="59"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:36" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" ref="G18:J18" si="62">G5/G3</f>
+        <f t="shared" ref="G18:J18" si="60">G5/G3</f>
         <v>0.83567501527183863</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.84262295081967209</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.8727710843373494</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.88430744595676536</v>
       </c>
       <c r="K18" s="8">
@@ -2814,97 +2891,101 @@
         <v>0.88641975308641974</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" ref="L18:N18" si="63">L5/L3</f>
+        <f t="shared" ref="L18:N18" si="61">L5/L3</f>
         <v>0.89509246088193462</v>
       </c>
       <c r="M18" s="8">
+        <f t="shared" si="61"/>
+        <v>0.90068886337543042</v>
+      </c>
+      <c r="N18" s="8">
+        <f t="shared" si="61"/>
+        <v>0.92564881926584053</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" ref="O18:R18" si="62">O5/O3</f>
+        <v>0.90545361875637098</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" si="62"/>
+        <v>0.90812650120096083</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="62"/>
+        <v>0.91024106684903405</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="62"/>
+        <v>0.91910143329658212</v>
+      </c>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="X18" s="8">
+        <f>X5/X3</f>
+        <v>0.84280785960701976</v>
+      </c>
+      <c r="Y18" s="8">
+        <f>Y5/Y3</f>
+        <v>0.86194029850746268</v>
+      </c>
+      <c r="Z18" s="8">
+        <f t="shared" ref="Z18:AK18" si="63">Z5/Z3</f>
+        <v>0.90502191801891874</v>
+      </c>
+      <c r="AA18" s="8">
         <f t="shared" si="63"/>
-        <v>0.90068886337543042</v>
-      </c>
-      <c r="N18" s="8">
+        <v>0.91182746878547105</v>
+      </c>
+      <c r="AB18" s="8">
         <f t="shared" si="63"/>
-        <v>0.92564881926584053</v>
-      </c>
-      <c r="O18" s="8">
-        <f t="shared" ref="O18:R18" si="64">O5/O3</f>
-        <v>0.90545361875637098</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" si="64"/>
-        <v>0.90812650120096083</v>
-      </c>
-      <c r="Q18" s="8">
-        <f t="shared" si="64"/>
-        <v>0.91024106684903405</v>
-      </c>
-      <c r="R18" s="8">
-        <f t="shared" si="64"/>
         <v>0.92</v>
       </c>
-      <c r="T18" s="8">
-        <f>T5/T3</f>
-        <v>0.84280785960701976</v>
-      </c>
-      <c r="U18" s="8">
-        <f>U5/U3</f>
-        <v>0.86194029850746268</v>
-      </c>
-      <c r="V18" s="8">
-        <f t="shared" ref="V18:AG18" si="65">V5/V3</f>
-        <v>0.90502191801891874</v>
-      </c>
-      <c r="W18" s="8">
-        <f t="shared" si="65"/>
-        <v>0.91188169778651318</v>
-      </c>
-      <c r="X18" s="8">
-        <f t="shared" si="65"/>
+      <c r="AC18" s="8">
+        <f t="shared" si="63"/>
+        <v>0.92</v>
+      </c>
+      <c r="AD18" s="8">
+        <f t="shared" si="63"/>
         <v>0.92000000000000015</v>
       </c>
-      <c r="Y18" s="8">
-        <f t="shared" si="65"/>
+      <c r="AE18" s="8">
+        <f t="shared" si="63"/>
+        <v>0.91999999999999993</v>
+      </c>
+      <c r="AF18" s="8">
+        <f t="shared" si="63"/>
+        <v>0.92000000000000015</v>
+      </c>
+      <c r="AG18" s="8">
+        <f t="shared" si="63"/>
+        <v>0.92000000000000015</v>
+      </c>
+      <c r="AH18" s="8">
+        <f t="shared" si="63"/>
+        <v>0.91999999999999993</v>
+      </c>
+      <c r="AI18" s="8">
+        <f t="shared" si="63"/>
         <v>0.92</v>
       </c>
-      <c r="Z18" s="8">
-        <f t="shared" si="65"/>
-        <v>0.91999999999999993</v>
-      </c>
-      <c r="AA18" s="8">
-        <f t="shared" si="65"/>
+      <c r="AJ18" s="8">
+        <f t="shared" si="63"/>
         <v>0.92</v>
       </c>
-      <c r="AB18" s="8">
-        <f t="shared" si="65"/>
-        <v>0.92</v>
-      </c>
-      <c r="AC18" s="8">
-        <f t="shared" si="65"/>
+      <c r="AK18" s="8">
+        <f t="shared" si="63"/>
         <v>0.92000000000000015</v>
       </c>
-      <c r="AD18" s="8">
-        <f t="shared" si="65"/>
-        <v>0.92000000000000015</v>
-      </c>
-      <c r="AE18" s="8">
-        <f t="shared" si="65"/>
-        <v>0.92000000000000015</v>
-      </c>
-      <c r="AF18" s="8">
-        <f t="shared" si="65"/>
-        <v>0.92</v>
-      </c>
-      <c r="AG18" s="8">
-        <f t="shared" si="65"/>
-        <v>0.91999999999999993</v>
-      </c>
-      <c r="AI18" t="s">
+      <c r="AM18" t="s">
         <v>41</v>
       </c>
-      <c r="AJ18" s="8">
+      <c r="AN18" s="8">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="19" spans="2:36" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>36</v>
       </c>
@@ -2917,111 +2998,115 @@
         <v>3.0165441176470589</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" ref="L19:N19" si="66">L6/H6-1</f>
+        <f t="shared" ref="L19:N19" si="64">L6/H6-1</f>
         <v>0.30173199635369197</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.53924284395198518</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.68996415770609332</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" ref="O19" si="67">O6/K6-1</f>
+        <f t="shared" ref="O19" si="65">O6/K6-1</f>
         <v>-0.56224256292906172</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" ref="P19" si="68">P6/L6-1</f>
+        <f t="shared" ref="P19" si="66">P6/L6-1</f>
         <v>0.37675070028011182</v>
       </c>
       <c r="Q19" s="8">
-        <f t="shared" ref="Q19" si="69">Q6/M6-1</f>
+        <f t="shared" ref="Q19" si="67">Q6/M6-1</f>
         <v>0.17816436712657491</v>
       </c>
       <c r="R19" s="8">
-        <f t="shared" ref="R19" si="70">R6/N6-1</f>
-        <v>0.19999999999999996</v>
-      </c>
+        <f t="shared" ref="R19" si="68">R6/N6-1</f>
+        <v>5.4612937433722308E-2</v>
+      </c>
+      <c r="S19" s="8"/>
       <c r="T19" s="8"/>
-      <c r="U19" s="8">
-        <f>U6/T6-1</f>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8">
+        <f>Y6/X6-1</f>
         <v>0.20016429353778764</v>
       </c>
-      <c r="V19" s="8">
-        <f t="shared" ref="V19:AG19" si="71">V6/U6-1</f>
+      <c r="Z19" s="8">
+        <f t="shared" ref="Z19:AK19" si="69">Z6/Y6-1</f>
         <v>1.1334702258726899</v>
       </c>
-      <c r="W19" s="8">
-        <f t="shared" si="71"/>
-        <v>-0.13311945246497714</v>
-      </c>
-      <c r="X19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AA19" s="8">
+        <f t="shared" si="69"/>
+        <v>-0.16244251951662936</v>
+      </c>
+      <c r="AB19" s="8">
+        <f t="shared" si="69"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="Y19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AC19" s="8">
+        <f t="shared" si="69"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="Z19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AD19" s="8">
+        <f t="shared" si="69"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AA19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AE19" s="8">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AB19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AF19" s="8">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AC19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AG19" s="8">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AH19" s="8">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AE19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AI19" s="8">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AF19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AJ19" s="8">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG19" s="8">
-        <f t="shared" si="71"/>
+      <c r="AK19" s="8">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AI19" t="s">
+      <c r="AM19" t="s">
         <v>42</v>
       </c>
-      <c r="AJ19" s="8">
+      <c r="AN19" s="8">
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="2:36" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" ref="G20:J20" si="72">G7/G3</f>
+        <f t="shared" ref="G20:J20" si="70">G7/G3</f>
         <v>0.3536957849725107</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>0.32349726775956283</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>0.26554216867469882</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>0.23178542834267413</v>
       </c>
       <c r="K20" s="8">
@@ -3029,98 +3114,102 @@
         <v>0.51069958847736618</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" ref="L20:N20" si="73">L7/L3</f>
+        <f t="shared" ref="L20:N20" si="71">L7/L3</f>
         <v>0.25426742532005692</v>
       </c>
       <c r="M20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.21383467278989668</v>
+      </c>
+      <c r="N20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.18821603927986907</v>
+      </c>
+      <c r="O20" s="8">
+        <f t="shared" ref="O20:R20" si="72">O7/O3</f>
+        <v>0.2311416921508665</v>
+      </c>
+      <c r="P20" s="8">
+        <f t="shared" si="72"/>
+        <v>0.24139311449159326</v>
+      </c>
+      <c r="Q20" s="8">
+        <f t="shared" si="72"/>
+        <v>0.22003761326722515</v>
+      </c>
+      <c r="R20" s="8">
+        <f t="shared" si="72"/>
+        <v>0.22588202866593166</v>
+      </c>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="X20" s="8">
+        <f>X7/X3</f>
+        <v>0.33763311834408277</v>
+      </c>
+      <c r="Y20" s="8">
+        <f>Y7/Y3</f>
+        <v>0.28631840796019897</v>
+      </c>
+      <c r="Z20" s="8">
+        <f t="shared" ref="Z20:AK20" si="73">Z7/Z3</f>
+        <v>0.26963008536491584</v>
+      </c>
+      <c r="AA20" s="8">
         <f t="shared" si="73"/>
-        <v>0.21383467278989668</v>
-      </c>
-      <c r="N20" s="8">
+        <v>0.22878547105561861</v>
+      </c>
+      <c r="AB20" s="8">
         <f t="shared" si="73"/>
-        <v>0.18821603927986907</v>
-      </c>
-      <c r="O20" s="8">
-        <f t="shared" ref="O20:R20" si="74">O7/O3</f>
-        <v>0.2311416921508665</v>
-      </c>
-      <c r="P20" s="8">
-        <f t="shared" si="74"/>
-        <v>0.24139311449159326</v>
-      </c>
-      <c r="Q20" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22003761326722515</v>
-      </c>
-      <c r="R20" s="8">
-        <f t="shared" si="74"/>
         <v>0.23</v>
       </c>
-      <c r="T20" s="8">
-        <f>T7/T3</f>
-        <v>0.33763311834408277</v>
-      </c>
-      <c r="U20" s="8">
-        <f>U7/U3</f>
-        <v>0.28631840796019897</v>
-      </c>
-      <c r="V20" s="8">
-        <f t="shared" ref="V20:AG20" si="75">V7/V3</f>
-        <v>0.26963008536491584</v>
-      </c>
-      <c r="W20" s="8">
-        <f t="shared" si="75"/>
-        <v>0.2301464738640086</v>
-      </c>
-      <c r="X20" s="8">
-        <f t="shared" si="75"/>
-        <v>0.23000000000000004</v>
-      </c>
-      <c r="Y20" s="8">
-        <f t="shared" si="75"/>
+      <c r="AC20" s="8">
+        <f t="shared" si="73"/>
         <v>0.22</v>
       </c>
-      <c r="Z20" s="8">
-        <f t="shared" si="75"/>
+      <c r="AD20" s="8">
+        <f t="shared" si="73"/>
         <v>0.21</v>
       </c>
-      <c r="AA20" s="8">
-        <f t="shared" si="75"/>
+      <c r="AE20" s="8">
+        <f t="shared" si="73"/>
         <v>0.2</v>
       </c>
-      <c r="AB20" s="8">
-        <f t="shared" si="75"/>
+      <c r="AF20" s="8">
+        <f t="shared" si="73"/>
         <v>0.2</v>
       </c>
-      <c r="AC20" s="8">
-        <f t="shared" si="75"/>
+      <c r="AG20" s="8">
+        <f t="shared" si="73"/>
         <v>0.2</v>
       </c>
-      <c r="AD20" s="8">
-        <f t="shared" si="75"/>
+      <c r="AH20" s="8">
+        <f t="shared" si="73"/>
         <v>0.2</v>
       </c>
-      <c r="AE20" s="8">
-        <f t="shared" si="75"/>
+      <c r="AI20" s="8">
+        <f t="shared" si="73"/>
         <v>0.2</v>
       </c>
-      <c r="AF20" s="8">
-        <f t="shared" si="75"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AG20" s="8">
-        <f t="shared" si="75"/>
+      <c r="AJ20" s="8">
+        <f t="shared" si="73"/>
         <v>0.2</v>
       </c>
-      <c r="AI20" t="s">
+      <c r="AK20" s="8">
+        <f t="shared" si="73"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM20" t="s">
         <v>66</v>
       </c>
-      <c r="AJ20" s="2">
-        <f>NPV(AJ19,W13:EM13)</f>
-        <v>25665.261872429706</v>
-      </c>
-    </row>
-    <row r="21" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="AN20" s="2">
+        <f>NPV(AN19,AB13:EQ13)</f>
+        <v>29039.65374519816</v>
+      </c>
+    </row>
+    <row r="21" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>38</v>
       </c>
@@ -3129,116 +3218,120 @@
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8">
-        <f t="shared" ref="K21" si="76">K8/G8-1</f>
+        <f t="shared" ref="K21" si="74">K8/G8-1</f>
         <v>4.9681372549019613</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" ref="L21" si="77">L8/H8-1</f>
+        <f t="shared" ref="L21" si="75">L8/H8-1</f>
         <v>0.79319371727748678</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" ref="M21" si="78">M8/I8-1</f>
+        <f t="shared" ref="M21" si="76">M8/I8-1</f>
         <v>0.76139410187667589</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" ref="N21" si="79">N8/J8-1</f>
+        <f t="shared" ref="N21" si="77">N8/J8-1</f>
         <v>0.52795031055900621</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" ref="O21" si="80">O8/K8-1</f>
+        <f t="shared" ref="O21" si="78">O8/K8-1</f>
         <v>-0.71498973305954827</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21" si="81">P8/L8-1</f>
+        <f t="shared" ref="P21" si="79">P8/L8-1</f>
         <v>4.3795620437956373E-3</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" ref="Q21" si="82">Q8/M8-1</f>
+        <f t="shared" ref="Q21" si="80">Q8/M8-1</f>
         <v>4.7184170471841647E-2</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" ref="R21" si="83">R8/N8-1</f>
-        <v>0.10000000000000009</v>
-      </c>
+        <f t="shared" ref="R21" si="81">R8/N8-1</f>
+        <v>-2.0325203252032575E-2</v>
+      </c>
+      <c r="S21" s="8"/>
       <c r="T21" s="8"/>
-      <c r="U21" s="8">
-        <f>U8/T8-1</f>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="8">
+        <f>Y8/X8-1</f>
         <v>0.14534075104311528</v>
       </c>
-      <c r="V21" s="8">
-        <f t="shared" ref="V21:AG21" si="84">V8/U8-1</f>
+      <c r="Z21" s="8">
+        <f t="shared" ref="Z21:AK21" si="82">Z8/Y8-1</f>
         <v>1.7413479052823315</v>
       </c>
-      <c r="W21" s="8">
-        <f t="shared" si="84"/>
-        <v>-0.36172757475083051</v>
-      </c>
-      <c r="X21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AA21" s="8">
+        <f t="shared" si="82"/>
+        <v>-0.38139534883720927</v>
+      </c>
+      <c r="AB21" s="8">
+        <f t="shared" si="82"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Y21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AC21" s="8">
+        <f t="shared" si="82"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Z21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AD21" s="8">
+        <f t="shared" si="82"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AA21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AE21" s="8">
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AF21" s="8">
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AG21" s="8">
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AH21" s="8">
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AI21" s="8">
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AJ21" s="8">
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG21" s="8">
-        <f t="shared" si="84"/>
+      <c r="AK21" s="8">
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI21" t="s">
+      <c r="AM21" t="s">
         <v>43</v>
       </c>
-      <c r="AJ21" s="2">
+      <c r="AN21" s="2">
         <f>Main!D8</f>
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="22" spans="2:36" x14ac:dyDescent="0.3">
+        <v>2476.8000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>39</v>
       </c>
       <c r="G22" s="8">
-        <f t="shared" ref="G22:J22" si="85">G9/G3</f>
+        <f t="shared" ref="G22:J22" si="83">G9/G3</f>
         <v>-0.43188759926695186</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>-0.28907103825136632</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>-9.4457831325301181E-2</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>1.2409927942353859E-2</v>
       </c>
       <c r="K22" s="8">
@@ -3246,115 +3339,119 @@
         <v>-2.4246913580246914</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" ref="L22:N22" si="86">L9/L3</f>
+        <f t="shared" ref="L22:N22" si="84">L9/L3</f>
         <v>-0.11059743954480805</v>
       </c>
       <c r="M22" s="8">
+        <f t="shared" si="84"/>
+        <v>1.9804822043627948E-2</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="84"/>
+        <v>0.12391863455693231</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" ref="O22:R22" si="85">O9/O3</f>
+        <v>9.9388379204892394E-3</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="85"/>
+        <v>0.13550840672538039</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" si="85"/>
+        <v>0.23679261412207206</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="85"/>
+        <v>0.3194597574421168</v>
+      </c>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="X22" s="8">
+        <f>X9/X3</f>
+        <v>-0.25828708564571745</v>
+      </c>
+      <c r="Y22" s="8">
+        <f>Y9/Y3</f>
+        <v>-0.17437810945273638</v>
+      </c>
+      <c r="Z22" s="8">
+        <f t="shared" ref="Z22:AK22" si="86">Z9/Z3</f>
+        <v>-0.43097746673844506</v>
+      </c>
+      <c r="AA22" s="8">
         <f t="shared" si="86"/>
-        <v>1.9804822043627948E-2</v>
-      </c>
-      <c r="N22" s="8">
+        <v>0.20063564131668563</v>
+      </c>
+      <c r="AB22" s="8">
         <f t="shared" si="86"/>
-        <v>0.12391863455693231</v>
-      </c>
-      <c r="O22" s="8">
-        <f t="shared" ref="O22:R22" si="87">O9/O3</f>
-        <v>9.9388379204892394E-3</v>
-      </c>
-      <c r="P22" s="8">
-        <f t="shared" si="87"/>
-        <v>0.13550840672538039</v>
-      </c>
-      <c r="Q22" s="8">
-        <f t="shared" si="87"/>
-        <v>0.23679261412207206</v>
-      </c>
-      <c r="R22" s="8">
-        <f t="shared" si="87"/>
-        <v>0.22409090909090915</v>
-      </c>
-      <c r="T22" s="8">
-        <f>T9/T3</f>
-        <v>-0.25828708564571745</v>
-      </c>
-      <c r="U22" s="8">
-        <f>U9/U3</f>
-        <v>-0.17437810945273638</v>
-      </c>
-      <c r="V22" s="8">
-        <f t="shared" ref="V22:AG22" si="88">V9/V3</f>
-        <v>-0.43097746673844506</v>
-      </c>
-      <c r="W22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.16753240675745248</v>
-      </c>
-      <c r="X22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.30627444295140499</v>
-      </c>
-      <c r="Y22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.39159424430686551</v>
-      </c>
-      <c r="Z22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.43177749822097405</v>
-      </c>
-      <c r="AA22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.45531009563926994</v>
-      </c>
-      <c r="AB22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.46342864440460202</v>
+        <v>0.33000681044267877</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.46892511932846648</v>
+        <f t="shared" si="86"/>
+        <v>0.4106715969614948</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.47429948802090632</v>
+        <f t="shared" si="86"/>
+        <v>0.44898926455570792</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.47955457378550009</v>
+        <f t="shared" si="86"/>
+        <v>0.47168611358077173</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.48469313193517</v>
+        <f t="shared" si="86"/>
+        <v>0.47930375098323041</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="88"/>
-        <v>0.48971785149333952</v>
-      </c>
-      <c r="AI22" t="s">
+        <f t="shared" si="86"/>
+        <v>0.48446147345786239</v>
+      </c>
+      <c r="AH22" s="8">
+        <f t="shared" si="86"/>
+        <v>0.48950458125629631</v>
+      </c>
+      <c r="AI22" s="8">
+        <f t="shared" si="86"/>
+        <v>0.49443572529646079</v>
+      </c>
+      <c r="AJ22" s="8">
+        <f t="shared" si="86"/>
+        <v>0.49925749263743002</v>
+      </c>
+      <c r="AK22" s="8">
+        <f t="shared" si="86"/>
+        <v>0.50397240807764776</v>
+      </c>
+      <c r="AM22" t="s">
         <v>44</v>
       </c>
-      <c r="AJ22" s="2">
-        <f>AJ20+AJ21</f>
-        <v>27725.261872429706</v>
-      </c>
-    </row>
-    <row r="23" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="AN22" s="2">
+        <f>AN20+AN21</f>
+        <v>31516.45374519816</v>
+      </c>
+    </row>
+    <row r="23" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="8">
-        <f t="shared" ref="G23:J23" si="89">G12/G11</f>
+        <f t="shared" ref="G23:J23" si="87">G12/G11</f>
         <v>-1.6666666666666663E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>-3.5353535353535318E-2</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>-5.714285714285719E-2</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>4.5918367346938792E-2</v>
       </c>
       <c r="K23" s="8">
@@ -3362,115 +3459,119 @@
         <v>-6.9613644274277764E-4</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" ref="L23:N23" si="90">L12/L11</f>
+        <f t="shared" ref="L23:N23" si="88">L12/L11</f>
         <v>1.923076923076919E-2</v>
       </c>
       <c r="M23" s="8">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="8">
+        <f t="shared" si="88"/>
+        <v>-1.4265335235378044E-2</v>
+      </c>
+      <c r="O23" s="8">
+        <f t="shared" ref="O23:R23" si="89">O12/O11</f>
+        <v>-6.9672131147541047E-2</v>
+      </c>
+      <c r="P23" s="8">
+        <f t="shared" si="89"/>
+        <v>-4.5045045045045027E-3</v>
+      </c>
+      <c r="Q23" s="8">
+        <f t="shared" si="89"/>
+        <v>-1.3084112149532716E-2</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="89"/>
+        <v>1.2558869701726847E-2</v>
+      </c>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="X23" s="8">
+        <f>X12/X11</f>
+        <v>-3.7974683544303835E-3</v>
+      </c>
+      <c r="Y23" s="8">
+        <f>Y12/Y11</f>
+        <v>-4.362801377726748E-2</v>
+      </c>
+      <c r="Z23" s="8">
+        <f t="shared" ref="Z23:AK23" si="90">Z12/Z11</f>
+        <v>1.6494845360824739E-3</v>
+      </c>
+      <c r="AA23" s="8">
         <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="8">
+        <v>-1.8921475875118255E-3</v>
+      </c>
+      <c r="AB23" s="8">
         <f t="shared" si="90"/>
-        <v>-1.4265335235378044E-2</v>
-      </c>
-      <c r="O23" s="8">
-        <f t="shared" ref="O23:R23" si="91">O12/O11</f>
-        <v>-6.9672131147541047E-2</v>
-      </c>
-      <c r="P23" s="8">
-        <f t="shared" si="91"/>
-        <v>-4.5045045045045027E-3</v>
-      </c>
-      <c r="Q23" s="8">
-        <f t="shared" si="91"/>
-        <v>-1.3084112149532716E-2</v>
-      </c>
-      <c r="R23" s="8">
-        <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="8">
-        <f>T12/T11</f>
-        <v>-3.7974683544303835E-3</v>
-      </c>
-      <c r="U23" s="8">
-        <f>U12/U11</f>
-        <v>-4.362801377726748E-2</v>
-      </c>
-      <c r="V23" s="8">
-        <f t="shared" ref="V23:AG23" si="92">V12/V11</f>
-        <v>1.6494845360824739E-3</v>
-      </c>
-      <c r="W23" s="8">
-        <f t="shared" si="92"/>
-        <v>-9.5625584852907317E-3</v>
-      </c>
-      <c r="X23" s="8">
-        <f t="shared" si="92"/>
         <v>0.15</v>
       </c>
-      <c r="Y23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AC23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="Z23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AD23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AA23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AE23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AB23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AF23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AC23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AG23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AD23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AH23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AE23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AI23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AF23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AJ23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AG23" s="8">
-        <f t="shared" si="92"/>
+      <c r="AK23" s="8">
+        <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AI23" t="s">
+      <c r="AM23" t="s">
         <v>45</v>
       </c>
-      <c r="AJ23" s="1">
-        <f>AJ22/AG14</f>
-        <v>147.47479719377503</v>
-      </c>
-    </row>
-    <row r="24" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="AN23" s="1">
+        <f>AN22/AK14</f>
+        <v>165.87607234314819</v>
+      </c>
+    </row>
+    <row r="24" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>40</v>
       </c>
       <c r="G24" s="8">
-        <f t="shared" ref="G24:J24" si="93">G13/G3</f>
+        <f t="shared" ref="G24:J24" si="91">G13/G3</f>
         <v>-0.37263286499694576</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>-0.22404371584699473</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>-3.5662650602409612E-2</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>7.4859887910328243E-2</v>
       </c>
       <c r="K24" s="8">
@@ -3478,260 +3579,251 @@
         <v>-2.3662551440329218</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" ref="L24:N24" si="94">L13/L3</f>
+        <f t="shared" ref="L24:N24" si="92">L13/L3</f>
         <v>-3.627311522048373E-2</v>
       </c>
       <c r="M24" s="8">
+        <f t="shared" si="92"/>
+        <v>8.5820895522388002E-2</v>
+      </c>
+      <c r="N24" s="8">
+        <f t="shared" si="92"/>
+        <v>0.16623801730184695</v>
+      </c>
+      <c r="O24" s="8">
+        <f t="shared" ref="O24:R24" si="93">O13/O3</f>
+        <v>6.6513761467889856E-2</v>
+      </c>
+      <c r="P24" s="8">
+        <f t="shared" si="93"/>
+        <v>0.17854283426741402</v>
+      </c>
+      <c r="Q24" s="8">
+        <f t="shared" si="93"/>
+        <v>0.27799623867327738</v>
+      </c>
+      <c r="R24" s="8">
+        <f t="shared" si="93"/>
+        <v>0.34674751929437703</v>
+      </c>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="X24" s="8">
+        <f>X13/X3</f>
+        <v>-0.23788810559471998</v>
+      </c>
+      <c r="Y24" s="8">
+        <f>Y13/Y3</f>
+        <v>-0.11305970149253737</v>
+      </c>
+      <c r="Z24" s="8">
+        <f t="shared" ref="Z24:AK24" si="94">Z13/Z3</f>
+        <v>-0.3723756056294702</v>
+      </c>
+      <c r="AA24" s="8">
         <f t="shared" si="94"/>
-        <v>8.5820895522388002E-2</v>
-      </c>
-      <c r="N24" s="8">
+        <v>0.24040862656072651</v>
+      </c>
+      <c r="AB24" s="8">
         <f t="shared" si="94"/>
-        <v>0.16623801730184695</v>
-      </c>
-      <c r="O24" s="8">
-        <f t="shared" ref="O24:R24" si="95">O13/O3</f>
-        <v>6.6513761467889856E-2</v>
-      </c>
-      <c r="P24" s="8">
-        <f t="shared" si="95"/>
-        <v>0.17854283426741402</v>
-      </c>
-      <c r="Q24" s="8">
-        <f t="shared" si="95"/>
-        <v>0.27799623867327738</v>
-      </c>
-      <c r="R24" s="8">
-        <f t="shared" si="95"/>
-        <v>0.25077727272727279</v>
-      </c>
-      <c r="T24" s="8">
-        <f>T13/T3</f>
-        <v>-0.23788810559471998</v>
-      </c>
-      <c r="U24" s="8">
-        <f>U13/U3</f>
-        <v>-0.11305970149253737</v>
-      </c>
-      <c r="V24" s="8">
-        <f t="shared" ref="V24:AG24" si="96">V13/V3</f>
-        <v>-0.3723756056294702</v>
-      </c>
-      <c r="W24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.2075029247976041</v>
-      </c>
-      <c r="X24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.28410000852369599</v>
-      </c>
-      <c r="Y24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.35168567225733705</v>
-      </c>
-      <c r="Z24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.38387650960469438</v>
-      </c>
-      <c r="AA24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.40309840092335397</v>
-      </c>
-      <c r="AB24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.40954393662964161</v>
+        <v>0.30509417869304362</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.41391823385996018</v>
+        <f t="shared" si="94"/>
+        <v>0.36855242781055492</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.41819441139270996</v>
+        <f t="shared" si="94"/>
+        <v>0.39908958574633691</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.42237476102452054</v>
+        <f t="shared" si="94"/>
+        <v>0.41757409672903067</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.4264615188173238</v>
+        <f t="shared" si="94"/>
+        <v>0.42357811964794956</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="96"/>
-        <v>0.4304568665051503</v>
-      </c>
-      <c r="AI24" t="s">
+        <f t="shared" si="94"/>
+        <v>0.42765418505972574</v>
+      </c>
+      <c r="AH24" s="8">
+        <f t="shared" si="94"/>
+        <v>0.43163869463847948</v>
+      </c>
+      <c r="AI24" s="8">
+        <f t="shared" si="94"/>
+        <v>0.43553378991889302</v>
+      </c>
+      <c r="AJ24" s="8">
+        <f t="shared" si="94"/>
+        <v>0.4393415602841092</v>
+      </c>
+      <c r="AK24" s="8">
+        <f t="shared" si="94"/>
+        <v>0.44306404428367918</v>
+      </c>
+      <c r="AM24" t="s">
         <v>46</v>
       </c>
-      <c r="AJ24" s="1">
+      <c r="AN24" s="1">
         <f>Main!D3</f>
-        <v>218.54</v>
-      </c>
-    </row>
-    <row r="25" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="AI25" s="6" t="s">
+        <v>165.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AM25" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AJ25" s="9">
-        <f>AJ23/AJ24-1</f>
-        <v>-0.32518167294877354</v>
-      </c>
-    </row>
-    <row r="26" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="AI26" t="s">
+      <c r="AN25" s="9">
+        <f>AN23/AN24-1</f>
+        <v>4.7006198858159376E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AM26" t="s">
         <v>48</v>
       </c>
-      <c r="AJ26" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="2:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AN26" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="2:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="T27" s="7">
-        <f>T13</f>
+      <c r="X27" s="7">
+        <f>X13</f>
         <v>-158.59999999999982</v>
       </c>
-      <c r="U27" s="7">
-        <f>U13</f>
+      <c r="Y27" s="7">
+        <f>Y13</f>
         <v>-90.900000000000048</v>
       </c>
-      <c r="V27" s="7">
-        <f>V13</f>
+      <c r="Z27" s="7">
+        <f>Z13</f>
         <v>-484.2000000000001</v>
       </c>
-      <c r="W27" s="7">
-        <f t="shared" ref="W27:AG27" si="97">W13</f>
-        <v>443.41300000000024</v>
-      </c>
-      <c r="X27" s="7">
-        <f t="shared" si="97"/>
-        <v>849.93063150000023</v>
-      </c>
-      <c r="Y27" s="7">
-        <f t="shared" si="97"/>
-        <v>1367.7611457450005</v>
-      </c>
-      <c r="Z27" s="7">
-        <f t="shared" si="97"/>
-        <v>1716.8998580923499</v>
-      </c>
       <c r="AA27" s="7">
-        <f t="shared" si="97"/>
-        <v>1947.1000064569305</v>
+        <f t="shared" ref="AA27:AK27" si="95">AA13</f>
+        <v>529.50000000000011</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="97"/>
-        <v>2096.9281441432745</v>
+        <f t="shared" si="95"/>
+        <v>940.75790000000006</v>
       </c>
       <c r="AC27" s="7">
-        <f t="shared" si="97"/>
-        <v>2225.2914819172015</v>
+        <f t="shared" si="95"/>
+        <v>1477.3608345</v>
       </c>
       <c r="AD27" s="7">
-        <f t="shared" si="97"/>
-        <v>2360.6949503486853</v>
+        <f t="shared" si="95"/>
+        <v>1839.7361427850003</v>
       </c>
       <c r="AE27" s="7">
-        <f t="shared" si="97"/>
-        <v>2503.5075440007063</v>
+        <f t="shared" si="95"/>
+        <v>2078.9423736403996</v>
       </c>
       <c r="AF27" s="7">
-        <f t="shared" si="97"/>
-        <v>2654.1171833876397</v>
+        <f t="shared" si="95"/>
+        <v>2235.364163830649</v>
       </c>
       <c r="AG27" s="7">
-        <f t="shared" si="97"/>
-        <v>2812.9316748911651</v>
-      </c>
-    </row>
-    <row r="28" spans="2:36" x14ac:dyDescent="0.3">
+        <f t="shared" si="95"/>
+        <v>2369.7186781477467</v>
+      </c>
+      <c r="AH27" s="7">
+        <f t="shared" si="95"/>
+        <v>2511.3875375519306</v>
+      </c>
+      <c r="AI27" s="7">
+        <f t="shared" si="95"/>
+        <v>2660.7527384824448</v>
+      </c>
+      <c r="AJ27" s="7">
+        <f t="shared" si="95"/>
+        <v>2818.2158331881101</v>
+      </c>
+      <c r="AK27" s="7">
+        <f t="shared" si="95"/>
+        <v>2984.198920549687</v>
+      </c>
+    </row>
+    <row r="28" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>50</v>
       </c>
-      <c r="T28" s="2">
+      <c r="X28" s="2">
         <v>8</v>
       </c>
-      <c r="U28" s="2">
+      <c r="Y28" s="2">
         <v>13.7</v>
       </c>
-      <c r="V28" s="2">
+      <c r="Z28" s="2">
         <v>15.6</v>
       </c>
-      <c r="W28">
-        <f>V28*1.2</f>
-        <v>18.72</v>
-      </c>
-      <c r="X28">
-        <f t="shared" ref="X28:Z28" si="98">W28*1.2</f>
-        <v>22.463999999999999</v>
-      </c>
-      <c r="Y28">
-        <f t="shared" si="98"/>
-        <v>26.956799999999998</v>
-      </c>
-      <c r="Z28">
-        <f t="shared" si="98"/>
-        <v>32.348159999999993</v>
-      </c>
       <c r="AA28">
-        <f>Z28*1.05</f>
-        <v>33.965567999999998</v>
+        <v>15.9</v>
       </c>
       <c r="AB28">
-        <f t="shared" ref="AB28:AG28" si="99">AA28*1.05</f>
-        <v>35.663846399999997</v>
+        <f t="shared" ref="AB28:AD28" si="96">AA28*1.2</f>
+        <v>19.079999999999998</v>
       </c>
       <c r="AC28">
-        <f t="shared" si="99"/>
-        <v>37.447038720000002</v>
+        <f t="shared" si="96"/>
+        <v>22.895999999999997</v>
       </c>
       <c r="AD28">
-        <f t="shared" si="99"/>
-        <v>39.319390656000003</v>
+        <f t="shared" si="96"/>
+        <v>27.475199999999997</v>
       </c>
       <c r="AE28">
-        <f t="shared" si="99"/>
-        <v>41.285360188800006</v>
+        <f>AD28*1.05</f>
+        <v>28.848959999999998</v>
       </c>
       <c r="AF28">
-        <f t="shared" si="99"/>
-        <v>43.349628198240005</v>
+        <f t="shared" ref="AF28:AK28" si="97">AE28*1.05</f>
+        <v>30.291408000000001</v>
       </c>
       <c r="AG28">
-        <f t="shared" si="99"/>
-        <v>45.517109608152005</v>
-      </c>
-    </row>
-    <row r="29" spans="2:36" x14ac:dyDescent="0.3">
+        <f t="shared" si="97"/>
+        <v>31.805978400000001</v>
+      </c>
+      <c r="AH28">
+        <f t="shared" si="97"/>
+        <v>33.396277320000003</v>
+      </c>
+      <c r="AI28">
+        <f t="shared" si="97"/>
+        <v>35.066091186000001</v>
+      </c>
+      <c r="AJ28">
+        <f t="shared" si="97"/>
+        <v>36.8193957453</v>
+      </c>
+      <c r="AK28">
+        <f t="shared" si="97"/>
+        <v>38.660365532565002</v>
+      </c>
+    </row>
+    <row r="29" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>51</v>
       </c>
-      <c r="T29" s="2">
+      <c r="X29" s="2">
         <v>10.5</v>
       </c>
-      <c r="U29" s="2">
+      <c r="Y29" s="2">
         <v>11.4</v>
       </c>
-      <c r="V29" s="2">
+      <c r="Z29" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="W29" s="2">
-        <v>10</v>
-      </c>
-      <c r="X29" s="2">
-        <v>10</v>
-      </c>
-      <c r="Y29" s="2">
-        <v>10</v>
-      </c>
-      <c r="Z29" s="2">
-        <v>10</v>
-      </c>
       <c r="AA29" s="2">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AB29" s="2">
         <v>10</v>
@@ -3751,34 +3843,34 @@
       <c r="AG29" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="AH29" s="2">
+        <v>10</v>
+      </c>
+      <c r="AI29" s="2">
+        <v>10</v>
+      </c>
+      <c r="AJ29" s="2">
+        <v>10</v>
+      </c>
+      <c r="AK29" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>52</v>
       </c>
-      <c r="T30" s="2">
+      <c r="X30" s="2">
         <v>-3.3</v>
       </c>
-      <c r="U30" s="2">
+      <c r="Y30" s="2">
         <v>-27.4</v>
       </c>
-      <c r="V30" s="2">
+      <c r="Z30" s="2">
         <v>-43.4</v>
       </c>
-      <c r="W30" s="2">
-        <v>0</v>
-      </c>
-      <c r="X30" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="2">
-        <v>0</v>
-      </c>
       <c r="AA30" s="2">
-        <v>0</v>
+        <v>-28.2</v>
       </c>
       <c r="AB30" s="2">
         <v>0</v>
@@ -3798,92 +3890,91 @@
       <c r="AG30" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="AH30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>53</v>
       </c>
-      <c r="T31" s="2">
+      <c r="X31" s="2">
         <v>55.3</v>
       </c>
-      <c r="U31" s="2">
+      <c r="Y31" s="2">
         <v>47.6</v>
       </c>
-      <c r="V31" s="2">
+      <c r="Z31" s="2">
         <v>801.6</v>
       </c>
-      <c r="W31">
-        <f>V31*0.4</f>
-        <v>320.64000000000004</v>
-      </c>
-      <c r="X31">
-        <f>W31*0.8</f>
-        <v>256.51200000000006</v>
-      </c>
-      <c r="Y31">
-        <f>X31*0.8</f>
-        <v>205.20960000000005</v>
-      </c>
-      <c r="Z31">
-        <f>Y31*0.95</f>
-        <v>194.94912000000005</v>
-      </c>
       <c r="AA31">
-        <f>Z31*1.03</f>
-        <v>200.79759360000006</v>
+        <v>343.2</v>
       </c>
       <c r="AB31">
-        <f t="shared" ref="AB31:AG31" si="100">AA31*1.03</f>
-        <v>206.82152140800005</v>
+        <f>AA31*0.8</f>
+        <v>274.56</v>
       </c>
       <c r="AC31">
-        <f t="shared" si="100"/>
-        <v>213.02616705024005</v>
+        <f>AB31*0.8</f>
+        <v>219.64800000000002</v>
       </c>
       <c r="AD31">
-        <f t="shared" si="100"/>
-        <v>219.41695206174725</v>
+        <f>AC31*0.95</f>
+        <v>208.66560000000001</v>
       </c>
       <c r="AE31">
-        <f t="shared" si="100"/>
-        <v>225.99946062359967</v>
+        <f>AD31*1.03</f>
+        <v>214.92556800000003</v>
       </c>
       <c r="AF31">
-        <f t="shared" si="100"/>
-        <v>232.77944444230766</v>
+        <f t="shared" ref="AF31:AK31" si="98">AE31*1.03</f>
+        <v>221.37333504000003</v>
       </c>
       <c r="AG31">
-        <f t="shared" si="100"/>
-        <v>239.76282777557691</v>
-      </c>
-    </row>
-    <row r="32" spans="2:36" x14ac:dyDescent="0.3">
+        <f t="shared" si="98"/>
+        <v>228.01453509120003</v>
+      </c>
+      <c r="AH31">
+        <f t="shared" si="98"/>
+        <v>234.85497114393604</v>
+      </c>
+      <c r="AI31">
+        <f t="shared" si="98"/>
+        <v>241.90062027825414</v>
+      </c>
+      <c r="AJ31">
+        <f t="shared" si="98"/>
+        <v>249.15763888660177</v>
+      </c>
+      <c r="AK31">
+        <f t="shared" si="98"/>
+        <v>256.63236805319985</v>
+      </c>
+    </row>
+    <row r="32" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>54</v>
       </c>
-      <c r="T32" s="2">
+      <c r="X32" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="U32" s="2">
+      <c r="Y32" s="2">
         <v>0.5</v>
       </c>
-      <c r="V32" s="2">
+      <c r="Z32" s="2">
         <v>-4.2</v>
       </c>
-      <c r="W32" s="2">
-        <v>0</v>
-      </c>
-      <c r="X32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="2">
-        <v>0</v>
-      </c>
       <c r="AA32" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AB32" s="2">
         <v>0</v>
@@ -3903,34 +3994,34 @@
       <c r="AG32" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AH32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>55</v>
       </c>
-      <c r="T33" s="2">
+      <c r="X33" s="2">
         <v>-30.2</v>
       </c>
-      <c r="U33" s="2">
+      <c r="Y33" s="2">
         <v>-53.3</v>
       </c>
-      <c r="V33" s="2">
+      <c r="Z33" s="2">
         <v>-104.3</v>
       </c>
-      <c r="W33" s="2">
-        <v>0</v>
-      </c>
-      <c r="X33" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="2">
-        <v>0</v>
-      </c>
       <c r="AA33" s="2">
-        <v>0</v>
+        <v>-241.4</v>
       </c>
       <c r="AB33" s="2">
         <v>0</v>
@@ -3950,34 +4041,34 @@
       <c r="AG33" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AH33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>56</v>
       </c>
-      <c r="T34" s="2">
+      <c r="X34" s="2">
         <v>-1.9</v>
       </c>
-      <c r="U34" s="2">
+      <c r="Y34" s="2">
         <v>3.9</v>
       </c>
-      <c r="V34" s="2">
+      <c r="Z34" s="2">
         <v>-19.5</v>
       </c>
-      <c r="W34" s="2">
-        <v>0</v>
-      </c>
-      <c r="X34" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="2">
-        <v>0</v>
-      </c>
       <c r="AA34" s="2">
-        <v>0</v>
+        <v>-37.1</v>
       </c>
       <c r="AB34" s="2">
         <v>0</v>
@@ -3997,34 +4088,34 @@
       <c r="AG34" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AH34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>51</v>
       </c>
-      <c r="T35" s="2">
+      <c r="X35" s="2">
         <v>-10.3</v>
       </c>
-      <c r="U35" s="2">
+      <c r="Y35" s="2">
         <v>-5.8</v>
       </c>
-      <c r="V35" s="2">
+      <c r="Z35" s="2">
         <v>-2.4</v>
       </c>
-      <c r="W35" s="2">
-        <v>0</v>
-      </c>
-      <c r="X35" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="2">
-        <v>0</v>
-      </c>
       <c r="AA35" s="2">
-        <v>0</v>
+        <v>-7.2</v>
       </c>
       <c r="AB35" s="2">
         <v>0</v>
@@ -4044,34 +4135,34 @@
       <c r="AG35" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AH35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>57</v>
       </c>
-      <c r="T36" s="2">
+      <c r="X36" s="2">
         <v>10.9</v>
       </c>
-      <c r="U36" s="2">
+      <c r="Y36" s="2">
         <v>12.5</v>
       </c>
-      <c r="V36" s="2">
+      <c r="Z36" s="2">
         <v>-0.6</v>
       </c>
-      <c r="W36" s="2">
-        <v>0</v>
-      </c>
-      <c r="X36" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="2">
-        <v>0</v>
-      </c>
       <c r="AA36" s="2">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="AB36" s="2">
         <v>0</v>
@@ -4091,34 +4182,34 @@
       <c r="AG36" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AH36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>58</v>
       </c>
-      <c r="T37" s="2">
+      <c r="X37" s="2">
         <v>21.5</v>
       </c>
-      <c r="U37" s="2">
+      <c r="Y37" s="2">
         <v>12.7</v>
       </c>
-      <c r="V37" s="2">
+      <c r="Z37" s="2">
         <v>59.3</v>
       </c>
-      <c r="W37" s="2">
-        <v>0</v>
-      </c>
-      <c r="X37" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="2">
-        <v>0</v>
-      </c>
       <c r="AA37" s="2">
-        <v>0</v>
+        <v>90.7</v>
       </c>
       <c r="AB37" s="2">
         <v>0</v>
@@ -4138,654 +4229,676 @@
       <c r="AG37" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AH37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:148" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T38" s="7">
-        <f>T27+SUM(T28:T37)</f>
+      <c r="X38" s="7">
+        <f>X27+SUM(X28:X37)</f>
         <v>-93.999999999999829</v>
       </c>
-      <c r="U38" s="7">
-        <f>U27+SUM(U28:U37)</f>
+      <c r="Y38" s="7">
+        <f>Y27+SUM(Y28:Y37)</f>
         <v>-75.100000000000037</v>
       </c>
-      <c r="V38" s="7">
-        <f>V27+SUM(V28:V37)</f>
+      <c r="Z38" s="7">
+        <f>Z27+SUM(Z28:Z37)</f>
         <v>221.99999999999983</v>
       </c>
-      <c r="W38" s="7">
-        <f t="shared" ref="W38" si="101">W27+SUM(W28:W37)</f>
-        <v>792.77300000000025</v>
-      </c>
-      <c r="X38" s="7">
-        <f t="shared" ref="X38" si="102">X27+SUM(X28:X37)</f>
-        <v>1138.9066315000002</v>
-      </c>
-      <c r="Y38" s="7">
-        <f t="shared" ref="Y38" si="103">Y27+SUM(Y28:Y37)</f>
-        <v>1609.9275457450005</v>
-      </c>
-      <c r="Z38" s="7">
-        <f t="shared" ref="Z38" si="104">Z27+SUM(Z28:Z37)</f>
-        <v>1954.1971380923499</v>
-      </c>
       <c r="AA38" s="7">
-        <f t="shared" ref="AA38" si="105">AA27+SUM(AA28:AA37)</f>
-        <v>2191.8631680569306</v>
+        <f t="shared" ref="AA38" si="99">AA27+SUM(AA28:AA37)</f>
+        <v>690.60000000000014</v>
       </c>
       <c r="AB38" s="7">
-        <f t="shared" ref="AB38" si="106">AB27+SUM(AB28:AB37)</f>
-        <v>2349.4135119512744</v>
+        <f t="shared" ref="AB38" si="100">AB27+SUM(AB28:AB37)</f>
+        <v>1244.3978999999999</v>
       </c>
       <c r="AC38" s="7">
-        <f t="shared" ref="AC38" si="107">AC27+SUM(AC28:AC37)</f>
-        <v>2485.7646876874414</v>
+        <f t="shared" ref="AC38" si="101">AC27+SUM(AC28:AC37)</f>
+        <v>1729.9048345000001</v>
       </c>
       <c r="AD38" s="7">
-        <f t="shared" ref="AD38" si="108">AD27+SUM(AD28:AD37)</f>
-        <v>2629.4312930664328</v>
+        <f t="shared" ref="AD38" si="102">AD27+SUM(AD28:AD37)</f>
+        <v>2085.8769427850002</v>
       </c>
       <c r="AE38" s="7">
-        <f t="shared" ref="AE38" si="109">AE27+SUM(AE28:AE37)</f>
-        <v>2780.7923648131059</v>
+        <f t="shared" ref="AE38" si="103">AE27+SUM(AE28:AE37)</f>
+        <v>2332.7169016403996</v>
       </c>
       <c r="AF38" s="7">
-        <f t="shared" ref="AF38" si="110">AF27+SUM(AF28:AF37)</f>
-        <v>2940.2462560281874</v>
+        <f t="shared" ref="AF38" si="104">AF27+SUM(AF28:AF37)</f>
+        <v>2497.0289068706488</v>
       </c>
       <c r="AG38" s="7">
-        <f t="shared" ref="AG38" si="111">AG27+SUM(AG28:AG37)</f>
-        <v>3108.2116122748939</v>
-      </c>
-    </row>
-    <row r="39" spans="2:144" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AG38" si="105">AG27+SUM(AG28:AG37)</f>
+        <v>2639.5391916389467</v>
+      </c>
+      <c r="AH38" s="7">
+        <f t="shared" ref="AH38" si="106">AH27+SUM(AH28:AH37)</f>
+        <v>2789.6387860158666</v>
+      </c>
+      <c r="AI38" s="7">
+        <f t="shared" ref="AI38" si="107">AI27+SUM(AI28:AI37)</f>
+        <v>2947.7194499466991</v>
+      </c>
+      <c r="AJ38" s="7">
+        <f t="shared" ref="AJ38" si="108">AJ27+SUM(AJ28:AJ37)</f>
+        <v>3114.192867820012</v>
+      </c>
+      <c r="AK38" s="7">
+        <f t="shared" ref="AK38" si="109">AK27+SUM(AK28:AK37)</f>
+        <v>3289.4916541354519</v>
+      </c>
+    </row>
+    <row r="39" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>60</v>
       </c>
-      <c r="T39" s="2">
-        <v>6.2</v>
-      </c>
-      <c r="U39" s="2">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="V39" s="2">
-        <v>6.2</v>
-      </c>
-      <c r="W39" s="2">
-        <v>6.2</v>
-      </c>
       <c r="X39" s="2">
         <v>6.2</v>
       </c>
       <c r="Y39" s="2">
-        <v>6.2</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="Z39" s="2">
         <v>6.2</v>
       </c>
       <c r="AA39" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="AB39" s="2">
-        <v>6.2</v>
+        <f>AA39*1.2</f>
+        <v>8.0399999999999991</v>
       </c>
       <c r="AC39" s="2">
-        <v>6.2</v>
+        <f t="shared" ref="AC39:AK39" si="110">AB39*1.2</f>
+        <v>9.6479999999999979</v>
       </c>
       <c r="AD39" s="2">
-        <v>6.2</v>
+        <f t="shared" si="110"/>
+        <v>11.577599999999997</v>
       </c>
       <c r="AE39" s="2">
-        <v>6.2</v>
+        <f t="shared" si="110"/>
+        <v>13.893119999999996</v>
       </c>
       <c r="AF39" s="2">
-        <v>6.2</v>
+        <f t="shared" si="110"/>
+        <v>16.671743999999993</v>
       </c>
       <c r="AG39" s="2">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="40" spans="2:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="110"/>
+        <v>20.00609279999999</v>
+      </c>
+      <c r="AH39" s="2">
+        <f t="shared" si="110"/>
+        <v>24.007311359999989</v>
+      </c>
+      <c r="AI39" s="2">
+        <f t="shared" si="110"/>
+        <v>28.808773631999983</v>
+      </c>
+      <c r="AJ39" s="2">
+        <f t="shared" si="110"/>
+        <v>34.570528358399976</v>
+      </c>
+      <c r="AK39" s="2">
+        <f t="shared" si="110"/>
+        <v>41.484634030079967</v>
+      </c>
+    </row>
+    <row r="40" spans="2:148" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="T40" s="7">
-        <f>T38-T39</f>
+      <c r="X40" s="7">
+        <f>X38-X39</f>
         <v>-100.19999999999983</v>
       </c>
-      <c r="U40" s="7">
-        <f>U38-U39</f>
+      <c r="Y40" s="7">
+        <f>Y38-Y39</f>
         <v>-84.80000000000004</v>
       </c>
-      <c r="V40" s="7">
-        <f>V38-V39</f>
+      <c r="Z40" s="7">
+        <f>Z38-Z39</f>
         <v>215.79999999999984</v>
       </c>
-      <c r="W40" s="7">
-        <f t="shared" ref="W40" si="112">W38-W39</f>
-        <v>786.57300000000021</v>
-      </c>
-      <c r="X40" s="7">
-        <f t="shared" ref="X40" si="113">X38-X39</f>
-        <v>1132.7066315000002</v>
-      </c>
-      <c r="Y40" s="7">
-        <f t="shared" ref="Y40" si="114">Y38-Y39</f>
-        <v>1603.7275457450005</v>
-      </c>
-      <c r="Z40" s="7">
-        <f t="shared" ref="Z40" si="115">Z38-Z39</f>
-        <v>1947.9971380923498</v>
-      </c>
       <c r="AA40" s="7">
-        <f t="shared" ref="AA40" si="116">AA38-AA39</f>
-        <v>2185.6631680569308</v>
+        <f t="shared" ref="AA40" si="111">AA38-AA39</f>
+        <v>683.90000000000009</v>
       </c>
       <c r="AB40" s="7">
-        <f t="shared" ref="AB40" si="117">AB38-AB39</f>
-        <v>2343.2135119512745</v>
+        <f t="shared" ref="AB40" si="112">AB38-AB39</f>
+        <v>1236.3579</v>
       </c>
       <c r="AC40" s="7">
-        <f t="shared" ref="AC40" si="118">AC38-AC39</f>
-        <v>2479.5646876874416</v>
+        <f t="shared" ref="AC40" si="113">AC38-AC39</f>
+        <v>1720.2568345000002</v>
       </c>
       <c r="AD40" s="7">
-        <f t="shared" ref="AD40" si="119">AD38-AD39</f>
-        <v>2623.231293066433</v>
+        <f t="shared" ref="AD40" si="114">AD38-AD39</f>
+        <v>2074.2993427850001</v>
       </c>
       <c r="AE40" s="7">
-        <f t="shared" ref="AE40" si="120">AE38-AE39</f>
-        <v>2774.5923648131061</v>
+        <f t="shared" ref="AE40" si="115">AE38-AE39</f>
+        <v>2318.8237816403994</v>
       </c>
       <c r="AF40" s="7">
-        <f t="shared" ref="AF40" si="121">AF38-AF39</f>
-        <v>2934.0462560281876</v>
+        <f t="shared" ref="AF40" si="116">AF38-AF39</f>
+        <v>2480.3571628706486</v>
       </c>
       <c r="AG40" s="7">
-        <f t="shared" ref="AG40" si="122">AG38-AG39</f>
-        <v>3102.0116122748941</v>
-      </c>
-      <c r="AH40" s="6">
-        <f>AG40*(1+$AJ$18)</f>
-        <v>3070.9914961521449</v>
-      </c>
-      <c r="AI40" s="6">
-        <f t="shared" ref="AI40:CT40" si="123">AH40*(1+$AJ$18)</f>
-        <v>3040.2815811906235</v>
-      </c>
-      <c r="AJ40" s="6">
+        <f t="shared" ref="AG40" si="117">AG38-AG39</f>
+        <v>2619.5330988389469</v>
+      </c>
+      <c r="AH40" s="7">
+        <f t="shared" ref="AH40" si="118">AH38-AH39</f>
+        <v>2765.6314746558664</v>
+      </c>
+      <c r="AI40" s="7">
+        <f t="shared" ref="AI40" si="119">AI38-AI39</f>
+        <v>2918.9106763146992</v>
+      </c>
+      <c r="AJ40" s="7">
+        <f t="shared" ref="AJ40" si="120">AJ38-AJ39</f>
+        <v>3079.6223394616122</v>
+      </c>
+      <c r="AK40" s="7">
+        <f t="shared" ref="AK40" si="121">AK38-AK39</f>
+        <v>3248.0070201053718</v>
+      </c>
+      <c r="AL40" s="6">
+        <f>AK40*(1+$AN$18)</f>
+        <v>3215.5269499043179</v>
+      </c>
+      <c r="AM40" s="6">
+        <f t="shared" ref="AM40:CX40" si="122">AL40*(1+$AN$18)</f>
+        <v>3183.3716804052747</v>
+      </c>
+      <c r="AN40" s="6">
+        <f t="shared" si="122"/>
+        <v>3151.5379636012217</v>
+      </c>
+      <c r="AO40" s="6">
+        <f t="shared" si="122"/>
+        <v>3120.0225839652094</v>
+      </c>
+      <c r="AP40" s="6">
+        <f t="shared" si="122"/>
+        <v>3088.8223581255575</v>
+      </c>
+      <c r="AQ40" s="6">
+        <f t="shared" si="122"/>
+        <v>3057.9341345443017</v>
+      </c>
+      <c r="AR40" s="6">
+        <f t="shared" si="122"/>
+        <v>3027.3547931988587</v>
+      </c>
+      <c r="AS40" s="6">
+        <f t="shared" si="122"/>
+        <v>2997.0812452668702</v>
+      </c>
+      <c r="AT40" s="6">
+        <f t="shared" si="122"/>
+        <v>2967.1104328142014</v>
+      </c>
+      <c r="AU40" s="6">
+        <f t="shared" si="122"/>
+        <v>2937.4393284860594</v>
+      </c>
+      <c r="AV40" s="6">
+        <f t="shared" si="122"/>
+        <v>2908.0649352011988</v>
+      </c>
+      <c r="AW40" s="6">
+        <f t="shared" si="122"/>
+        <v>2878.9842858491866</v>
+      </c>
+      <c r="AX40" s="6">
+        <f t="shared" si="122"/>
+        <v>2850.1944429906948</v>
+      </c>
+      <c r="AY40" s="6">
+        <f t="shared" si="122"/>
+        <v>2821.692498560788</v>
+      </c>
+      <c r="AZ40" s="6">
+        <f t="shared" si="122"/>
+        <v>2793.4755735751801</v>
+      </c>
+      <c r="BA40" s="6">
+        <f t="shared" si="122"/>
+        <v>2765.5408178394282</v>
+      </c>
+      <c r="BB40" s="6">
+        <f t="shared" si="122"/>
+        <v>2737.8854096610339</v>
+      </c>
+      <c r="BC40" s="6">
+        <f t="shared" si="122"/>
+        <v>2710.5065555644237</v>
+      </c>
+      <c r="BD40" s="6">
+        <f t="shared" si="122"/>
+        <v>2683.4014900087795</v>
+      </c>
+      <c r="BE40" s="6">
+        <f t="shared" si="122"/>
+        <v>2656.5674751086917</v>
+      </c>
+      <c r="BF40" s="6">
+        <f t="shared" si="122"/>
+        <v>2630.0018003576047</v>
+      </c>
+      <c r="BG40" s="6">
+        <f t="shared" si="122"/>
+        <v>2603.7017823540286</v>
+      </c>
+      <c r="BH40" s="6">
+        <f t="shared" si="122"/>
+        <v>2577.6647645304884</v>
+      </c>
+      <c r="BI40" s="6">
+        <f t="shared" si="122"/>
+        <v>2551.8881168851835</v>
+      </c>
+      <c r="BJ40" s="6">
+        <f t="shared" si="122"/>
+        <v>2526.3692357163318</v>
+      </c>
+      <c r="BK40" s="6">
+        <f t="shared" si="122"/>
+        <v>2501.1055433591682</v>
+      </c>
+      <c r="BL40" s="6">
+        <f t="shared" si="122"/>
+        <v>2476.0944879255767</v>
+      </c>
+      <c r="BM40" s="6">
+        <f t="shared" si="122"/>
+        <v>2451.3335430463208</v>
+      </c>
+      <c r="BN40" s="6">
+        <f t="shared" si="122"/>
+        <v>2426.8202076158577</v>
+      </c>
+      <c r="BO40" s="6">
+        <f t="shared" si="122"/>
+        <v>2402.5520055396992</v>
+      </c>
+      <c r="BP40" s="6">
+        <f t="shared" si="122"/>
+        <v>2378.5264854843022</v>
+      </c>
+      <c r="BQ40" s="6">
+        <f t="shared" si="122"/>
+        <v>2354.7412206294589</v>
+      </c>
+      <c r="BR40" s="6">
+        <f t="shared" si="122"/>
+        <v>2331.1938084231642</v>
+      </c>
+      <c r="BS40" s="6">
+        <f t="shared" si="122"/>
+        <v>2307.8818703389325</v>
+      </c>
+      <c r="BT40" s="6">
+        <f t="shared" si="122"/>
+        <v>2284.8030516355429</v>
+      </c>
+      <c r="BU40" s="6">
+        <f t="shared" si="122"/>
+        <v>2261.9550211191877</v>
+      </c>
+      <c r="BV40" s="6">
+        <f t="shared" si="122"/>
+        <v>2239.3354709079958</v>
+      </c>
+      <c r="BW40" s="6">
+        <f t="shared" si="122"/>
+        <v>2216.9421161989158</v>
+      </c>
+      <c r="BX40" s="6">
+        <f t="shared" si="122"/>
+        <v>2194.7726950369265</v>
+      </c>
+      <c r="BY40" s="6">
+        <f t="shared" si="122"/>
+        <v>2172.8249680865574</v>
+      </c>
+      <c r="BZ40" s="6">
+        <f t="shared" si="122"/>
+        <v>2151.0967184056917</v>
+      </c>
+      <c r="CA40" s="6">
+        <f t="shared" si="122"/>
+        <v>2129.5857512216348</v>
+      </c>
+      <c r="CB40" s="6">
+        <f t="shared" si="122"/>
+        <v>2108.2898937094183</v>
+      </c>
+      <c r="CC40" s="6">
+        <f t="shared" si="122"/>
+        <v>2087.2069947723239</v>
+      </c>
+      <c r="CD40" s="6">
+        <f t="shared" si="122"/>
+        <v>2066.3349248246009</v>
+      </c>
+      <c r="CE40" s="6">
+        <f t="shared" si="122"/>
+        <v>2045.6715755763548</v>
+      </c>
+      <c r="CF40" s="6">
+        <f t="shared" si="122"/>
+        <v>2025.2148598205913</v>
+      </c>
+      <c r="CG40" s="6">
+        <f t="shared" si="122"/>
+        <v>2004.9627112223855</v>
+      </c>
+      <c r="CH40" s="6">
+        <f t="shared" si="122"/>
+        <v>1984.9130841101617</v>
+      </c>
+      <c r="CI40" s="6">
+        <f t="shared" si="122"/>
+        <v>1965.06395326906</v>
+      </c>
+      <c r="CJ40" s="6">
+        <f t="shared" si="122"/>
+        <v>1945.4133137363694</v>
+      </c>
+      <c r="CK40" s="6">
+        <f t="shared" si="122"/>
+        <v>1925.9591805990058</v>
+      </c>
+      <c r="CL40" s="6">
+        <f t="shared" si="122"/>
+        <v>1906.6995887930157</v>
+      </c>
+      <c r="CM40" s="6">
+        <f t="shared" si="122"/>
+        <v>1887.6325929050854</v>
+      </c>
+      <c r="CN40" s="6">
+        <f t="shared" si="122"/>
+        <v>1868.7562669760346</v>
+      </c>
+      <c r="CO40" s="6">
+        <f t="shared" si="122"/>
+        <v>1850.0687043062742</v>
+      </c>
+      <c r="CP40" s="6">
+        <f t="shared" si="122"/>
+        <v>1831.5680172632115</v>
+      </c>
+      <c r="CQ40" s="6">
+        <f t="shared" si="122"/>
+        <v>1813.2523370905794</v>
+      </c>
+      <c r="CR40" s="6">
+        <f t="shared" si="122"/>
+        <v>1795.1198137196736</v>
+      </c>
+      <c r="CS40" s="6">
+        <f t="shared" si="122"/>
+        <v>1777.1686155824768</v>
+      </c>
+      <c r="CT40" s="6">
+        <f t="shared" si="122"/>
+        <v>1759.3969294266522</v>
+      </c>
+      <c r="CU40" s="6">
+        <f t="shared" si="122"/>
+        <v>1741.8029601323856</v>
+      </c>
+      <c r="CV40" s="6">
+        <f t="shared" si="122"/>
+        <v>1724.3849305310616</v>
+      </c>
+      <c r="CW40" s="6">
+        <f t="shared" si="122"/>
+        <v>1707.1410812257509</v>
+      </c>
+      <c r="CX40" s="6">
+        <f t="shared" si="122"/>
+        <v>1690.0696704134934</v>
+      </c>
+      <c r="CY40" s="6">
+        <f t="shared" ref="CY40:ER40" si="123">CX40*(1+$AN$18)</f>
+        <v>1673.1689737093584</v>
+      </c>
+      <c r="CZ40" s="6">
         <f t="shared" si="123"/>
-        <v>3009.8787653787172</v>
-      </c>
-      <c r="AK40" s="6">
+        <v>1656.4372839722648</v>
+      </c>
+      <c r="DA40" s="6">
         <f t="shared" si="123"/>
-        <v>2979.7799777249302</v>
-      </c>
-      <c r="AL40" s="6">
+        <v>1639.8729111325422</v>
+      </c>
+      <c r="DB40" s="6">
         <f t="shared" si="123"/>
-        <v>2949.9821779476811</v>
-      </c>
-      <c r="AM40" s="6">
+        <v>1623.4741820212168</v>
+      </c>
+      <c r="DC40" s="6">
         <f t="shared" si="123"/>
-        <v>2920.4823561682042</v>
-      </c>
-      <c r="AN40" s="6">
+        <v>1607.2394402010048</v>
+      </c>
+      <c r="DD40" s="6">
         <f t="shared" si="123"/>
-        <v>2891.2775326065221</v>
-      </c>
-      <c r="AO40" s="6">
+        <v>1591.1670457989946</v>
+      </c>
+      <c r="DE40" s="6">
         <f t="shared" si="123"/>
-        <v>2862.3647572804566</v>
-      </c>
-      <c r="AP40" s="6">
+        <v>1575.2553753410048</v>
+      </c>
+      <c r="DF40" s="6">
         <f t="shared" si="123"/>
-        <v>2833.741109707652</v>
-      </c>
-      <c r="AQ40" s="6">
+        <v>1559.5028215875948</v>
+      </c>
+      <c r="DG40" s="6">
         <f t="shared" si="123"/>
-        <v>2805.4036986105752</v>
-      </c>
-      <c r="AR40" s="6">
+        <v>1543.9077933717188</v>
+      </c>
+      <c r="DH40" s="6">
         <f t="shared" si="123"/>
-        <v>2777.3496616244693</v>
-      </c>
-      <c r="AS40" s="6">
+        <v>1528.4687154380015</v>
+      </c>
+      <c r="DI40" s="6">
         <f t="shared" si="123"/>
-        <v>2749.5761650082245</v>
-      </c>
-      <c r="AT40" s="6">
+        <v>1513.1840282836215</v>
+      </c>
+      <c r="DJ40" s="6">
         <f t="shared" si="123"/>
-        <v>2722.0804033581421</v>
-      </c>
-      <c r="AU40" s="6">
+        <v>1498.0521880007852</v>
+      </c>
+      <c r="DK40" s="6">
         <f t="shared" si="123"/>
-        <v>2694.8595993245608</v>
-      </c>
-      <c r="AV40" s="6">
+        <v>1483.0716661207773</v>
+      </c>
+      <c r="DL40" s="6">
         <f t="shared" si="123"/>
-        <v>2667.911003331315</v>
-      </c>
-      <c r="AW40" s="6">
+        <v>1468.2409494595695</v>
+      </c>
+      <c r="DM40" s="6">
         <f t="shared" si="123"/>
-        <v>2641.231893298002</v>
-      </c>
-      <c r="AX40" s="6">
+        <v>1453.5585399649738</v>
+      </c>
+      <c r="DN40" s="6">
         <f t="shared" si="123"/>
-        <v>2614.8195743650217</v>
-      </c>
-      <c r="AY40" s="6">
+        <v>1439.022954565324</v>
+      </c>
+      <c r="DO40" s="6">
         <f t="shared" si="123"/>
-        <v>2588.6713786213713</v>
-      </c>
-      <c r="AZ40" s="6">
+        <v>1424.6327250196707</v>
+      </c>
+      <c r="DP40" s="6">
         <f t="shared" si="123"/>
-        <v>2562.7846648351574</v>
-      </c>
-      <c r="BA40" s="6">
+        <v>1410.3863977694739</v>
+      </c>
+      <c r="DQ40" s="6">
         <f t="shared" si="123"/>
-        <v>2537.1568181868056</v>
-      </c>
-      <c r="BB40" s="6">
+        <v>1396.2825337917791</v>
+      </c>
+      <c r="DR40" s="6">
         <f t="shared" si="123"/>
-        <v>2511.7852500049376</v>
-      </c>
-      <c r="BC40" s="6">
+        <v>1382.3197084538613</v>
+      </c>
+      <c r="DS40" s="6">
         <f t="shared" si="123"/>
-        <v>2486.667397504888</v>
-      </c>
-      <c r="BD40" s="6">
+        <v>1368.4965113693227</v>
+      </c>
+      <c r="DT40" s="6">
         <f t="shared" si="123"/>
-        <v>2461.8007235298392</v>
-      </c>
-      <c r="BE40" s="6">
+        <v>1354.8115462556293</v>
+      </c>
+      <c r="DU40" s="6">
         <f t="shared" si="123"/>
-        <v>2437.1827162945406</v>
-      </c>
-      <c r="BF40" s="6">
+        <v>1341.263430793073</v>
+      </c>
+      <c r="DV40" s="6">
         <f t="shared" si="123"/>
-        <v>2412.8108891315951</v>
-      </c>
-      <c r="BG40" s="6">
+        <v>1327.8507964851422</v>
+      </c>
+      <c r="DW40" s="6">
         <f t="shared" si="123"/>
-        <v>2388.682780240279</v>
-      </c>
-      <c r="BH40" s="6">
+        <v>1314.5722885202906</v>
+      </c>
+      <c r="DX40" s="6">
         <f t="shared" si="123"/>
-        <v>2364.7959524378762</v>
-      </c>
-      <c r="BI40" s="6">
+        <v>1301.4265656350876</v>
+      </c>
+      <c r="DY40" s="6">
         <f t="shared" si="123"/>
-        <v>2341.1479929134975</v>
-      </c>
-      <c r="BJ40" s="6">
+        <v>1288.4122999787367</v>
+      </c>
+      <c r="DZ40" s="6">
         <f t="shared" si="123"/>
-        <v>2317.7365129843624</v>
-      </c>
-      <c r="BK40" s="6">
+        <v>1275.5281769789492</v>
+      </c>
+      <c r="EA40" s="6">
         <f t="shared" si="123"/>
-        <v>2294.5591478545189</v>
-      </c>
-      <c r="BL40" s="6">
+        <v>1262.7728952091597</v>
+      </c>
+      <c r="EB40" s="6">
         <f t="shared" si="123"/>
-        <v>2271.6135563759735</v>
-      </c>
-      <c r="BM40" s="6">
+        <v>1250.1451662570682</v>
+      </c>
+      <c r="EC40" s="6">
         <f t="shared" si="123"/>
-        <v>2248.8974208122136</v>
-      </c>
-      <c r="BN40" s="6">
+        <v>1237.6437145944976</v>
+      </c>
+      <c r="ED40" s="6">
         <f t="shared" si="123"/>
-        <v>2226.4084466040913</v>
-      </c>
-      <c r="BO40" s="6">
+        <v>1225.2672774485527</v>
+      </c>
+      <c r="EE40" s="6">
         <f t="shared" si="123"/>
-        <v>2204.1443621380504</v>
-      </c>
-      <c r="BP40" s="6">
+        <v>1213.0146046740672</v>
+      </c>
+      <c r="EF40" s="6">
         <f t="shared" si="123"/>
-        <v>2182.1029185166699</v>
-      </c>
-      <c r="BQ40" s="6">
+        <v>1200.8844586273265</v>
+      </c>
+      <c r="EG40" s="6">
         <f t="shared" si="123"/>
-        <v>2160.281889331503</v>
-      </c>
-      <c r="BR40" s="6">
+        <v>1188.8756140410533</v>
+      </c>
+      <c r="EH40" s="6">
         <f t="shared" si="123"/>
-        <v>2138.6790704381879</v>
-      </c>
-      <c r="BS40" s="6">
+        <v>1176.9868579006427</v>
+      </c>
+      <c r="EI40" s="6">
         <f t="shared" si="123"/>
-        <v>2117.292279733806</v>
-      </c>
-      <c r="BT40" s="6">
+        <v>1165.2169893216362</v>
+      </c>
+      <c r="EJ40" s="6">
         <f t="shared" si="123"/>
-        <v>2096.1193569364677</v>
-      </c>
-      <c r="BU40" s="6">
+        <v>1153.5648194284199</v>
+      </c>
+      <c r="EK40" s="6">
         <f t="shared" si="123"/>
-        <v>2075.158163367103</v>
-      </c>
-      <c r="BV40" s="6">
+        <v>1142.0291712341357</v>
+      </c>
+      <c r="EL40" s="6">
         <f t="shared" si="123"/>
-        <v>2054.4065817334322</v>
-      </c>
-      <c r="BW40" s="6">
+        <v>1130.6088795217943</v>
+      </c>
+      <c r="EM40" s="6">
         <f t="shared" si="123"/>
-        <v>2033.8625159160979</v>
-      </c>
-      <c r="BX40" s="6">
+        <v>1119.3027907265764</v>
+      </c>
+      <c r="EN40" s="6">
         <f t="shared" si="123"/>
-        <v>2013.5238907569369</v>
-      </c>
-      <c r="BY40" s="6">
+        <v>1108.1097628193106</v>
+      </c>
+      <c r="EO40" s="6">
         <f t="shared" si="123"/>
-        <v>1993.3886518493675</v>
-      </c>
-      <c r="BZ40" s="6">
+        <v>1097.0286651911174</v>
+      </c>
+      <c r="EP40" s="6">
         <f t="shared" si="123"/>
-        <v>1973.4547653308739</v>
-      </c>
-      <c r="CA40" s="6">
+        <v>1086.0583785392062</v>
+      </c>
+      <c r="EQ40" s="6">
         <f t="shared" si="123"/>
-        <v>1953.7202176775652</v>
-      </c>
-      <c r="CB40" s="6">
+        <v>1075.1977947538142</v>
+      </c>
+      <c r="ER40" s="6">
         <f t="shared" si="123"/>
-        <v>1934.1830155007895</v>
-      </c>
-      <c r="CC40" s="6">
-        <f t="shared" si="123"/>
-        <v>1914.8411853457815</v>
-      </c>
-      <c r="CD40" s="6">
-        <f t="shared" si="123"/>
-        <v>1895.6927734923236</v>
-      </c>
-      <c r="CE40" s="6">
-        <f t="shared" si="123"/>
-        <v>1876.7358457574003</v>
-      </c>
-      <c r="CF40" s="6">
-        <f t="shared" si="123"/>
-        <v>1857.9684872998262</v>
-      </c>
-      <c r="CG40" s="6">
-        <f t="shared" si="123"/>
-        <v>1839.3888024268279</v>
-      </c>
-      <c r="CH40" s="6">
-        <f t="shared" si="123"/>
-        <v>1820.9949144025595</v>
-      </c>
-      <c r="CI40" s="6">
-        <f t="shared" si="123"/>
-        <v>1802.7849652585339</v>
-      </c>
-      <c r="CJ40" s="6">
-        <f t="shared" si="123"/>
-        <v>1784.7571156059487</v>
-      </c>
-      <c r="CK40" s="6">
-        <f t="shared" si="123"/>
-        <v>1766.9095444498892</v>
-      </c>
-      <c r="CL40" s="6">
-        <f t="shared" si="123"/>
-        <v>1749.2404490053902</v>
-      </c>
-      <c r="CM40" s="6">
-        <f t="shared" si="123"/>
-        <v>1731.7480445153362</v>
-      </c>
-      <c r="CN40" s="6">
-        <f t="shared" si="123"/>
-        <v>1714.4305640701828</v>
-      </c>
-      <c r="CO40" s="6">
-        <f t="shared" si="123"/>
-        <v>1697.286258429481</v>
-      </c>
-      <c r="CP40" s="6">
-        <f t="shared" si="123"/>
-        <v>1680.3133958451863</v>
-      </c>
-      <c r="CQ40" s="6">
-        <f t="shared" si="123"/>
-        <v>1663.5102618867345</v>
-      </c>
-      <c r="CR40" s="6">
-        <f t="shared" si="123"/>
-        <v>1646.875159267867</v>
-      </c>
-      <c r="CS40" s="6">
-        <f t="shared" si="123"/>
-        <v>1630.4064076751883</v>
-      </c>
-      <c r="CT40" s="6">
-        <f t="shared" si="123"/>
-        <v>1614.1023435984364</v>
-      </c>
-      <c r="CU40" s="6">
-        <f t="shared" ref="CU40:EN40" si="124">CT40*(1+$AJ$18)</f>
-        <v>1597.961320162452</v>
-      </c>
-      <c r="CV40" s="6">
-        <f t="shared" si="124"/>
-        <v>1581.9817069608275</v>
-      </c>
-      <c r="CW40" s="6">
-        <f t="shared" si="124"/>
-        <v>1566.1618898912193</v>
-      </c>
-      <c r="CX40" s="6">
-        <f t="shared" si="124"/>
-        <v>1550.5002709923072</v>
-      </c>
-      <c r="CY40" s="6">
-        <f t="shared" si="124"/>
-        <v>1534.9952682823841</v>
-      </c>
-      <c r="CZ40" s="6">
-        <f t="shared" si="124"/>
-        <v>1519.6453155995603</v>
-      </c>
-      <c r="DA40" s="6">
-        <f t="shared" si="124"/>
-        <v>1504.4488624435646</v>
-      </c>
-      <c r="DB40" s="6">
-        <f t="shared" si="124"/>
-        <v>1489.404373819129</v>
-      </c>
-      <c r="DC40" s="6">
-        <f t="shared" si="124"/>
-        <v>1474.5103300809376</v>
-      </c>
-      <c r="DD40" s="6">
-        <f t="shared" si="124"/>
-        <v>1459.7652267801282</v>
-      </c>
-      <c r="DE40" s="6">
-        <f t="shared" si="124"/>
-        <v>1445.1675745123268</v>
-      </c>
-      <c r="DF40" s="6">
-        <f t="shared" si="124"/>
-        <v>1430.7158987672035</v>
-      </c>
-      <c r="DG40" s="6">
-        <f t="shared" si="124"/>
-        <v>1416.4087397795315</v>
-      </c>
-      <c r="DH40" s="6">
-        <f t="shared" si="124"/>
-        <v>1402.2446523817362</v>
-      </c>
-      <c r="DI40" s="6">
-        <f t="shared" si="124"/>
-        <v>1388.2222058579189</v>
-      </c>
-      <c r="DJ40" s="6">
-        <f t="shared" si="124"/>
-        <v>1374.3399837993397</v>
-      </c>
-      <c r="DK40" s="6">
-        <f t="shared" si="124"/>
-        <v>1360.5965839613464</v>
-      </c>
-      <c r="DL40" s="6">
-        <f t="shared" si="124"/>
-        <v>1346.990618121733</v>
-      </c>
-      <c r="DM40" s="6">
-        <f t="shared" si="124"/>
-        <v>1333.5207119405156</v>
-      </c>
-      <c r="DN40" s="6">
-        <f t="shared" si="124"/>
-        <v>1320.1855048211105</v>
-      </c>
-      <c r="DO40" s="6">
-        <f t="shared" si="124"/>
-        <v>1306.9836497728993</v>
-      </c>
-      <c r="DP40" s="6">
-        <f t="shared" si="124"/>
-        <v>1293.9138132751702</v>
-      </c>
-      <c r="DQ40" s="6">
-        <f t="shared" si="124"/>
-        <v>1280.9746751424186</v>
-      </c>
-      <c r="DR40" s="6">
-        <f t="shared" si="124"/>
-        <v>1268.1649283909944</v>
-      </c>
-      <c r="DS40" s="6">
-        <f t="shared" si="124"/>
-        <v>1255.4832791070844</v>
-      </c>
-      <c r="DT40" s="6">
-        <f t="shared" si="124"/>
-        <v>1242.9284463160136</v>
-      </c>
-      <c r="DU40" s="6">
-        <f t="shared" si="124"/>
-        <v>1230.4991618528534</v>
-      </c>
-      <c r="DV40" s="6">
-        <f t="shared" si="124"/>
-        <v>1218.1941702343249</v>
-      </c>
-      <c r="DW40" s="6">
-        <f t="shared" si="124"/>
-        <v>1206.0122285319817</v>
-      </c>
-      <c r="DX40" s="6">
-        <f t="shared" si="124"/>
-        <v>1193.952106246662</v>
-      </c>
-      <c r="DY40" s="6">
-        <f t="shared" si="124"/>
-        <v>1182.0125851841954</v>
-      </c>
-      <c r="DZ40" s="6">
-        <f t="shared" si="124"/>
-        <v>1170.1924593323533</v>
-      </c>
-      <c r="EA40" s="6">
-        <f t="shared" si="124"/>
-        <v>1158.4905347390297</v>
-      </c>
-      <c r="EB40" s="6">
-        <f t="shared" si="124"/>
-        <v>1146.9056293916394</v>
-      </c>
-      <c r="EC40" s="6">
-        <f t="shared" si="124"/>
-        <v>1135.4365730977231</v>
-      </c>
-      <c r="ED40" s="6">
-        <f t="shared" si="124"/>
-        <v>1124.0822073667459</v>
-      </c>
-      <c r="EE40" s="6">
-        <f t="shared" si="124"/>
-        <v>1112.8413852930785</v>
-      </c>
-      <c r="EF40" s="6">
-        <f t="shared" si="124"/>
-        <v>1101.7129714401476</v>
-      </c>
-      <c r="EG40" s="6">
-        <f t="shared" si="124"/>
-        <v>1090.695841725746</v>
-      </c>
-      <c r="EH40" s="6">
-        <f t="shared" si="124"/>
-        <v>1079.7888833084885</v>
-      </c>
-      <c r="EI40" s="6">
-        <f t="shared" si="124"/>
-        <v>1068.9909944754036</v>
-      </c>
-      <c r="EJ40" s="6">
-        <f t="shared" si="124"/>
-        <v>1058.3010845306496</v>
-      </c>
-      <c r="EK40" s="6">
-        <f t="shared" si="124"/>
-        <v>1047.7180736853431</v>
-      </c>
-      <c r="EL40" s="6">
-        <f t="shared" si="124"/>
-        <v>1037.2408929484898</v>
-      </c>
-      <c r="EM40" s="6">
-        <f t="shared" si="124"/>
-        <v>1026.8684840190049</v>
-      </c>
-      <c r="EN40" s="6">
-        <f t="shared" si="124"/>
-        <v>1016.5997991788148</v>
-      </c>
-    </row>
-    <row r="43" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="AJ43" s="10">
-        <f>NPV(AJ19,W40:EN40)</f>
-        <v>28943.426750104489</v>
-      </c>
-    </row>
-    <row r="44" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="AJ44" s="2">
+        <v>1064.4458168062761</v>
+      </c>
+    </row>
+    <row r="43" spans="2:148" x14ac:dyDescent="0.3">
+      <c r="AN43" s="2">
+        <f>NPV(AN19,AB40:ER40)</f>
+        <v>32093.213717611809</v>
+      </c>
+    </row>
+    <row r="44" spans="2:148" x14ac:dyDescent="0.3">
+      <c r="AN44" s="2">
         <f>Main!D8</f>
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="45" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="AJ45" s="10">
-        <f>AJ43+AJ44</f>
-        <v>31003.426750104489</v>
-      </c>
-    </row>
-    <row r="46" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="AJ46" s="1">
-        <f>AJ45/AG14</f>
-        <v>164.91184441544939</v>
-      </c>
-    </row>
-    <row r="47" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="AJ47" s="1">
+        <v>2476.8000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:148" x14ac:dyDescent="0.3">
+      <c r="AN45" s="2">
+        <f>AN43+AN44</f>
+        <v>34570.013717611808</v>
+      </c>
+    </row>
+    <row r="46" spans="2:148" x14ac:dyDescent="0.3">
+      <c r="AN46" s="1">
+        <f>AN45/AK14</f>
+        <v>181.94744061900951</v>
+      </c>
+    </row>
+    <row r="47" spans="2:148" x14ac:dyDescent="0.3">
+      <c r="AN47" s="1">
         <f>Main!D3</f>
-        <v>218.54</v>
-      </c>
-    </row>
-    <row r="48" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="AJ48" s="9">
-        <f>AJ46/AJ47-1</f>
-        <v>-0.24539285981765624</v>
+        <v>165.1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:148" x14ac:dyDescent="0.3">
+      <c r="AN48" s="9">
+        <f>AN46/AN47-1</f>
+        <v>0.10204385596008181</v>
       </c>
     </row>
   </sheetData>
